--- a/research/traditional_assets/database/data/canada/canada_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_healthcare_products.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,43 +581,46 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Healthcare Products</t>
         </is>
+      </c>
+      <c r="D2">
+        <v>0.04611</v>
       </c>
       <c r="F2">
         <v>0.061</v>
       </c>
       <c r="G2">
-        <v>0.1955593509820666</v>
+        <v>0.1722430650661634</v>
       </c>
       <c r="H2">
-        <v>0.1251067463706234</v>
+        <v>0.09508816761870259</v>
       </c>
       <c r="I2">
-        <v>0.04324927830739501</v>
+        <v>0.01509145761974454</v>
       </c>
       <c r="J2">
-        <v>0.04324927830739501</v>
+        <v>0.01509145761974454</v>
       </c>
       <c r="K2">
-        <v>-368</v>
+        <v>-521.559</v>
       </c>
       <c r="L2">
-        <v>-0.07856532877882152</v>
+        <v>-0.1083405742626456</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>10.236</v>
       </c>
       <c r="N2">
-        <v>0.001572277601333292</v>
+        <v>0.00148230101310843</v>
       </c>
       <c r="O2">
-        <v>-0.02717391304347826</v>
+        <v>-0.01962577579909464</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -629,79 +632,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>10</v>
+        <v>10.236</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>329</v>
+        <v>383.23</v>
       </c>
       <c r="V2">
-        <v>0.05172793308386529</v>
+        <v>0.0554965042256295</v>
       </c>
       <c r="W2">
-        <v>-0.05398269033299105</v>
+        <v>-0.4320652173913044</v>
       </c>
       <c r="X2">
-        <v>0.115534001773422</v>
+        <v>0.09251376067924655</v>
       </c>
       <c r="Y2">
-        <v>-0.1695166921064131</v>
+        <v>-0.524578978070551</v>
       </c>
       <c r="Z2">
-        <v>0.7197182942896443</v>
+        <v>0.7230433207923469</v>
       </c>
       <c r="AA2">
-        <v>0.03112729681265645</v>
+        <v>-1</v>
       </c>
       <c r="AB2">
-        <v>0.09445601860441014</v>
+        <v>0.09068416350128548</v>
       </c>
       <c r="AC2">
-        <v>-0.06332872179175368</v>
+        <v>-1.089889922207992</v>
       </c>
       <c r="AD2">
-        <v>4629</v>
+        <v>4703.413</v>
       </c>
       <c r="AE2">
-        <v>107.1019020408087</v>
+        <v>111.65340853987</v>
       </c>
       <c r="AF2">
-        <v>4736.101902040808</v>
+        <v>4815.066408539869</v>
       </c>
       <c r="AG2">
-        <v>4407.101902040808</v>
+        <v>4431.83640853987</v>
       </c>
       <c r="AH2">
-        <v>0.4268180465754771</v>
+        <v>0.4108226904021725</v>
       </c>
       <c r="AI2">
-        <v>0.4155531768293432</v>
+        <v>0.415634068778575</v>
       </c>
       <c r="AJ2">
-        <v>0.4093042010093074</v>
+        <v>0.3909070055768731</v>
       </c>
       <c r="AK2">
-        <v>0.3981804595807162</v>
+        <v>0.3956417669686046</v>
       </c>
       <c r="AL2">
-        <v>400</v>
+        <v>412.055</v>
       </c>
       <c r="AM2">
-        <v>387</v>
+        <v>396.846</v>
       </c>
       <c r="AN2">
-        <v>6.908955223880597</v>
+        <v>8.588763458139161</v>
       </c>
       <c r="AO2">
-        <v>0.4725</v>
+        <v>0.141563626214947</v>
       </c>
       <c r="AP2">
-        <v>6.577764032896729</v>
+        <v>8.092845471600715</v>
       </c>
       <c r="AQ2">
-        <v>0.4883720930232558</v>
+        <v>0.1469890083306875</v>
       </c>
     </row>
     <row r="3">
@@ -775,10 +778,10 @@
         <v>-0.05398269033299105</v>
       </c>
       <c r="X3">
-        <v>0.115534001773422</v>
+        <v>0.1154891690103688</v>
       </c>
       <c r="Y3">
-        <v>-0.1695166921064131</v>
+        <v>-0.1694718593433599</v>
       </c>
       <c r="Z3">
         <v>0.7197182942896443</v>
@@ -787,10 +790,10 @@
         <v>0.03112729681265645</v>
       </c>
       <c r="AB3">
-        <v>0.09445601860441014</v>
+        <v>0.0944303212737059</v>
       </c>
       <c r="AC3">
-        <v>-0.06332872179175368</v>
+        <v>-0.06330302446104945</v>
       </c>
       <c r="AD3">
         <v>4629</v>
@@ -833,6 +836,1762 @@
       </c>
       <c r="AQ3">
         <v>0.4883720930232558</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aurora Spine Corporation (TSXV:ASG)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.08929999999999999</v>
+      </c>
+      <c r="G4">
+        <v>0.001834319526627221</v>
+      </c>
+      <c r="H4">
+        <v>-0.04514792899408285</v>
+      </c>
+      <c r="I4">
+        <v>-0.02710059171597633</v>
+      </c>
+      <c r="J4">
+        <v>-0.02710059171597633</v>
+      </c>
+      <c r="K4">
+        <v>-0.636</v>
+      </c>
+      <c r="L4">
+        <v>-0.03763313609467456</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.882</v>
+      </c>
+      <c r="V4">
+        <v>0.042</v>
+      </c>
+      <c r="W4">
+        <v>-0.1705093833780161</v>
+      </c>
+      <c r="X4">
+        <v>0.0966712835592704</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2671806669372865</v>
+      </c>
+      <c r="Z4">
+        <v>2.401591587324144</v>
+      </c>
+      <c r="AA4">
+        <v>-0.06508455307659515</v>
+      </c>
+      <c r="AB4">
+        <v>0.0892476479653716</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1543322010419668</v>
+      </c>
+      <c r="AD4">
+        <v>3.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>3.7</v>
+      </c>
+      <c r="AG4">
+        <v>2.818</v>
+      </c>
+      <c r="AH4">
+        <v>0.1497975708502024</v>
+      </c>
+      <c r="AI4">
+        <v>0.4243119266055047</v>
+      </c>
+      <c r="AJ4">
+        <v>0.1183138802586279</v>
+      </c>
+      <c r="AK4">
+        <v>0.3595304924725696</v>
+      </c>
+      <c r="AL4">
+        <v>0.178</v>
+      </c>
+      <c r="AM4">
+        <v>0.178</v>
+      </c>
+      <c r="AN4">
+        <v>15.16393442622951</v>
+      </c>
+      <c r="AO4">
+        <v>-2.573033707865169</v>
+      </c>
+      <c r="AP4">
+        <v>11.54918032786885</v>
+      </c>
+      <c r="AQ4">
+        <v>-2.573033707865169</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nanalysis Scientific Corp. (TSXV:NSCI)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.366</v>
+      </c>
+      <c r="G5">
+        <v>-0.2471698113207547</v>
+      </c>
+      <c r="H5">
+        <v>-0.3144654088050314</v>
+      </c>
+      <c r="I5">
+        <v>-0.1324772096657333</v>
+      </c>
+      <c r="J5">
+        <v>-0.1324772096657333</v>
+      </c>
+      <c r="K5">
+        <v>-6.13</v>
+      </c>
+      <c r="L5">
+        <v>-0.1927672955974843</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.165</v>
+      </c>
+      <c r="V5">
+        <v>0.006547619047619048</v>
+      </c>
+      <c r="W5">
+        <v>-0.326063829787234</v>
+      </c>
+      <c r="X5">
+        <v>0.1083282791170878</v>
+      </c>
+      <c r="Y5">
+        <v>-0.4343921089043219</v>
+      </c>
+      <c r="Z5">
+        <v>1.166378529857733</v>
+      </c>
+      <c r="AA5">
+        <v>-0.1545185730495727</v>
+      </c>
+      <c r="AB5">
+        <v>0.08556619991573863</v>
+      </c>
+      <c r="AC5">
+        <v>-0.2400847729653113</v>
+      </c>
+      <c r="AD5">
+        <v>13.1</v>
+      </c>
+      <c r="AE5">
+        <v>0.2138763368516019</v>
+      </c>
+      <c r="AF5">
+        <v>13.3138763368516</v>
+      </c>
+      <c r="AG5">
+        <v>13.1488763368516</v>
+      </c>
+      <c r="AH5">
+        <v>0.3456903745653968</v>
+      </c>
+      <c r="AI5">
+        <v>0.4435906974303274</v>
+      </c>
+      <c r="AJ5">
+        <v>0.3428751398438265</v>
+      </c>
+      <c r="AK5">
+        <v>0.4405149523373488</v>
+      </c>
+      <c r="AL5">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="AM5">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="AN5">
+        <v>-2.183333333333333</v>
+      </c>
+      <c r="AO5">
+        <v>-5.289765721331689</v>
+      </c>
+      <c r="AP5">
+        <v>-2.191479389475267</v>
+      </c>
+      <c r="AQ5">
+        <v>-5.289765721331689</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ASEP Medical Holdings Inc. (CNSX:ASEP)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>-21.84530386740332</v>
+      </c>
+      <c r="H6">
+        <v>-22.32044198895028</v>
+      </c>
+      <c r="I6">
+        <v>-17.95580110497238</v>
+      </c>
+      <c r="J6">
+        <v>-17.95580110497238</v>
+      </c>
+      <c r="K6">
+        <v>-3.43</v>
+      </c>
+      <c r="L6">
+        <v>-18.95027624309392</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="V6">
+        <v>0.003061224489795918</v>
+      </c>
+      <c r="W6">
+        <v>-0.3580375782881002</v>
+      </c>
+      <c r="X6">
+        <v>0.09328211659350227</v>
+      </c>
+      <c r="Y6">
+        <v>-0.4513196948816025</v>
+      </c>
+      <c r="Z6">
+        <v>0.01928404005966333</v>
+      </c>
+      <c r="AA6">
+        <v>-0.3462603878116344</v>
+      </c>
+      <c r="AB6">
+        <v>0.08979038130658748</v>
+      </c>
+      <c r="AC6">
+        <v>-0.4360507691182218</v>
+      </c>
+      <c r="AD6">
+        <v>0.217</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0.217</v>
+      </c>
+      <c r="AG6">
+        <v>0.208</v>
+      </c>
+      <c r="AH6">
+        <v>0.06873614190687362</v>
+      </c>
+      <c r="AI6">
+        <v>0.01454716095729704</v>
+      </c>
+      <c r="AJ6">
+        <v>0.06607369758576874</v>
+      </c>
+      <c r="AK6">
+        <v>0.01395224040783472</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-0.017</v>
+      </c>
+      <c r="AN6">
+        <v>-0.09434782608695653</v>
+      </c>
+      <c r="AP6">
+        <v>-0.09043478260869565</v>
+      </c>
+      <c r="AQ6">
+        <v>191.1764705882353</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Venus Concept Inc. (NasdaqCM:VERO)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>-0.0892</v>
+      </c>
+      <c r="G7">
+        <v>-0.2577380952380952</v>
+      </c>
+      <c r="H7">
+        <v>-0.3601190476190476</v>
+      </c>
+      <c r="I7">
+        <v>-0.4082965183399098</v>
+      </c>
+      <c r="J7">
+        <v>-0.4082965183399098</v>
+      </c>
+      <c r="K7">
+        <v>-50.1</v>
+      </c>
+      <c r="L7">
+        <v>-0.7455357142857143</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>4.49</v>
+      </c>
+      <c r="V7">
+        <v>1.644688644688645</v>
+      </c>
+      <c r="W7">
+        <v>4.106557377049181</v>
+      </c>
+      <c r="X7">
+        <v>0.5629894966559543</v>
+      </c>
+      <c r="Y7">
+        <v>3.543567880393226</v>
+      </c>
+      <c r="Z7">
+        <v>1.014988753340952</v>
+      </c>
+      <c r="AA7">
+        <v>-0.4144163741432761</v>
+      </c>
+      <c r="AB7">
+        <v>0.07658579707146654</v>
+      </c>
+      <c r="AC7">
+        <v>-0.4910021712147427</v>
+      </c>
+      <c r="AD7">
+        <v>34.6</v>
+      </c>
+      <c r="AE7">
+        <v>4.337630162209679</v>
+      </c>
+      <c r="AF7">
+        <v>38.93763016220968</v>
+      </c>
+      <c r="AG7">
+        <v>34.44763016220968</v>
+      </c>
+      <c r="AH7">
+        <v>0.9344815150424378</v>
+      </c>
+      <c r="AI7">
+        <v>0.7860212536350533</v>
+      </c>
+      <c r="AJ7">
+        <v>0.9265687460957373</v>
+      </c>
+      <c r="AK7">
+        <v>0.7646935041459226</v>
+      </c>
+      <c r="AL7">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="AM7">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="AN7">
+        <v>-1.526246140273489</v>
+      </c>
+      <c r="AO7">
+        <v>-3.256083429895713</v>
+      </c>
+      <c r="AP7">
+        <v>-1.519524929960727</v>
+      </c>
+      <c r="AQ7">
+        <v>-3.256083429895713</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Zentek Ltd. (TSXV:ZEN)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>-272.1724137931034</v>
+      </c>
+      <c r="H8">
+        <v>-294.4827586206896</v>
+      </c>
+      <c r="I8">
+        <v>-256.8965517241379</v>
+      </c>
+      <c r="J8">
+        <v>-256.8965517241379</v>
+      </c>
+      <c r="K8">
+        <v>-7.95</v>
+      </c>
+      <c r="L8">
+        <v>-274.1379310344827</v>
+      </c>
+      <c r="M8">
+        <v>0.224</v>
+      </c>
+      <c r="N8">
+        <v>0.002345549738219896</v>
+      </c>
+      <c r="O8">
+        <v>-0.02817610062893082</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0.224</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>2.17</v>
+      </c>
+      <c r="V8">
+        <v>0.02272251308900523</v>
+      </c>
+      <c r="W8">
+        <v>-0.4320652173913044</v>
+      </c>
+      <c r="X8">
+        <v>0.0910755142882895</v>
+      </c>
+      <c r="Y8">
+        <v>-0.5231407316795939</v>
+      </c>
+      <c r="Z8">
+        <v>0.002099015634047481</v>
+      </c>
+      <c r="AA8">
+        <v>-0.539229878401853</v>
+      </c>
+      <c r="AB8">
+        <v>0.09076333796025958</v>
+      </c>
+      <c r="AC8">
+        <v>-0.6299932163621126</v>
+      </c>
+      <c r="AD8">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="AG8">
+        <v>-1.487</v>
+      </c>
+      <c r="AH8">
+        <v>0.007101046962560952</v>
+      </c>
+      <c r="AI8">
+        <v>0.04748661614405896</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.01581696148405008</v>
+      </c>
+      <c r="AK8">
+        <v>-0.1217555064275772</v>
+      </c>
+      <c r="AL8">
+        <v>0.225</v>
+      </c>
+      <c r="AM8">
+        <v>0.05499999999999999</v>
+      </c>
+      <c r="AN8">
+        <v>-0.09539106145251397</v>
+      </c>
+      <c r="AO8">
+        <v>-33.11111111111111</v>
+      </c>
+      <c r="AP8">
+        <v>0.20768156424581</v>
+      </c>
+      <c r="AQ8">
+        <v>-135.4545454545455</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Therma Bright Inc. (TSXV:THRM)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.091</v>
+      </c>
+      <c r="G9">
+        <v>-283</v>
+      </c>
+      <c r="H9">
+        <v>-285.3333333333333</v>
+      </c>
+      <c r="I9">
+        <v>-396.6666666666666</v>
+      </c>
+      <c r="J9">
+        <v>-396.6666666666666</v>
+      </c>
+      <c r="K9">
+        <v>-1.96</v>
+      </c>
+      <c r="L9">
+        <v>-653.3333333333333</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0.108</v>
+      </c>
+      <c r="V9">
+        <v>0.009818181818181818</v>
+      </c>
+      <c r="W9">
+        <v>-1.4</v>
+      </c>
+      <c r="X9">
+        <v>0.09096515881326808</v>
+      </c>
+      <c r="Y9">
+        <v>-1.490965158813268</v>
+      </c>
+      <c r="Z9">
+        <v>0.002054794520547945</v>
+      </c>
+      <c r="AA9">
+        <v>-0.815068493150685</v>
+      </c>
+      <c r="AB9">
+        <v>0.09078074922531687</v>
+      </c>
+      <c r="AC9">
+        <v>-0.9058492423760018</v>
+      </c>
+      <c r="AD9">
+        <v>0.042</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0.042</v>
+      </c>
+      <c r="AG9">
+        <v>-0.066</v>
+      </c>
+      <c r="AH9">
+        <v>0.003803658757471473</v>
+      </c>
+      <c r="AI9">
+        <v>0.03677758318739054</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.006036217303822938</v>
+      </c>
+      <c r="AK9">
+        <v>-0.06382978723404255</v>
+      </c>
+      <c r="AL9">
+        <v>0.005</v>
+      </c>
+      <c r="AM9">
+        <v>-0.009000000000000001</v>
+      </c>
+      <c r="AN9">
+        <v>-0.0368421052631579</v>
+      </c>
+      <c r="AO9">
+        <v>-238</v>
+      </c>
+      <c r="AP9">
+        <v>0.05789473684210527</v>
+      </c>
+      <c r="AQ9">
+        <v>132.2222222222222</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Frequency Exchange Corp. (TSXV:FREQ)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>-1.596006144393241</v>
+      </c>
+      <c r="H10">
+        <v>-1.597542242703533</v>
+      </c>
+      <c r="I10">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="J10">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="K10">
+        <v>-0.973</v>
+      </c>
+      <c r="L10">
+        <v>-1.494623655913978</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0.195</v>
+      </c>
+      <c r="V10">
+        <v>0.02758132956152758</v>
+      </c>
+      <c r="W10">
+        <v>6.006172839506172</v>
+      </c>
+      <c r="X10">
+        <v>0.0930347378396113</v>
+      </c>
+      <c r="Y10">
+        <v>5.913138101666561</v>
+      </c>
+      <c r="Z10">
+        <v>9.573529411764701</v>
+      </c>
+      <c r="AA10">
+        <v>-1</v>
+      </c>
+      <c r="AB10">
+        <v>0.08988992220799204</v>
+      </c>
+      <c r="AC10">
+        <v>-1.089889922207992</v>
+      </c>
+      <c r="AD10">
+        <v>0.469</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0.469</v>
+      </c>
+      <c r="AG10">
+        <v>0.274</v>
+      </c>
+      <c r="AH10">
+        <v>0.06220984215413184</v>
+      </c>
+      <c r="AI10">
+        <v>2.057017543859649</v>
+      </c>
+      <c r="AJ10">
+        <v>0.03730936819172113</v>
+      </c>
+      <c r="AK10">
+        <v>8.303030303030308</v>
+      </c>
+      <c r="AL10">
+        <v>0.033</v>
+      </c>
+      <c r="AM10">
+        <v>0.029</v>
+      </c>
+      <c r="AN10">
+        <v>-0.5153846153846153</v>
+      </c>
+      <c r="AO10">
+        <v>-28.18181818181818</v>
+      </c>
+      <c r="AP10">
+        <v>-0.301098901098901</v>
+      </c>
+      <c r="AQ10">
+        <v>-32.06896551724138</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Scryb Inc. (CNSX:SCYB)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>-10.125</v>
+      </c>
+      <c r="H11">
+        <v>-11.07142857142857</v>
+      </c>
+      <c r="I11">
+        <v>-10.35714285714286</v>
+      </c>
+      <c r="J11">
+        <v>-10.35714285714286</v>
+      </c>
+      <c r="K11">
+        <v>-13.6</v>
+      </c>
+      <c r="L11">
+        <v>-12.14285714285714</v>
+      </c>
+      <c r="M11">
+        <v>0.012</v>
+      </c>
+      <c r="N11">
+        <v>0.003592814371257485</v>
+      </c>
+      <c r="O11">
+        <v>-0.0008823529411764706</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0.012</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>0.047</v>
+      </c>
+      <c r="V11">
+        <v>0.01407185628742515</v>
+      </c>
+      <c r="W11">
+        <v>-2.490842490842491</v>
+      </c>
+      <c r="X11">
+        <v>0.09251376067924655</v>
+      </c>
+      <c r="Y11">
+        <v>-2.583356251521737</v>
+      </c>
+      <c r="Z11">
+        <v>0.1978449037272567</v>
+      </c>
+      <c r="AA11">
+        <v>-1</v>
+      </c>
+      <c r="AB11">
+        <v>0.09010418571350341</v>
+      </c>
+      <c r="AC11">
+        <v>-1.090104185713503</v>
+      </c>
+      <c r="AD11">
+        <v>0.169</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0.169</v>
+      </c>
+      <c r="AG11">
+        <v>0.122</v>
+      </c>
+      <c r="AH11">
+        <v>0.0481618694784839</v>
+      </c>
+      <c r="AI11">
+        <v>0.02104869846805331</v>
+      </c>
+      <c r="AJ11">
+        <v>0.03523974581166956</v>
+      </c>
+      <c r="AK11">
+        <v>0.01528438987722375</v>
+      </c>
+      <c r="AL11">
+        <v>0.205</v>
+      </c>
+      <c r="AM11">
+        <v>0.205</v>
+      </c>
+      <c r="AN11">
+        <v>-0.0155045871559633</v>
+      </c>
+      <c r="AO11">
+        <v>-56.58536585365854</v>
+      </c>
+      <c r="AP11">
+        <v>-0.01119266055045872</v>
+      </c>
+      <c r="AQ11">
+        <v>-56.58536585365854</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Profound Medical Corp. (TSX:PRN)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.223</v>
+      </c>
+      <c r="G12">
+        <v>-1.302895322939866</v>
+      </c>
+      <c r="H12">
+        <v>-3.106904231625835</v>
+      </c>
+      <c r="I12">
+        <v>-3.685968819599109</v>
+      </c>
+      <c r="J12">
+        <v>-3.685968819599109</v>
+      </c>
+      <c r="K12">
+        <v>-31.4</v>
+      </c>
+      <c r="L12">
+        <v>-3.496659242761692</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>27.1</v>
+      </c>
+      <c r="V12">
+        <v>0.1202307009760426</v>
+      </c>
+      <c r="W12">
+        <v>-0.8134715025906735</v>
+      </c>
+      <c r="X12">
+        <v>0.09175373593957653</v>
+      </c>
+      <c r="Y12">
+        <v>-0.9052252385302499</v>
+      </c>
+      <c r="Z12">
+        <v>0.6839299314546838</v>
+      </c>
+      <c r="AA12">
+        <v>-1</v>
+      </c>
+      <c r="AB12">
+        <v>0.09042853331079978</v>
+      </c>
+      <c r="AC12">
+        <v>-1.0904285333108</v>
+      </c>
+      <c r="AD12">
+        <v>6.23</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>6.23</v>
+      </c>
+      <c r="AG12">
+        <v>-20.87</v>
+      </c>
+      <c r="AH12">
+        <v>0.02689634330613479</v>
+      </c>
+      <c r="AI12">
+        <v>0.1668899008840075</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.1020388207108982</v>
+      </c>
+      <c r="AK12">
+        <v>-2.040078201368524</v>
+      </c>
+      <c r="AL12">
+        <v>0.677</v>
+      </c>
+      <c r="AM12">
+        <v>-1.233</v>
+      </c>
+      <c r="AN12">
+        <v>-0.1916923076923077</v>
+      </c>
+      <c r="AO12">
+        <v>-48.89217134416543</v>
+      </c>
+      <c r="AP12">
+        <v>0.6421538461538462</v>
+      </c>
+      <c r="AQ12">
+        <v>26.84509326845094</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ocumetics Technology Corp. (TSXV:OTC)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="K13">
+        <v>-2.13</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>1.48</v>
+      </c>
+      <c r="V13">
+        <v>0.0592</v>
+      </c>
+      <c r="W13">
+        <v>-4.76510067114094</v>
+      </c>
+      <c r="X13">
+        <v>0.09117774341553864</v>
+      </c>
+      <c r="Y13">
+        <v>-4.856278414556479</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>-1</v>
+      </c>
+      <c r="AB13">
+        <v>0.09068416350128548</v>
+      </c>
+      <c r="AC13">
+        <v>-1.090684163501285</v>
+      </c>
+      <c r="AD13">
+        <v>0.256</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0.256</v>
+      </c>
+      <c r="AG13">
+        <v>-1.224</v>
+      </c>
+      <c r="AH13">
+        <v>0.01013620525815648</v>
+      </c>
+      <c r="AI13">
+        <v>-0.2601626016260163</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.05148048452220727</v>
+      </c>
+      <c r="AK13">
+        <v>0.4967532467532467</v>
+      </c>
+      <c r="AL13">
+        <v>0.221</v>
+      </c>
+      <c r="AM13">
+        <v>0.201</v>
+      </c>
+      <c r="AN13">
+        <v>-0.1142857142857143</v>
+      </c>
+      <c r="AO13">
+        <v>-10.72398190045249</v>
+      </c>
+      <c r="AP13">
+        <v>0.5464285714285714</v>
+      </c>
+      <c r="AQ13">
+        <v>-11.7910447761194</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ondine Biomedical Inc. (AIM:OBI)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>-5.487394957983193</v>
+      </c>
+      <c r="H14">
+        <v>-9.327731092436975</v>
+      </c>
+      <c r="I14">
+        <v>-8.991596638655462</v>
+      </c>
+      <c r="J14">
+        <v>-8.991596638655462</v>
+      </c>
+      <c r="K14">
+        <v>-10.4</v>
+      </c>
+      <c r="L14">
+        <v>-8.739495798319329</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0.89</v>
+      </c>
+      <c r="V14">
+        <v>0.02</v>
+      </c>
+      <c r="W14">
+        <v>-3.322683706070288</v>
+      </c>
+      <c r="X14">
+        <v>0.09102920172696571</v>
+      </c>
+      <c r="Y14">
+        <v>-3.413712907797253</v>
+      </c>
+      <c r="Z14">
+        <v>2.191528545119707</v>
+      </c>
+      <c r="AA14">
+        <v>-1</v>
+      </c>
+      <c r="AB14">
+        <v>0.09075152213893052</v>
+      </c>
+      <c r="AC14">
+        <v>-1.090751522138931</v>
+      </c>
+      <c r="AD14">
+        <v>0.256</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0.256</v>
+      </c>
+      <c r="AG14">
+        <v>-0.634</v>
+      </c>
+      <c r="AH14">
+        <v>0.005719903476628832</v>
+      </c>
+      <c r="AI14">
+        <v>0.9481481481481481</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.01445310719007888</v>
+      </c>
+      <c r="AK14">
+        <v>1.02258064516129</v>
+      </c>
+      <c r="AL14">
+        <v>0.047</v>
+      </c>
+      <c r="AM14">
+        <v>0.019</v>
+      </c>
+      <c r="AN14">
+        <v>-0.02438095238095238</v>
+      </c>
+      <c r="AO14">
+        <v>-227.6595744680851</v>
+      </c>
+      <c r="AP14">
+        <v>0.06038095238095238</v>
+      </c>
+      <c r="AQ14">
+        <v>-563.1578947368421</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Perimeter Medical Imaging AI, Inc. (TSXV:PINK)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>-13.69958275382476</v>
+      </c>
+      <c r="H15">
+        <v>-21.9749652294854</v>
+      </c>
+      <c r="I15">
+        <v>-26.70375521557719</v>
+      </c>
+      <c r="J15">
+        <v>-26.70375521557719</v>
+      </c>
+      <c r="K15">
+        <v>-15.5</v>
+      </c>
+      <c r="L15">
+        <v>-21.557719054242</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="V15">
+        <v>0.38582995951417</v>
+      </c>
+      <c r="W15">
+        <v>-0.8244680851063829</v>
+      </c>
+      <c r="X15">
+        <v>0.0910478383465467</v>
+      </c>
+      <c r="Y15">
+        <v>-0.9155159234529296</v>
+      </c>
+      <c r="Z15">
+        <v>0.767342582710781</v>
+      </c>
+      <c r="AA15">
+        <v>-1</v>
+      </c>
+      <c r="AB15">
+        <v>0.09077209982135916</v>
+      </c>
+      <c r="AC15">
+        <v>-1.090772099821359</v>
+      </c>
+      <c r="AD15">
+        <v>0.156</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0.156</v>
+      </c>
+      <c r="AG15">
+        <v>-9.373999999999999</v>
+      </c>
+      <c r="AH15">
+        <v>0.006276150627615064</v>
+      </c>
+      <c r="AI15">
+        <v>0.01204075331892559</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.6116403497324806</v>
+      </c>
+      <c r="AK15">
+        <v>-2.736135434909514</v>
+      </c>
+      <c r="AL15">
+        <v>0.067</v>
+      </c>
+      <c r="AM15">
+        <v>0.067</v>
+      </c>
+      <c r="AN15">
+        <v>-0.008297872340425531</v>
+      </c>
+      <c r="AO15">
+        <v>-286.5671641791045</v>
+      </c>
+      <c r="AP15">
+        <v>0.4986170212765957</v>
+      </c>
+      <c r="AQ15">
+        <v>-286.5671641791045</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Theralase Technologies Inc. (TSXV:TLT)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.00292</v>
+      </c>
+      <c r="G16">
+        <v>-1.641586867305062</v>
+      </c>
+      <c r="H16">
+        <v>-4.555403556771546</v>
+      </c>
+      <c r="I16">
+        <v>-4.418604651162791</v>
+      </c>
+      <c r="J16">
+        <v>-4.418604651162791</v>
+      </c>
+      <c r="K16">
+        <v>-3.2</v>
+      </c>
+      <c r="L16">
+        <v>-4.377564979480164</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0.244</v>
+      </c>
+      <c r="V16">
+        <v>0.005350877192982456</v>
+      </c>
+      <c r="W16">
+        <v>-2.644628099173554</v>
+      </c>
+      <c r="X16">
+        <v>0.09100936279745553</v>
+      </c>
+      <c r="Y16">
+        <v>-2.73563746197101</v>
+      </c>
+      <c r="Z16">
+        <v>0.5463378176382661</v>
+      </c>
+      <c r="AA16">
+        <v>-1</v>
+      </c>
+      <c r="AB16">
+        <v>0.09078430492121679</v>
+      </c>
+      <c r="AC16">
+        <v>-1.090784304921217</v>
+      </c>
+      <c r="AD16">
+        <v>0.235</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0.235</v>
+      </c>
+      <c r="AG16">
+        <v>-0.009000000000000008</v>
+      </c>
+      <c r="AH16">
+        <v>0.005127086287771353</v>
+      </c>
+      <c r="AI16">
+        <v>0.1294765840220386</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.0001974073830361257</v>
+      </c>
+      <c r="AK16">
+        <v>-0.00572883513685551</v>
+      </c>
+      <c r="AL16">
+        <v>0.019</v>
+      </c>
+      <c r="AM16">
+        <v>-0.027</v>
+      </c>
+      <c r="AN16">
+        <v>-0.07580645161290323</v>
+      </c>
+      <c r="AO16">
+        <v>-170</v>
+      </c>
+      <c r="AP16">
+        <v>0.002903225806451615</v>
+      </c>
+      <c r="AQ16">
+        <v>119.6296296296296</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NuGen Medical Devices Inc. (TSXV:NGMD)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Healthcare Products</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>-9.442477876106196</v>
+      </c>
+      <c r="H17">
+        <v>-9.964601769911505</v>
+      </c>
+      <c r="I17">
+        <v>-8.495575221238939</v>
+      </c>
+      <c r="J17">
+        <v>-8.495575221238939</v>
+      </c>
+      <c r="K17">
+        <v>-6.15</v>
+      </c>
+      <c r="L17">
+        <v>-10.88495575221239</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>6.92</v>
+      </c>
+      <c r="V17">
+        <v>0.6123893805309734</v>
+      </c>
+      <c r="W17">
+        <v>68.33333333333334</v>
+      </c>
+      <c r="X17">
+        <v>0.1327307924698036</v>
+      </c>
+      <c r="Y17">
+        <v>68.20060254086354</v>
+      </c>
+      <c r="Z17">
+        <v>0.1902356902356902</v>
+      </c>
+      <c r="AA17">
+        <v>-1</v>
+      </c>
+      <c r="AB17">
+        <v>0.1072813771448742</v>
+      </c>
+      <c r="AC17">
+        <v>-1.107281377144874</v>
+      </c>
+      <c r="AD17">
+        <v>14.3</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>14.3</v>
+      </c>
+      <c r="AG17">
+        <v>7.380000000000001</v>
+      </c>
+      <c r="AH17">
+        <v>0.55859375</v>
+      </c>
+      <c r="AI17">
+        <v>1.519659936238045</v>
+      </c>
+      <c r="AJ17">
+        <v>0.3950749464668095</v>
+      </c>
+      <c r="AK17">
+        <v>2.963855421686746</v>
+      </c>
+      <c r="AL17">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="AM17">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="AN17">
+        <v>-3.25</v>
+      </c>
+      <c r="AO17">
+        <v>-5.122732123799359</v>
+      </c>
+      <c r="AP17">
+        <v>-1.677272727272727</v>
+      </c>
+      <c r="AQ17">
+        <v>-5.122732123799359</v>
       </c>
     </row>
   </sheetData>
@@ -1127,49 +2886,49 @@
         <v>0.925</v>
       </c>
       <c r="F2">
-        <v>3.0264862924606</v>
+        <v>2.54664683944834</v>
       </c>
       <c r="G2">
         <v>7.06880880901613</v>
       </c>
       <c r="H2">
-        <v>6.9558907445629</v>
+        <v>8.280822314955831</v>
       </c>
       <c r="I2">
         <v>0.426818046575477</v>
       </c>
       <c r="J2">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="K2">
         <v>6360.2</v>
       </c>
       <c r="L2">
-        <v>9209.56571748358</v>
+        <v>8776.587547684279</v>
       </c>
       <c r="M2">
         <v>10767.3019020408</v>
       </c>
       <c r="N2">
-        <v>13541.0125163407</v>
+        <v>13995.7384987047</v>
       </c>
       <c r="O2">
         <v>4736.10190204081</v>
       </c>
       <c r="P2">
-        <v>4660.44679885714</v>
+        <v>5548.1509510204</v>
       </c>
       <c r="Q2">
-        <v>0.09445601860441009</v>
+        <v>0.0944303212737059</v>
       </c>
       <c r="R2">
-        <v>0.0844894289502196</v>
+        <v>0.08321262747912089</v>
       </c>
       <c r="S2">
         <v>0.06615</v>
       </c>
       <c r="T2">
-        <v>0.0425565</v>
+        <v>0.042483</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1178,20 +2937,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="W2">
-        <v>0.115534001773422</v>
+        <v>0.115489169010369</v>
       </c>
       <c r="X2">
-        <v>0.114854653362448</v>
+        <v>0.123942254958242</v>
       </c>
       <c r="Y2">
         <v>1.60944963072445</v>
       </c>
       <c r="Z2">
-        <v>1.59377037782959</v>
+        <v>1.80467101520189</v>
       </c>
       <c r="AA2">
         <v>4629</v>
@@ -1224,7 +2983,7 @@
         <v>6360.2</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +3171,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09086773821336736</v>
+        <v>0.09083876366469271</v>
       </c>
       <c r="C2">
-        <v>11953.59139140042</v>
+        <v>11954.92638300392</v>
       </c>
       <c r="D2">
-        <v>11624.59139140042</v>
+        <v>11625.92638300392</v>
       </c>
       <c r="E2">
         <v>-4736.101902040808</v>
@@ -1463,19 +3222,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09086773821336736</v>
+        <v>0.09083876366469271</v>
       </c>
       <c r="T2">
         <v>1.040156204727314</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V2">
         <v>0.265</v>
       </c>
       <c r="W2">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +3253,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09067030370710193</v>
+        <v>0.09063111594098126</v>
       </c>
       <c r="C3">
-        <v>11893.77791388703</v>
+        <v>11897.81206033641</v>
       </c>
       <c r="D3">
-        <v>11675.74093290744</v>
+        <v>11679.77507935682</v>
       </c>
       <c r="E3">
         <v>-4625.1388830204</v>
@@ -1527,37 +3286,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M3">
-        <v>5.736788083355098</v>
+        <v>5.581439856726526</v>
       </c>
       <c r="N3">
-        <v>810.9298785833116</v>
+        <v>811.0852268099402</v>
       </c>
       <c r="O3">
-        <v>214.8964178245776</v>
+        <v>214.9375851046342</v>
       </c>
       <c r="P3">
-        <v>596.033460758734</v>
+        <v>596.147641705306</v>
       </c>
       <c r="Q3">
-        <v>896.033460758734</v>
+        <v>896.147641705306</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.0912023320273757</v>
+        <v>0.09117314236462754</v>
       </c>
       <c r="T3">
         <v>1.04787857655029</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V3">
         <v>0.265</v>
       </c>
       <c r="W3">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +3324,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>142.3560805803808</v>
+        <v>146.3182776541886</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +3335,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.0904728692008365</v>
+        <v>0.09042346821726982</v>
       </c>
       <c r="C4">
-        <v>11834.4165534932</v>
+        <v>11841.19888917815</v>
       </c>
       <c r="D4">
-        <v>11727.34259153402</v>
+        <v>11734.12492721897</v>
       </c>
       <c r="E4">
         <v>-4514.175863999993</v>
@@ -1609,37 +3368,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M4">
-        <v>11.4735761667102</v>
+        <v>11.16287971345305</v>
       </c>
       <c r="N4">
-        <v>805.1930904999565</v>
+        <v>805.5037869532136</v>
       </c>
       <c r="O4">
-        <v>213.3761689824885</v>
+        <v>213.4585035426016</v>
       </c>
       <c r="P4">
-        <v>591.816921517468</v>
+        <v>592.045283410612</v>
       </c>
       <c r="Q4">
-        <v>891.816921517468</v>
+        <v>892.045283410612</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09154375428656786</v>
+        <v>0.09151434511966308</v>
       </c>
       <c r="T4">
         <v>1.055758547798224</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V4">
         <v>0.265</v>
       </c>
       <c r="W4">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +3406,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>71.17804029019041</v>
+        <v>73.15913882709432</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +3417,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.0902754346945711</v>
+        <v>0.09021582049355839</v>
       </c>
       <c r="C5">
-        <v>11775.51333130818</v>
+        <v>11785.09389830643</v>
       </c>
       <c r="D5">
-        <v>11779.4023883694</v>
+        <v>11788.98295536765</v>
       </c>
       <c r="E5">
         <v>-4403.212844979585</v>
@@ -1691,37 +3450,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M5">
-        <v>17.21036425006529</v>
+        <v>16.74431957017958</v>
       </c>
       <c r="N5">
-        <v>799.4563024166015</v>
+        <v>799.9223470964872</v>
       </c>
       <c r="O5">
-        <v>211.8559201403994</v>
+        <v>211.9794219805691</v>
       </c>
       <c r="P5">
-        <v>587.600382276202</v>
+        <v>587.9429251159181</v>
       </c>
       <c r="Q5">
-        <v>887.600382276202</v>
+        <v>887.9429251159181</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.0918922161799702</v>
+        <v>0.09186258298304989</v>
       </c>
       <c r="T5">
         <v>1.063800992680136</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V5">
         <v>0.265</v>
       </c>
       <c r="W5">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +3488,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.45202686012694</v>
+        <v>48.77275921806289</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +3499,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09007800018830565</v>
+        <v>0.09000817276984695</v>
       </c>
       <c r="C6">
-        <v>11717.07437581275</v>
+        <v>11729.50424855644</v>
       </c>
       <c r="D6">
-        <v>11831.92645189438</v>
+        <v>11844.35632463807</v>
       </c>
       <c r="E6">
         <v>-4292.249825959176</v>
@@ -1773,37 +3532,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M6">
-        <v>22.94715233342039</v>
+        <v>22.3257594269061</v>
       </c>
       <c r="N6">
-        <v>793.7195143332464</v>
+        <v>794.3409072397607</v>
       </c>
       <c r="O6">
-        <v>210.3356712983103</v>
+        <v>210.5003404185366</v>
       </c>
       <c r="P6">
-        <v>583.383843034936</v>
+        <v>583.8405668212241</v>
       </c>
       <c r="Q6">
-        <v>883.383843034936</v>
+        <v>883.8405668212241</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09224793769615172</v>
+        <v>0.0922180758019239</v>
       </c>
       <c r="T6">
         <v>1.072010988497088</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V6">
         <v>0.265</v>
       </c>
       <c r="W6">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +3570,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.5890201450952</v>
+        <v>36.57956941354716</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +3581,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08988056568204024</v>
+        <v>0.08980052504613553</v>
       </c>
       <c r="C7">
-        <v>11659.10592528424</v>
+        <v>11674.4372359373</v>
       </c>
       <c r="D7">
-        <v>11884.92102038628</v>
+        <v>11900.25233103934</v>
       </c>
       <c r="E7">
         <v>-4181.286806938768</v>
@@ -1855,37 +3614,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M7">
-        <v>28.68394041677549</v>
+        <v>27.90719928363263</v>
       </c>
       <c r="N7">
-        <v>787.9827262498912</v>
+        <v>788.7594673830341</v>
       </c>
       <c r="O7">
-        <v>208.8154224562212</v>
+        <v>209.0212588565041</v>
       </c>
       <c r="P7">
-        <v>579.16730379367</v>
+        <v>579.7382085265301</v>
       </c>
       <c r="Q7">
-        <v>879.16730379367</v>
+        <v>879.7382085265301</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09261114808635815</v>
+        <v>0.09258105268014266</v>
       </c>
       <c r="T7">
         <v>1.080393826331239</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V7">
         <v>0.265</v>
       </c>
       <c r="W7">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +3652,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.47121611607616</v>
+        <v>29.26365553083773</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +3663,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08968313117577482</v>
+        <v>0.08959287732242409</v>
       </c>
       <c r="C8">
-        <v>11601.61433026648</v>
+        <v>11619.9002948368</v>
       </c>
       <c r="D8">
-        <v>11938.39244438892</v>
+        <v>11956.67840895925</v>
       </c>
       <c r="E8">
         <v>-4070.32378791836</v>
@@ -1937,37 +3696,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M8">
-        <v>34.42072850013059</v>
+        <v>33.48863914035915</v>
       </c>
       <c r="N8">
-        <v>782.2459381665361</v>
+        <v>783.1780275263076</v>
       </c>
       <c r="O8">
-        <v>207.2951736141321</v>
+        <v>207.5421772944715</v>
       </c>
       <c r="P8">
-        <v>574.9507645524041</v>
+        <v>575.635850231836</v>
       </c>
       <c r="Q8">
-        <v>874.9507645524041</v>
+        <v>875.635850231836</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09298208635720726</v>
+        <v>0.09295175247066392</v>
       </c>
       <c r="T8">
         <v>1.088955022417181</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V8">
         <v>0.265</v>
       </c>
       <c r="W8">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +3734,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.72601343006347</v>
+        <v>24.38637960903144</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +3745,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.0894856966695094</v>
+        <v>0.08938522959871266</v>
       </c>
       <c r="C9">
-        <v>11544.60605610667</v>
+        <v>11565.90100131764</v>
       </c>
       <c r="D9">
-        <v>11992.34718924952</v>
+        <v>12013.6421344605</v>
       </c>
       <c r="E9">
         <v>-3959.360768897952</v>
@@ -2019,37 +3778,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M9">
-        <v>40.15751658348568</v>
+        <v>39.07007899708568</v>
       </c>
       <c r="N9">
-        <v>776.5091500831811</v>
+        <v>777.596587669581</v>
       </c>
       <c r="O9">
-        <v>205.774924772043</v>
+        <v>206.063095732439</v>
       </c>
       <c r="P9">
-        <v>570.7342253111381</v>
+        <v>571.533491937142</v>
       </c>
       <c r="Q9">
-        <v>870.7342253111381</v>
+        <v>871.533491937142</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.0933610017951714</v>
+        <v>0.09333042429969103</v>
       </c>
       <c r="T9">
         <v>1.097700330246906</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V9">
         <v>0.265</v>
       </c>
       <c r="W9">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +3816,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.33658294005441</v>
+        <v>20.90261109345552</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +3827,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08928826216324398</v>
+        <v>0.08917758187500122</v>
       </c>
       <c r="C10">
-        <v>11488.08768556141</v>
+        <v>11512.44707650846</v>
       </c>
       <c r="D10">
-        <v>12046.79183772467</v>
+        <v>12071.15122867172</v>
       </c>
       <c r="E10">
         <v>-3848.397749877544</v>
@@ -2101,37 +3860,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M10">
-        <v>45.89430466684078</v>
+        <v>44.65151885381221</v>
       </c>
       <c r="N10">
-        <v>770.772361999826</v>
+        <v>772.0151478128546</v>
       </c>
       <c r="O10">
-        <v>204.2546759299539</v>
+        <v>204.5840141704065</v>
       </c>
       <c r="P10">
-        <v>566.5176860698721</v>
+        <v>567.4311336424481</v>
       </c>
       <c r="Q10">
-        <v>866.5176860698721</v>
+        <v>867.4311336424481</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09374815452526519</v>
+        <v>0.09371732812500132</v>
       </c>
       <c r="T10">
         <v>1.106635753464234</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V10">
         <v>0.265</v>
       </c>
       <c r="W10">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +3898,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.7945100725476</v>
+        <v>18.28978470677358</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +3909,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08909082765697855</v>
+        <v>0.08896993415128977</v>
       </c>
       <c r="C11">
-        <v>11432.06592147402</v>
+        <v>11459.54639009264</v>
       </c>
       <c r="D11">
-        <v>12101.73309265769</v>
+        <v>12129.21356127631</v>
       </c>
       <c r="E11">
         <v>-3737.434730857136</v>
@@ -2183,37 +3942,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M11">
-        <v>51.63109275019588</v>
+        <v>50.23295871053873</v>
       </c>
       <c r="N11">
-        <v>765.0355739164709</v>
+        <v>766.433707956128</v>
       </c>
       <c r="O11">
-        <v>202.7344270878648</v>
+        <v>203.1049326083739</v>
       </c>
       <c r="P11">
-        <v>562.3011468286061</v>
+        <v>563.3287753477541</v>
       </c>
       <c r="Q11">
-        <v>862.3011468286061</v>
+        <v>863.3287753477541</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09414381610656983</v>
+        <v>0.09411273533108766</v>
       </c>
       <c r="T11">
         <v>1.115767559609415</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V11">
         <v>0.265</v>
       </c>
       <c r="W11">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +3980,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.81734228670898</v>
+        <v>16.25758640602096</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +3991,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08889339315071314</v>
+        <v>0.08876228642757833</v>
       </c>
       <c r="C12">
-        <v>11376.54758952544</v>
+        <v>11407.20696389833</v>
       </c>
       <c r="D12">
-        <v>12157.17777972952</v>
+        <v>12187.83715410242</v>
       </c>
       <c r="E12">
         <v>-3626.471711836728</v>
@@ -2265,37 +4024,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M12">
-        <v>57.36788083355098</v>
+        <v>55.81439856726526</v>
       </c>
       <c r="N12">
-        <v>759.2987858331157</v>
+        <v>760.8522680994015</v>
       </c>
       <c r="O12">
-        <v>201.2141782457757</v>
+        <v>201.6258510463414</v>
       </c>
       <c r="P12">
-        <v>558.0846075873401</v>
+        <v>559.2264170530601</v>
       </c>
       <c r="Q12">
-        <v>858.0846075873401</v>
+        <v>859.2264170530601</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09454827016745904</v>
+        <v>0.09451692936397593</v>
       </c>
       <c r="T12">
         <v>1.125102294780045</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V12">
         <v>0.265</v>
       </c>
       <c r="W12">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +4062,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.23560805803808</v>
+        <v>14.63182776541887</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +4073,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08869595864444771</v>
+        <v>0.08855463870386691</v>
       </c>
       <c r="C13">
-        <v>11321.53964106114</v>
+        <v>11355.43697559311</v>
       </c>
       <c r="D13">
-        <v>12213.13285028563</v>
+        <v>12247.0301848176</v>
       </c>
       <c r="E13">
         <v>-3515.50869281632</v>
@@ -2347,37 +4106,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M13">
-        <v>63.10466891690607</v>
+        <v>61.39583842399178</v>
       </c>
       <c r="N13">
-        <v>753.5619977497606</v>
+        <v>755.270828242675</v>
       </c>
       <c r="O13">
-        <v>199.6939294036866</v>
+        <v>200.1467694843089</v>
       </c>
       <c r="P13">
-        <v>553.8680683460741</v>
+        <v>555.1240587583661</v>
       </c>
       <c r="Q13">
-        <v>853.8680683460741</v>
+        <v>855.1240587583661</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09496181308364911</v>
+        <v>0.09493020640883923</v>
       </c>
       <c r="T13">
         <v>1.134646799280352</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V13">
         <v>0.265</v>
       </c>
       <c r="W13">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +4144,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.94146187094371</v>
+        <v>13.30166160492624</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +4155,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08849852413818227</v>
+        <v>0.08834699098015547</v>
       </c>
       <c r="C14">
-        <v>11267.0491559964</v>
+        <v>11304.24476248678</v>
       </c>
       <c r="D14">
-        <v>12269.6053842413</v>
+        <v>12306.80099073168</v>
       </c>
       <c r="E14">
         <v>-3404.545673795911</v>
@@ -2429,37 +4188,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M14">
-        <v>68.84145700026117</v>
+        <v>66.97727828071831</v>
       </c>
       <c r="N14">
-        <v>747.8252096664056</v>
+        <v>749.6893883859484</v>
       </c>
       <c r="O14">
-        <v>198.1736805615975</v>
+        <v>198.6676879222763</v>
       </c>
       <c r="P14">
-        <v>549.6515291048081</v>
+        <v>551.021700463672</v>
       </c>
       <c r="Q14">
-        <v>849.6515291048081</v>
+        <v>851.021700463672</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09538475470247985</v>
+        <v>0.09535287611381303</v>
       </c>
       <c r="T14">
         <v>1.144408224337484</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V14">
         <v>0.265</v>
       </c>
       <c r="W14">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +4226,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.86300671503174</v>
+        <v>12.19318980451572</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +4237,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08830108963191687</v>
+        <v>0.08813934325644404</v>
       </c>
       <c r="C15">
-        <v>11213.08334580261</v>
+        <v>11253.63882544605</v>
       </c>
       <c r="D15">
-        <v>12326.60259306791</v>
+        <v>12367.15807271136</v>
       </c>
       <c r="E15">
         <v>-3293.582654775503</v>
@@ -2511,37 +4270,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M15">
-        <v>74.57824508361627</v>
+        <v>72.55871813744483</v>
       </c>
       <c r="N15">
-        <v>742.0884215830505</v>
+        <v>744.1079485292219</v>
       </c>
       <c r="O15">
-        <v>196.6534317195084</v>
+        <v>197.1886063602438</v>
       </c>
       <c r="P15">
-        <v>545.4349898635421</v>
+        <v>546.9193421689781</v>
       </c>
       <c r="Q15">
-        <v>845.4349898635421</v>
+        <v>846.9193421689781</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09581741911714581</v>
+        <v>0.09578526236372878</v>
       </c>
       <c r="T15">
         <v>1.154394049970642</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V15">
         <v>0.265</v>
       </c>
       <c r="W15">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +4308,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.95046773695237</v>
+        <v>11.25525212724528</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +4319,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08810365512565142</v>
+        <v>0.0879316955327326</v>
       </c>
       <c r="C16">
-        <v>11159.64955657721</v>
+        <v>11203.6278329251</v>
       </c>
       <c r="D16">
-        <v>12384.13182286293</v>
+        <v>12428.11009921081</v>
       </c>
       <c r="E16">
         <v>-3182.619635755095</v>
@@ -2593,37 +4352,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M16">
-        <v>80.31503316697136</v>
+        <v>78.14015799417136</v>
       </c>
       <c r="N16">
-        <v>736.3516334996954</v>
+        <v>738.5265086724954</v>
       </c>
       <c r="O16">
-        <v>195.1331828774193</v>
+        <v>195.7095247982113</v>
       </c>
       <c r="P16">
-        <v>541.2184506222761</v>
+        <v>542.8169838742841</v>
       </c>
       <c r="Q16">
-        <v>841.2184506222761</v>
+        <v>842.8169838742841</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09626014549494352</v>
+        <v>0.0962277041078286</v>
       </c>
       <c r="T16">
         <v>1.164612104106896</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V16">
         <v>0.265</v>
       </c>
       <c r="W16">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +4390,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.1682914700272</v>
+        <v>10.45130554672776</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +4401,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08790622061938601</v>
+        <v>0.08772404780902116</v>
       </c>
       <c r="C17">
-        <v>11106.75527219995</v>
+        <v>11154.22062511577</v>
       </c>
       <c r="D17">
-        <v>12442.20055750607</v>
+        <v>12489.66591042189</v>
       </c>
       <c r="E17">
         <v>-3071.656616734687</v>
@@ -2675,37 +4434,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M17">
-        <v>86.05182125032646</v>
+        <v>83.72159785089788</v>
       </c>
       <c r="N17">
-        <v>730.6148454163402</v>
+        <v>732.9450688157689</v>
       </c>
       <c r="O17">
-        <v>193.6129340353302</v>
+        <v>194.2304432361788</v>
       </c>
       <c r="P17">
-        <v>537.0019113810101</v>
+        <v>538.7146255795901</v>
       </c>
       <c r="Q17">
-        <v>837.0019113810101</v>
+        <v>838.7146255795901</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09671328896398354</v>
+        <v>0.09668055624590724</v>
       </c>
       <c r="T17">
         <v>1.175070583046357</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V17">
         <v>0.265</v>
       </c>
       <c r="W17">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +4472,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.490405372025389</v>
+        <v>9.754551843612578</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +4483,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08770878611312059</v>
+        <v>0.08751640008530971</v>
       </c>
       <c r="C18">
-        <v>11054.40811757838</v>
+        <v>11105.42621822182</v>
       </c>
       <c r="D18">
-        <v>12500.81642190491</v>
+        <v>12551.83452254835</v>
       </c>
       <c r="E18">
         <v>-2960.693597714279</v>
@@ -2757,37 +4516,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M18">
-        <v>91.78860933368156</v>
+        <v>89.30303770762441</v>
       </c>
       <c r="N18">
-        <v>724.8780573329852</v>
+        <v>727.3636289590423</v>
       </c>
       <c r="O18">
-        <v>192.0926851932411</v>
+        <v>192.7513616741462</v>
       </c>
       <c r="P18">
-        <v>532.7853721397441</v>
+        <v>534.6122672848961</v>
       </c>
       <c r="Q18">
-        <v>832.7853721397441</v>
+        <v>834.6122672848961</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.0971772215632388</v>
+        <v>0.09714419057774967</v>
       </c>
       <c r="T18">
         <v>1.185778073389138</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.05029999999999999</v>
       </c>
       <c r="V18">
         <v>0.265</v>
       </c>
       <c r="W18">
-        <v>0.0379995</v>
+        <v>0.03697049999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +4554,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.897255036273801</v>
+        <v>9.144892353386791</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +4565,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08764879660685516</v>
+        <v>0.0874961773615983</v>
       </c>
       <c r="C19">
-        <v>10961.36479675407</v>
+        <v>11000.55086233224</v>
       </c>
       <c r="D19">
-        <v>12518.73612010101</v>
+        <v>12557.92218567918</v>
       </c>
       <c r="E19">
         <v>-2849.730578693871</v>
@@ -2839,37 +4598,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M19">
-        <v>99.60040587271828</v>
+        <v>97.71403454937135</v>
       </c>
       <c r="N19">
-        <v>717.0662607939485</v>
+        <v>718.9526321172954</v>
       </c>
       <c r="O19">
-        <v>190.0225591103963</v>
+        <v>190.5224475110833</v>
       </c>
       <c r="P19">
-        <v>527.0437016835522</v>
+        <v>528.4301846062122</v>
       </c>
       <c r="Q19">
-        <v>827.0437016835522</v>
+        <v>828.4301846062122</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09765233326127129</v>
+        <v>0.09761899682120277</v>
       </c>
       <c r="T19">
         <v>1.196743575547408</v>
       </c>
       <c r="U19">
-        <v>0.05279999999999999</v>
+        <v>0.05179999999999999</v>
       </c>
       <c r="V19">
         <v>0.265</v>
       </c>
       <c r="W19">
-        <v>0.038808</v>
+        <v>0.038073</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +4636,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.199431111860171</v>
+        <v>8.357721287764807</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +4647,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08745944710058974</v>
+        <v>0.08729955463788686</v>
       </c>
       <c r="C20">
-        <v>10907.30163282979</v>
+        <v>10949.08662313851</v>
       </c>
       <c r="D20">
-        <v>12575.63597519713</v>
+        <v>12617.42096550585</v>
       </c>
       <c r="E20">
         <v>-2738.767559673463</v>
@@ -2921,37 +4680,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M20">
-        <v>105.4592532769958</v>
+        <v>103.4619189346285</v>
       </c>
       <c r="N20">
-        <v>711.2074133896709</v>
+        <v>713.2047477320383</v>
       </c>
       <c r="O20">
-        <v>188.4699645482628</v>
+        <v>188.9992581489902</v>
       </c>
       <c r="P20">
-        <v>522.7374488414082</v>
+        <v>524.2054895830481</v>
       </c>
       <c r="Q20">
-        <v>822.7374488414082</v>
+        <v>824.2054895830481</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09813903304949968</v>
+        <v>0.09810538370474008</v>
       </c>
       <c r="T20">
         <v>1.207976528977831</v>
       </c>
       <c r="U20">
-        <v>0.05279999999999999</v>
+        <v>0.05179999999999999</v>
       </c>
       <c r="V20">
         <v>0.265</v>
       </c>
       <c r="W20">
-        <v>0.038808</v>
+        <v>0.038073</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +4718,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.743907161201273</v>
+        <v>7.89340343844454</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +4729,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0872700975943243</v>
+        <v>0.08710293191417542</v>
       </c>
       <c r="C21">
-        <v>10853.75807026138</v>
+        <v>10898.18887216266</v>
       </c>
       <c r="D21">
-        <v>12633.05543164913</v>
+        <v>12677.48623355042</v>
       </c>
       <c r="E21">
         <v>-2627.804540653055</v>
@@ -3003,37 +4762,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M21">
-        <v>111.3181006812734</v>
+        <v>109.2098033198856</v>
       </c>
       <c r="N21">
-        <v>705.3485659853934</v>
+        <v>707.4568633467811</v>
       </c>
       <c r="O21">
-        <v>186.9173699861293</v>
+        <v>187.476068786897</v>
       </c>
       <c r="P21">
-        <v>518.4311959992641</v>
+        <v>519.9807945598841</v>
       </c>
       <c r="Q21">
-        <v>818.4311959992641</v>
+        <v>819.9807945598841</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09863775011644976</v>
+        <v>0.0986037801409573</v>
       </c>
       <c r="T21">
         <v>1.219486839283079</v>
       </c>
       <c r="U21">
-        <v>0.05279999999999999</v>
+        <v>0.05179999999999999</v>
       </c>
       <c r="V21">
         <v>0.265</v>
       </c>
       <c r="W21">
-        <v>0.038808</v>
+        <v>0.038073</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +4800,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.336333100085417</v>
+        <v>7.477961152210618</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +4811,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08708074808805889</v>
+        <v>0.08690630919046401</v>
       </c>
       <c r="C22">
-        <v>10800.74125908351</v>
+        <v>10847.86573840914</v>
       </c>
       <c r="D22">
-        <v>12691.00163949167</v>
+        <v>12738.1261188173</v>
       </c>
       <c r="E22">
         <v>-2516.841521632647</v>
@@ -3085,37 +4844,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M22">
-        <v>117.1769480855509</v>
+        <v>114.9576877051428</v>
       </c>
       <c r="N22">
-        <v>699.4897185811158</v>
+        <v>701.7089789615239</v>
       </c>
       <c r="O22">
-        <v>185.3647754239957</v>
+        <v>185.9528794248039</v>
       </c>
       <c r="P22">
-        <v>514.12494315712</v>
+        <v>515.7560995367201</v>
       </c>
       <c r="Q22">
-        <v>814.12494315712</v>
+        <v>815.7560995367201</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09914893511007362</v>
+        <v>0.09911463648808</v>
       </c>
       <c r="T22">
         <v>1.231284907345958</v>
       </c>
       <c r="U22">
-        <v>0.05279999999999999</v>
+        <v>0.05179999999999999</v>
       </c>
       <c r="V22">
         <v>0.265</v>
       </c>
       <c r="W22">
-        <v>0.038808</v>
+        <v>0.038073</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +4882,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.969516445081144</v>
+        <v>7.104063094600086</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +4893,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08723096858179348</v>
+        <v>0.08670968646675255</v>
       </c>
       <c r="C23">
-        <v>10643.76317940848</v>
+        <v>10798.1255071629</v>
       </c>
       <c r="D23">
-        <v>12644.98657883705</v>
+        <v>12799.34890659147</v>
       </c>
       <c r="E23">
         <v>-2405.878502612239</v>
@@ -3167,45 +4926,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M23">
-        <v>128.1622869685713</v>
+        <v>120.7055720903999</v>
       </c>
       <c r="N23">
-        <v>688.5043796980954</v>
+        <v>695.9610945762669</v>
       </c>
       <c r="O23">
-        <v>182.4536606199953</v>
+        <v>184.4296900627107</v>
       </c>
       <c r="P23">
-        <v>506.0507190781001</v>
+        <v>511.5314045135561</v>
       </c>
       <c r="Q23">
-        <v>806.0507190781001</v>
+        <v>811.5314045135561</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.0996730614959411</v>
+        <v>0.09963842590728171</v>
       </c>
       <c r="T23">
         <v>1.243381660676252</v>
       </c>
       <c r="U23">
-        <v>0.05499999999999999</v>
+        <v>0.05179999999999999</v>
       </c>
       <c r="V23">
         <v>0.265</v>
       </c>
       <c r="W23">
-        <v>0.040425</v>
+        <v>0.038073</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.372129321217046</v>
+        <v>6.765774375809606</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +4975,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08705778907552804</v>
+        <v>0.08678795374304112</v>
       </c>
       <c r="C24">
-        <v>10585.87747212786</v>
+        <v>10662.7218882661</v>
       </c>
       <c r="D24">
-        <v>12698.06389057684</v>
+        <v>12774.90830671508</v>
       </c>
       <c r="E24">
         <v>-2294.915483591831</v>
@@ -3249,37 +5008,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M24">
-        <v>134.2652530146938</v>
+        <v>130.6034733870203</v>
       </c>
       <c r="N24">
-        <v>682.4014136519729</v>
+        <v>686.0631932796464</v>
       </c>
       <c r="O24">
-        <v>180.8363746177728</v>
+        <v>181.8067462191063</v>
       </c>
       <c r="P24">
-        <v>501.5650390342001</v>
+        <v>504.2564470605401</v>
       </c>
       <c r="Q24">
-        <v>801.5650390342</v>
+        <v>804.25644706054</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1002106270199077</v>
+        <v>0.1001756458244117</v>
       </c>
       <c r="T24">
         <v>1.255788587168861</v>
       </c>
       <c r="U24">
-        <v>0.05499999999999999</v>
+        <v>0.05349999999999999</v>
       </c>
       <c r="V24">
         <v>0.265</v>
       </c>
       <c r="W24">
-        <v>0.040425</v>
+        <v>0.0393225</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +5046,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.082487079343544</v>
+        <v>6.253024100259719</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +5057,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08688460956926262</v>
+        <v>0.08660382601932969</v>
       </c>
       <c r="C25">
-        <v>10528.43922693765</v>
+        <v>10609.40578662112</v>
       </c>
       <c r="D25">
-        <v>12751.58866440704</v>
+        <v>12832.5552240905</v>
       </c>
       <c r="E25">
         <v>-2183.952464571422</v>
@@ -3331,37 +5090,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M25">
-        <v>140.3682190608162</v>
+        <v>136.5399949046121</v>
       </c>
       <c r="N25">
-        <v>676.2984476058505</v>
+        <v>680.1266717620546</v>
       </c>
       <c r="O25">
-        <v>179.2190886155504</v>
+        <v>180.2335680169445</v>
       </c>
       <c r="P25">
-        <v>497.0793589903001</v>
+        <v>499.8931037451101</v>
       </c>
       <c r="Q25">
-        <v>797.0793589903001</v>
+        <v>799.8931037451101</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1007621552847567</v>
+        <v>0.100726819505623</v>
       </c>
       <c r="T25">
         <v>1.268517771492447</v>
       </c>
       <c r="U25">
-        <v>0.05499999999999999</v>
+        <v>0.05349999999999999</v>
       </c>
       <c r="V25">
         <v>0.265</v>
       </c>
       <c r="W25">
-        <v>0.040425</v>
+        <v>0.0393225</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +5128,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.818031119372086</v>
+        <v>5.981153487204947</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +5139,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.0869760300629972</v>
+        <v>0.08641969829561826</v>
       </c>
       <c r="C26">
-        <v>10389.164674974</v>
+        <v>10556.61230804429</v>
       </c>
       <c r="D26">
-        <v>12723.2771314638</v>
+        <v>12890.72476453408</v>
       </c>
       <c r="E26">
         <v>-2072.989445551014</v>
@@ -3413,45 +5172,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M26">
-        <v>150.4658537916733</v>
+        <v>142.476516422204</v>
       </c>
       <c r="N26">
-        <v>666.2008128749934</v>
+        <v>674.1901502444628</v>
       </c>
       <c r="O26">
-        <v>176.5432154118733</v>
+        <v>178.6603898147826</v>
       </c>
       <c r="P26">
-        <v>489.6575974631202</v>
+        <v>495.5297604296801</v>
       </c>
       <c r="Q26">
-        <v>789.6575974631202</v>
+        <v>795.5297604296801</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1013281974513121</v>
+        <v>0.1012924977573924</v>
       </c>
       <c r="T26">
         <v>1.281581934350865</v>
       </c>
       <c r="U26">
-        <v>0.05649999999999999</v>
+        <v>0.05349999999999999</v>
       </c>
       <c r="V26">
         <v>0.265</v>
       </c>
       <c r="W26">
-        <v>0.04152749999999999</v>
+        <v>0.0393225</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.427588028027794</v>
+        <v>5.731938758571409</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +5221,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08681387555673177</v>
+        <v>0.08638257057190681</v>
       </c>
       <c r="C27">
-        <v>10328.50503970666</v>
+        <v>10457.44260967246</v>
       </c>
       <c r="D27">
-        <v>12773.58051521687</v>
+        <v>12902.51808518266</v>
       </c>
       <c r="E27">
         <v>-1962.026426530606</v>
@@ -3495,37 +5254,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M27">
-        <v>156.7352643663264</v>
+        <v>150.6322983202039</v>
       </c>
       <c r="N27">
-        <v>659.9314023003403</v>
+        <v>666.0343683464628</v>
       </c>
       <c r="O27">
-        <v>174.8818216095902</v>
+        <v>176.4991076118126</v>
       </c>
       <c r="P27">
-        <v>485.0495806907501</v>
+        <v>489.5352607346501</v>
       </c>
       <c r="Q27">
-        <v>785.0495806907502</v>
+        <v>789.5352607346501</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1019093340756424</v>
+        <v>0.1018732607625424</v>
       </c>
       <c r="T27">
         <v>1.294994474885506</v>
       </c>
       <c r="U27">
-        <v>0.05649999999999999</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="V27">
         <v>0.265</v>
       </c>
       <c r="W27">
-        <v>0.04152749999999999</v>
+        <v>0.03991049999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +5292,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.210484506906683</v>
+        <v>5.421590693190195</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +5303,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08665172105046634</v>
+        <v>0.08620432284819537</v>
       </c>
       <c r="C28">
-        <v>10268.24474724037</v>
+        <v>10403.40034359896</v>
       </c>
       <c r="D28">
-        <v>12824.28324177098</v>
+        <v>12959.43883812957</v>
       </c>
       <c r="E28">
         <v>-1851.063407510198</v>
@@ -3577,37 +5336,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M28">
-        <v>163.0046749409794</v>
+        <v>156.6575902530121</v>
       </c>
       <c r="N28">
-        <v>653.6619917256874</v>
+        <v>660.0090764136546</v>
       </c>
       <c r="O28">
-        <v>173.2204278073071</v>
+        <v>174.9024052496185</v>
       </c>
       <c r="P28">
-        <v>480.4415639183802</v>
+        <v>485.1066711640361</v>
       </c>
       <c r="Q28">
-        <v>780.4415639183802</v>
+        <v>785.1066711640361</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1025061770952248</v>
+        <v>0.1024697200651289</v>
       </c>
       <c r="T28">
         <v>1.308769516515679</v>
       </c>
       <c r="U28">
-        <v>0.05649999999999999</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="V28">
         <v>0.265</v>
       </c>
       <c r="W28">
-        <v>0.04152749999999999</v>
+        <v>0.03991049999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +5374,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.010081256641041</v>
+        <v>5.213067974221341</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +5385,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08648956654420092</v>
+        <v>0.08602607512448393</v>
       </c>
       <c r="C29">
-        <v>10208.38857191215</v>
+        <v>10349.86252617542</v>
       </c>
       <c r="D29">
-        <v>12875.39008546316</v>
+        <v>13016.86403972644</v>
       </c>
       <c r="E29">
         <v>-1740.10038848979</v>
@@ -3659,37 +5418,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M29">
-        <v>169.2740855156325</v>
+        <v>162.6828821858203</v>
       </c>
       <c r="N29">
-        <v>647.3925811510342</v>
+        <v>653.9837844808465</v>
       </c>
       <c r="O29">
-        <v>171.5590340050241</v>
+        <v>173.3057028874243</v>
       </c>
       <c r="P29">
-        <v>475.8335471460101</v>
+        <v>480.6780815934221</v>
       </c>
       <c r="Q29">
-        <v>775.8335471460101</v>
+        <v>780.6780815934221</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1031193719783574</v>
+        <v>0.1030825207184711</v>
       </c>
       <c r="T29">
         <v>1.322921956546678</v>
       </c>
       <c r="U29">
-        <v>0.05649999999999999</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="V29">
         <v>0.265</v>
       </c>
       <c r="W29">
-        <v>0.04152749999999999</v>
+        <v>0.03991049999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +5456,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.824522691580261</v>
+        <v>5.019991382583513</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +5467,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08632741203793551</v>
+        <v>0.0858478274007725</v>
       </c>
       <c r="C30">
-        <v>10148.94136446956</v>
+        <v>10296.83589310982</v>
       </c>
       <c r="D30">
-        <v>12926.90589704098</v>
+        <v>13074.80042568124</v>
       </c>
       <c r="E30">
         <v>-1629.137369469382</v>
@@ -3741,37 +5500,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M30">
-        <v>175.5434960902856</v>
+        <v>168.7081741186284</v>
       </c>
       <c r="N30">
-        <v>641.1231705763812</v>
+        <v>647.9584925480383</v>
       </c>
       <c r="O30">
-        <v>169.897640202741</v>
+        <v>171.7090005252302</v>
       </c>
       <c r="P30">
-        <v>471.2255303736401</v>
+        <v>476.2494920228081</v>
       </c>
       <c r="Q30">
-        <v>771.2255303736401</v>
+        <v>776.2494920228081</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1037496000526882</v>
+        <v>0.103712343612184</v>
       </c>
       <c r="T30">
         <v>1.337467519911872</v>
       </c>
       <c r="U30">
-        <v>0.05649999999999999</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="V30">
         <v>0.265</v>
       </c>
       <c r="W30">
-        <v>0.04152749999999999</v>
+        <v>0.03991049999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +5538,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.652218309738109</v>
+        <v>4.840705976062674</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +5549,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08616525753167008</v>
+        <v>0.08566957967706107</v>
       </c>
       <c r="C31">
-        <v>10089.90805360547</v>
+        <v>10244.32730056533</v>
       </c>
       <c r="D31">
-        <v>12978.8356051973</v>
+        <v>13133.25485215717</v>
       </c>
       <c r="E31">
         <v>-1518.174350448974</v>
@@ -3823,37 +5582,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M31">
-        <v>181.8129066649386</v>
+        <v>174.7334660514366</v>
       </c>
       <c r="N31">
-        <v>634.8537600017281</v>
+        <v>641.9332006152301</v>
       </c>
       <c r="O31">
-        <v>168.236246400458</v>
+        <v>170.112298163036</v>
       </c>
       <c r="P31">
-        <v>466.6175136012702</v>
+        <v>471.8209024521941</v>
       </c>
       <c r="Q31">
-        <v>766.6175136012702</v>
+        <v>771.8209024521941</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1043975810305212</v>
+        <v>0.1043599079958607</v>
       </c>
       <c r="T31">
         <v>1.352422817456367</v>
       </c>
       <c r="U31">
-        <v>0.05649999999999999</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="V31">
         <v>0.265</v>
       </c>
       <c r="W31">
-        <v>0.04152749999999999</v>
+        <v>0.03991049999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +5620,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.491796988712657</v>
+        <v>4.673785080336375</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +5631,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08600310302540465</v>
+        <v>0.08549133195334963</v>
       </c>
       <c r="C32">
-        <v>10031.29364752996</v>
+        <v>10192.34372786511</v>
       </c>
       <c r="D32">
-        <v>13031.18421814221</v>
+        <v>13192.23429847735</v>
       </c>
       <c r="E32">
         <v>-1407.211331428566</v>
@@ -3905,37 +5664,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M32">
-        <v>188.0823172395917</v>
+        <v>180.7587579842447</v>
       </c>
       <c r="N32">
-        <v>628.584349427075</v>
+        <v>635.907908682422</v>
       </c>
       <c r="O32">
-        <v>166.5748525981749</v>
+        <v>168.5155958008418</v>
       </c>
       <c r="P32">
-        <v>462.0094968289002</v>
+        <v>467.3923128815802</v>
       </c>
       <c r="Q32">
-        <v>762.0094968289002</v>
+        <v>767.3923128815802</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1050640757505781</v>
+        <v>0.1050259742190709</v>
       </c>
       <c r="T32">
         <v>1.367805409216418</v>
       </c>
       <c r="U32">
-        <v>0.05649999999999999</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="V32">
         <v>0.265</v>
       </c>
       <c r="W32">
-        <v>0.04152749999999999</v>
+        <v>0.03991049999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +5702,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.342070422422236</v>
+        <v>4.517992244325162</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +5713,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08615993851913922</v>
+        <v>0.08531308422963818</v>
       </c>
       <c r="C33">
-        <v>9869.692488666271</v>
+        <v>10140.89228027015</v>
       </c>
       <c r="D33">
-        <v>12980.54607829892</v>
+        <v>13251.7458699028</v>
       </c>
       <c r="E33">
         <v>-1296.248312408158</v>
@@ -3987,45 +5746,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M33">
-        <v>199.1675228397305</v>
+        <v>186.7840499170529</v>
       </c>
       <c r="N33">
-        <v>617.4991438269362</v>
+        <v>629.8826167496138</v>
       </c>
       <c r="O33">
-        <v>163.6372731141381</v>
+        <v>166.9188934386477</v>
       </c>
       <c r="P33">
-        <v>453.8618707127981</v>
+        <v>462.9637233109661</v>
       </c>
       <c r="Q33">
-        <v>753.8618707127981</v>
+        <v>762.9637233109661</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1057498891581728</v>
+        <v>0.1057113467096206</v>
       </c>
       <c r="T33">
         <v>1.383633873201399</v>
       </c>
       <c r="U33">
-        <v>0.05789999999999999</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="V33">
         <v>0.265</v>
       </c>
       <c r="W33">
-        <v>0.0425565</v>
+        <v>0.03991049999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.100400783333717</v>
+        <v>4.37225055902435</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +5795,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08600807401287382</v>
+        <v>0.08537003650592676</v>
       </c>
       <c r="C34">
-        <v>9807.756543675945</v>
+        <v>10010.85631720594</v>
       </c>
       <c r="D34">
-        <v>13029.573152329</v>
+        <v>13232.672925859</v>
       </c>
       <c r="E34">
         <v>-1185.28529338775</v>
@@ -4069,37 +5828,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M34">
-        <v>205.5922816410121</v>
+        <v>196.3601584585141</v>
       </c>
       <c r="N34">
-        <v>611.0743850256547</v>
+        <v>620.3065082081526</v>
       </c>
       <c r="O34">
-        <v>161.9347120317985</v>
+        <v>164.3812246751605</v>
       </c>
       <c r="P34">
-        <v>449.1396729938562</v>
+        <v>455.9252835329922</v>
       </c>
       <c r="Q34">
-        <v>749.1396729938562</v>
+        <v>755.9252835329921</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1064558735483438</v>
+        <v>0.1064168772145982</v>
       </c>
       <c r="T34">
         <v>1.399927880244762</v>
       </c>
       <c r="U34">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V34">
         <v>0.265</v>
       </c>
       <c r="W34">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +5866,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.972263258854539</v>
+        <v>4.159024280066506</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +5877,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08585620950660838</v>
+        <v>0.08519913878221531</v>
       </c>
       <c r="C35">
-        <v>9746.192349906374</v>
+        <v>9957.291346760849</v>
       </c>
       <c r="D35">
-        <v>13078.97197757984</v>
+        <v>13290.07097443432</v>
       </c>
       <c r="E35">
         <v>-1074.322274367341</v>
@@ -4151,37 +5910,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M35">
-        <v>212.0170404422937</v>
+        <v>202.4964134103427</v>
       </c>
       <c r="N35">
-        <v>604.649626224373</v>
+        <v>614.170253256324</v>
       </c>
       <c r="O35">
-        <v>160.2321509494589</v>
+        <v>162.7551171129259</v>
       </c>
       <c r="P35">
-        <v>444.4174752749142</v>
+        <v>451.4151361433982</v>
       </c>
       <c r="Q35">
-        <v>744.4174752749142</v>
+        <v>751.4151361433982</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1071829320994155</v>
+        <v>0.1071434683316647</v>
       </c>
       <c r="T35">
         <v>1.416708275558076</v>
       </c>
       <c r="U35">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V35">
         <v>0.265</v>
       </c>
       <c r="W35">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +5948,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.851891644949855</v>
+        <v>4.032993241276611</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +5959,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08570434500034295</v>
+        <v>0.08502824105850387</v>
       </c>
       <c r="C36">
-        <v>9685.004151693513</v>
+        <v>9904.226485195602</v>
       </c>
       <c r="D36">
-        <v>13128.74679838739</v>
+        <v>13347.96913188948</v>
       </c>
       <c r="E36">
         <v>-963.3592553469334</v>
@@ -4233,37 +5992,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M36">
-        <v>218.4417992435753</v>
+        <v>208.6326683621713</v>
       </c>
       <c r="N36">
-        <v>598.2248674230914</v>
+        <v>608.0339983044955</v>
       </c>
       <c r="O36">
-        <v>158.5295898671192</v>
+        <v>161.1290095506913</v>
       </c>
       <c r="P36">
-        <v>439.6952775559722</v>
+        <v>446.9049887538042</v>
       </c>
       <c r="Q36">
-        <v>739.6952775559721</v>
+        <v>746.9049887538042</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1079320227277924</v>
+        <v>0.1078920773613695</v>
       </c>
       <c r="T36">
         <v>1.433997167699065</v>
       </c>
       <c r="U36">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V36">
         <v>0.265</v>
       </c>
       <c r="W36">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +6030,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.738600714216036</v>
+        <v>3.91437579300377</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +6041,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08555248049407754</v>
+        <v>0.08485734333479245</v>
       </c>
       <c r="C37">
-        <v>9624.196258231057</v>
+        <v>9851.668297278447</v>
       </c>
       <c r="D37">
-        <v>13178.90192394534</v>
+        <v>13406.37396299273</v>
       </c>
       <c r="E37">
         <v>-852.396236326525</v>
@@ -4315,37 +6074,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M37">
-        <v>224.866558044857</v>
+        <v>214.7689233139999</v>
       </c>
       <c r="N37">
-        <v>591.8001086218097</v>
+        <v>601.8977433526669</v>
       </c>
       <c r="O37">
-        <v>156.8270287847796</v>
+        <v>159.5029019884567</v>
       </c>
       <c r="P37">
-        <v>434.9730798370301</v>
+        <v>442.3948413642102</v>
       </c>
       <c r="Q37">
-        <v>734.9730798370301</v>
+        <v>742.3948413642102</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1087041622985808</v>
+        <v>0.1086637205150653</v>
       </c>
       <c r="T37">
         <v>1.451818025752086</v>
       </c>
       <c r="U37">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V37">
         <v>0.265</v>
       </c>
       <c r="W37">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +6112,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.63178355095272</v>
+        <v>3.802536484632233</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +6123,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08540061598781212</v>
+        <v>0.08468644561108102</v>
       </c>
       <c r="C38">
-        <v>9563.773044814086</v>
+        <v>9799.623463180727</v>
       </c>
       <c r="D38">
-        <v>13229.44172954878</v>
+        <v>13465.29214791542</v>
       </c>
       <c r="E38">
         <v>-741.4332173061175</v>
@@ -4397,37 +6156,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M38">
-        <v>231.2913168461386</v>
+        <v>220.9051782658284</v>
       </c>
       <c r="N38">
-        <v>585.3753498205282</v>
+        <v>595.7614884008383</v>
       </c>
       <c r="O38">
-        <v>155.12446770244</v>
+        <v>157.8767944262221</v>
       </c>
       <c r="P38">
-        <v>430.2508821180882</v>
+        <v>437.8846939746161</v>
       </c>
       <c r="Q38">
-        <v>730.2508821180882</v>
+        <v>737.8846939746161</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1095004312309564</v>
+        <v>0.1094594775173141</v>
       </c>
       <c r="T38">
         <v>1.470195785619263</v>
       </c>
       <c r="U38">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V38">
         <v>0.265</v>
       </c>
       <c r="W38">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +6194,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.530900674537368</v>
+        <v>3.696910471170227</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +6205,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08524875148154668</v>
+        <v>0.08451554788736958</v>
       </c>
       <c r="C39">
-        <v>9503.738954111355</v>
+        <v>9748.098781023917</v>
       </c>
       <c r="D39">
-        <v>13280.37065786645</v>
+        <v>13524.73048477902</v>
       </c>
       <c r="E39">
         <v>-630.4701982857096</v>
@@ -4479,37 +6238,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M39">
-        <v>237.7160756474202</v>
+        <v>227.041433217657</v>
       </c>
       <c r="N39">
-        <v>578.9505910192465</v>
+        <v>589.6252334490098</v>
       </c>
       <c r="O39">
-        <v>153.4219066201003</v>
+        <v>156.2506868639876</v>
       </c>
       <c r="P39">
-        <v>425.5286843991462</v>
+        <v>433.3745465850222</v>
       </c>
       <c r="Q39">
-        <v>725.5286843991462</v>
+        <v>733.3745465850222</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1103219785421376</v>
+        <v>0.1102804966466184</v>
       </c>
       <c r="T39">
         <v>1.489156966434605</v>
       </c>
       <c r="U39">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V39">
         <v>0.265</v>
       </c>
       <c r="W39">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +6276,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.435470926576898</v>
+        <v>3.596993971949411</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +6287,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08509688697528128</v>
+        <v>0.08434465016365814</v>
       </c>
       <c r="C40">
-        <v>9444.098497467119</v>
+        <v>9697.10116949445</v>
       </c>
       <c r="D40">
-        <v>13331.69322024263</v>
+        <v>13584.69589226996</v>
       </c>
       <c r="E40">
         <v>-519.5071792653016</v>
@@ -4561,37 +6320,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M40">
-        <v>244.1408344487018</v>
+        <v>233.1776881694855</v>
       </c>
       <c r="N40">
-        <v>572.525832217965</v>
+        <v>583.4889784971813</v>
       </c>
       <c r="O40">
-        <v>151.7193455377607</v>
+        <v>154.624579301753</v>
       </c>
       <c r="P40">
-        <v>420.8064866802043</v>
+        <v>428.8643991954282</v>
       </c>
       <c r="Q40">
-        <v>720.8064866802042</v>
+        <v>728.8643991954282</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1111700273794859</v>
+        <v>0.1111280002639647</v>
       </c>
       <c r="T40">
         <v>1.50872979824399</v>
       </c>
       <c r="U40">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V40">
         <v>0.265</v>
       </c>
       <c r="W40">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +6358,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.345063796930138</v>
+        <v>3.502336235845479</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +6369,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08494502246901584</v>
+        <v>0.08417375243994671</v>
       </c>
       <c r="C41">
-        <v>9384.85625623339</v>
+        <v>9646.637670528382</v>
       </c>
       <c r="D41">
-        <v>13383.41399802931</v>
+        <v>13645.1954123243</v>
       </c>
       <c r="E41">
         <v>-408.5441602448927</v>
@@ -4643,37 +6402,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M41">
-        <v>250.5655932499835</v>
+        <v>239.3139431213141</v>
       </c>
       <c r="N41">
-        <v>566.1010734166832</v>
+        <v>577.3527235453527</v>
       </c>
       <c r="O41">
-        <v>150.0167844554211</v>
+        <v>152.9984717395185</v>
       </c>
       <c r="P41">
-        <v>416.0842889612621</v>
+        <v>424.3542518058342</v>
       </c>
       <c r="Q41">
-        <v>716.0842889612621</v>
+        <v>724.3542518058342</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1120458810967473</v>
+        <v>0.1120032908851585</v>
       </c>
       <c r="T41">
         <v>1.528944362243847</v>
       </c>
       <c r="U41">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V41">
         <v>0.265</v>
       </c>
       <c r="W41">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +6440,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.259292930342185</v>
+        <v>3.412532742618672</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +6451,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08479315796275043</v>
+        <v>0.08400285471623527</v>
       </c>
       <c r="C42">
-        <v>9326.016883133063</v>
+        <v>9596.715452068172</v>
       </c>
       <c r="D42">
-        <v>13435.53764394939</v>
+        <v>13706.2362128845</v>
       </c>
       <c r="E42">
         <v>-297.5811412244848</v>
@@ -4725,37 +6484,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M42">
-        <v>256.9903520512651</v>
+        <v>245.4501980731427</v>
       </c>
       <c r="N42">
-        <v>559.6763146154017</v>
+        <v>571.216468593524</v>
       </c>
       <c r="O42">
-        <v>148.3142233730815</v>
+        <v>151.3723641772839</v>
       </c>
       <c r="P42">
-        <v>411.3620912423202</v>
+        <v>419.8441044162402</v>
       </c>
       <c r="Q42">
-        <v>711.3620912423203</v>
+        <v>719.8441044162402</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1129509299379174</v>
+        <v>0.1129077578603921</v>
       </c>
       <c r="T42">
         <v>1.549832745043698</v>
       </c>
       <c r="U42">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V42">
         <v>0.265</v>
       </c>
       <c r="W42">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +6522,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.177810607083631</v>
+        <v>3.327219424053204</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +6533,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08464129345648498</v>
+        <v>0.08383195699252384</v>
       </c>
       <c r="C43">
-        <v>9267.585103655314</v>
+        <v>9547.341810893706</v>
       </c>
       <c r="D43">
-        <v>13488.06888349205</v>
+        <v>13767.82559073044</v>
       </c>
       <c r="E43">
         <v>-186.6181222040768</v>
@@ -4807,37 +6566,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M43">
-        <v>263.4151108525467</v>
+        <v>251.5864530249712</v>
       </c>
       <c r="N43">
-        <v>553.25155581412</v>
+        <v>565.0802136416955</v>
       </c>
       <c r="O43">
-        <v>146.6116622907418</v>
+        <v>149.7462566150493</v>
       </c>
       <c r="P43">
-        <v>406.6398935233782</v>
+        <v>415.3339570266462</v>
       </c>
       <c r="Q43">
-        <v>706.6398935233782</v>
+        <v>715.3339570266462</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.113886658400822</v>
+        <v>0.1138428847330913</v>
       </c>
       <c r="T43">
         <v>1.571429208616426</v>
       </c>
       <c r="U43">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V43">
         <v>0.265</v>
       </c>
       <c r="W43">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +6604,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.100303031301103</v>
+        <v>3.246067730783615</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +6615,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08448942895021957</v>
+        <v>0.0836610592688124</v>
       </c>
       <c r="C44">
-        <v>9209.56571748358</v>
+        <v>9498.524175530067</v>
       </c>
       <c r="D44">
-        <v>13541.01251634072</v>
+        <v>13829.97097438721</v>
       </c>
       <c r="E44">
         <v>-75.65510318366887</v>
@@ -4889,37 +6648,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M44">
-        <v>269.8398696538284</v>
+        <v>257.7227079767998</v>
       </c>
       <c r="N44">
-        <v>546.8267970128384</v>
+        <v>558.943958689867</v>
       </c>
       <c r="O44">
-        <v>144.9091012084022</v>
+        <v>148.1201490528148</v>
       </c>
       <c r="P44">
-        <v>401.9176958044362</v>
+        <v>410.8238096370522</v>
       </c>
       <c r="Q44">
-        <v>701.9176958044362</v>
+        <v>710.8238096370522</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1148546533624475</v>
+        <v>0.1148102573600214</v>
       </c>
       <c r="T44">
         <v>1.593770377829594</v>
       </c>
       <c r="U44">
-        <v>0.05789999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V44">
         <v>0.265</v>
       </c>
       <c r="W44">
-        <v>0.0425565</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +6686,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.0264862924606</v>
+        <v>3.168780403860195</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +6697,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08515929444395416</v>
+        <v>0.08349016154510097</v>
       </c>
       <c r="C45">
-        <v>8868.144882512201</v>
+        <v>9450.270109234354</v>
       </c>
       <c r="D45">
-        <v>13310.55470038975</v>
+        <v>13892.6799271119</v>
       </c>
       <c r="E45">
         <v>35.30791583673908</v>
@@ -4971,45 +6730,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M45">
-        <v>288.6702939815916</v>
+        <v>263.8589629286283</v>
       </c>
       <c r="N45">
-        <v>527.9963726850751</v>
+        <v>552.8077037380384</v>
       </c>
       <c r="O45">
-        <v>139.9190387615449</v>
+        <v>146.4940414905802</v>
       </c>
       <c r="P45">
-        <v>388.0773339235302</v>
+        <v>406.3136622474582</v>
       </c>
       <c r="Q45">
-        <v>688.0773339235302</v>
+        <v>706.3136622474583</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1158566130595687</v>
+        <v>0.1158115728861421</v>
       </c>
       <c r="T45">
         <v>1.616895447716907</v>
       </c>
       <c r="U45">
-        <v>0.06049999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V45">
         <v>0.265</v>
       </c>
       <c r="W45">
-        <v>0.04446749999999999</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.829063757834207</v>
+        <v>3.095087836328563</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +6779,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08502653993768874</v>
+        <v>0.08331926382138954</v>
       </c>
       <c r="C46">
-        <v>8802.228816910983</v>
+        <v>9402.587313064198</v>
       </c>
       <c r="D46">
-        <v>13355.60165380894</v>
+        <v>13955.96014996215</v>
       </c>
       <c r="E46">
         <v>146.270934857147</v>
@@ -5053,45 +6812,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M46">
-        <v>295.3835566323262</v>
+        <v>269.9952178804569</v>
       </c>
       <c r="N46">
-        <v>521.2831100343406</v>
+        <v>546.6714487862098</v>
       </c>
       <c r="O46">
-        <v>138.1400241591002</v>
+        <v>144.8679339283456</v>
       </c>
       <c r="P46">
-        <v>383.1430858752403</v>
+        <v>401.8035148578642</v>
       </c>
       <c r="Q46">
-        <v>683.1430858752403</v>
+        <v>701.8035148578642</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.116894357031587</v>
+        <v>0.1168486496810527</v>
       </c>
       <c r="T46">
         <v>1.640846412957338</v>
       </c>
       <c r="U46">
-        <v>0.06049999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V46">
         <v>0.265</v>
       </c>
       <c r="W46">
-        <v>0.04446749999999999</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.764766854247066</v>
+        <v>3.024744930957459</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +6861,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08489378543142331</v>
+        <v>0.08397524109767809</v>
       </c>
       <c r="C47">
-        <v>8736.618691806141</v>
+        <v>9051.814604204774</v>
       </c>
       <c r="D47">
-        <v>13400.9545477245</v>
+        <v>13716.15046012314</v>
       </c>
       <c r="E47">
         <v>257.233953877555</v>
@@ -5135,37 +6894,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M47">
-        <v>302.0968192830609</v>
+        <v>288.6148124720814</v>
       </c>
       <c r="N47">
-        <v>514.5698473836057</v>
+        <v>528.0518541945853</v>
       </c>
       <c r="O47">
-        <v>136.3610095566555</v>
+        <v>139.9337413615651</v>
       </c>
       <c r="P47">
-        <v>378.2088378269502</v>
+        <v>388.1181128330202</v>
       </c>
       <c r="Q47">
-        <v>678.2088378269502</v>
+        <v>688.1181128330202</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1179698371480424</v>
+        <v>0.1179234383594147</v>
       </c>
       <c r="T47">
         <v>1.665668322388331</v>
       </c>
       <c r="U47">
-        <v>0.06049999999999999</v>
+        <v>0.05779999999999999</v>
       </c>
       <c r="V47">
         <v>0.265</v>
       </c>
       <c r="W47">
-        <v>0.04446749999999999</v>
+        <v>0.04248299999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +6932,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.703327590819353</v>
+        <v>2.829607599387039</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +6943,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08476103092515788</v>
+        <v>0.08382271837396665</v>
       </c>
       <c r="C48">
-        <v>8671.317634551735</v>
+        <v>8995.871970797991</v>
       </c>
       <c r="D48">
-        <v>13446.61650949051</v>
+        <v>13771.17084573676</v>
       </c>
       <c r="E48">
         <v>368.1969728979639</v>
@@ -5217,37 +6976,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M48">
-        <v>308.8100819337957</v>
+        <v>295.028474971461</v>
       </c>
       <c r="N48">
-        <v>507.8565847328711</v>
+        <v>521.6381916952057</v>
       </c>
       <c r="O48">
-        <v>134.5819949542108</v>
+        <v>138.2341207992295</v>
       </c>
       <c r="P48">
-        <v>373.2745897786602</v>
+        <v>383.4040708959762</v>
       </c>
       <c r="Q48">
-        <v>673.2745897786602</v>
+        <v>683.4040708959762</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1190851498614035</v>
+        <v>0.1190380340258642</v>
       </c>
       <c r="T48">
         <v>1.691409561798249</v>
       </c>
       <c r="U48">
-        <v>0.06049999999999999</v>
+        <v>0.05779999999999999</v>
       </c>
       <c r="V48">
         <v>0.265</v>
       </c>
       <c r="W48">
-        <v>0.04446749999999999</v>
+        <v>0.04248299999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +7014,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.644559599714585</v>
+        <v>2.768094390704712</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +7025,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08462827641889246</v>
+        <v>0.08367019565025523</v>
       </c>
       <c r="C49">
-        <v>8606.328815271732</v>
+        <v>8940.372528081367</v>
       </c>
       <c r="D49">
-        <v>13492.59070923091</v>
+        <v>13826.63442204055</v>
       </c>
       <c r="E49">
         <v>479.1599919183718</v>
@@ -5299,37 +7058,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M49">
-        <v>315.5233445845304</v>
+        <v>301.4421374708406</v>
       </c>
       <c r="N49">
-        <v>501.1433220821364</v>
+        <v>515.2245291958261</v>
       </c>
       <c r="O49">
-        <v>132.8029803517661</v>
+        <v>136.5345002368939</v>
       </c>
       <c r="P49">
-        <v>368.3403417303703</v>
+        <v>378.6900289589322</v>
       </c>
       <c r="Q49">
-        <v>668.3403417303703</v>
+        <v>678.6900289589322</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1202425498469669</v>
+        <v>0.1201946899061419</v>
       </c>
       <c r="T49">
         <v>1.718122168733071</v>
       </c>
       <c r="U49">
-        <v>0.06049999999999999</v>
+        <v>0.05779999999999999</v>
       </c>
       <c r="V49">
         <v>0.265</v>
       </c>
       <c r="W49">
-        <v>0.04446749999999999</v>
+        <v>0.04248299999999999</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +7096,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.588292374188742</v>
+        <v>2.709198765370569</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +7107,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08449552191262703</v>
+        <v>0.08351767292654379</v>
       </c>
       <c r="C50">
-        <v>8541.655447593668</v>
+        <v>8885.321652578379</v>
       </c>
       <c r="D50">
-        <v>13538.88036057326</v>
+        <v>13882.54656555797</v>
       </c>
       <c r="E50">
         <v>590.1230109387798</v>
@@ -5381,37 +7140,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M50">
-        <v>322.2366072352651</v>
+        <v>307.8557999702202</v>
       </c>
       <c r="N50">
-        <v>494.4300594314017</v>
+        <v>508.8108666964466</v>
       </c>
       <c r="O50">
-        <v>131.0239657493215</v>
+        <v>134.8348796745584</v>
       </c>
       <c r="P50">
-        <v>363.4060936820802</v>
+        <v>373.9759870218882</v>
       </c>
       <c r="Q50">
-        <v>663.4060936820802</v>
+        <v>673.9759870218882</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1214444652165904</v>
+        <v>0.1213958325510457</v>
       </c>
       <c r="T50">
         <v>1.745862183626923</v>
       </c>
       <c r="U50">
-        <v>0.06049999999999999</v>
+        <v>0.05779999999999999</v>
       </c>
       <c r="V50">
         <v>0.265</v>
       </c>
       <c r="W50">
-        <v>0.04446749999999999</v>
+        <v>0.04248299999999999</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +7178,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.534369616393144</v>
+        <v>2.652757124425349</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +7189,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08533517240636161</v>
+        <v>0.08336515020283235</v>
       </c>
       <c r="C51">
-        <v>8143.152830604046</v>
+        <v>8830.72480813193</v>
       </c>
       <c r="D51">
-        <v>13251.34076260404</v>
+        <v>13938.91274013193</v>
       </c>
       <c r="E51">
         <v>701.0860299591877</v>
@@ -5463,45 +7222,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M51">
-        <v>343.6302773023997</v>
+        <v>314.2694624695997</v>
       </c>
       <c r="N51">
-        <v>473.0363893642671</v>
+        <v>502.397204197067</v>
       </c>
       <c r="O51">
-        <v>125.3546431815308</v>
+        <v>133.1352591122228</v>
       </c>
       <c r="P51">
-        <v>347.6817461827363</v>
+        <v>369.2619450848442</v>
       </c>
       <c r="Q51">
-        <v>647.6817461827363</v>
+        <v>669.2619450848442</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1226935145222777</v>
+        <v>0.122644078829083</v>
       </c>
       <c r="T51">
         <v>1.774690042242103</v>
       </c>
       <c r="U51">
-        <v>0.06319999999999999</v>
+        <v>0.05779999999999999</v>
       </c>
       <c r="V51">
         <v>0.265</v>
       </c>
       <c r="W51">
-        <v>0.04645199999999999</v>
+        <v>0.04248299999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.376585302895147</v>
+        <v>2.598619223926873</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +7271,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08522226290009619</v>
+        <v>0.08321262747912091</v>
       </c>
       <c r="C52">
-        <v>8070.143044929279</v>
+        <v>8776.587547684278</v>
       </c>
       <c r="D52">
-        <v>13289.29399594968</v>
+        <v>13995.73849870468</v>
       </c>
       <c r="E52">
         <v>812.0490489795957</v>
@@ -5545,45 +7304,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M52">
-        <v>350.6431401044895</v>
+        <v>320.6831249689793</v>
       </c>
       <c r="N52">
-        <v>466.0235265621773</v>
+        <v>495.9835416976874</v>
       </c>
       <c r="O52">
-        <v>123.496234538977</v>
+        <v>131.4356385498872</v>
       </c>
       <c r="P52">
-        <v>342.5272920232003</v>
+        <v>364.5479031478002</v>
       </c>
       <c r="Q52">
-        <v>642.5272920232003</v>
+        <v>664.5479031478003</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1239925258001924</v>
+        <v>0.1239422549582418</v>
       </c>
       <c r="T52">
         <v>1.80467101520189</v>
       </c>
       <c r="U52">
-        <v>0.06319999999999999</v>
+        <v>0.05779999999999999</v>
       </c>
       <c r="V52">
         <v>0.265</v>
       </c>
       <c r="W52">
-        <v>0.04645199999999999</v>
+        <v>0.04248299999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.329053596837244</v>
+        <v>2.546646839448336</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +7353,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08510935339383077</v>
+        <v>0.08437207975540947</v>
       </c>
       <c r="C53">
-        <v>7997.351287813527</v>
+        <v>8244.92149777825</v>
       </c>
       <c r="D53">
-        <v>13327.46525785434</v>
+        <v>13575.03546781906</v>
       </c>
       <c r="E53">
         <v>923.0120680000036</v>
@@ -5627,37 +7386,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M53">
-        <v>357.6560029065793</v>
+        <v>346.9036863635017</v>
       </c>
       <c r="N53">
-        <v>459.0106637600875</v>
+        <v>469.762980303165</v>
       </c>
       <c r="O53">
-        <v>121.6378258964232</v>
+        <v>124.4871897803387</v>
       </c>
       <c r="P53">
-        <v>337.3728378636643</v>
+        <v>345.2757905228263</v>
       </c>
       <c r="Q53">
-        <v>637.3728378636642</v>
+        <v>645.2757905228264</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1253445579465934</v>
+        <v>0.1252934178681826</v>
       </c>
       <c r="T53">
         <v>1.83587570134371</v>
       </c>
       <c r="U53">
-        <v>0.06319999999999999</v>
+        <v>0.06129999999999999</v>
       </c>
       <c r="V53">
         <v>0.265</v>
       </c>
       <c r="W53">
-        <v>0.04645199999999999</v>
+        <v>0.04505549999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +7424,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.2833858792522</v>
+        <v>2.354159666700474</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +7435,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08679278388756534</v>
+        <v>0.08424528203169804</v>
       </c>
       <c r="C54">
-        <v>7339.075808122067</v>
+        <v>8178.730776050451</v>
       </c>
       <c r="D54">
-        <v>12780.15279718329</v>
+        <v>13619.80776511167</v>
       </c>
       <c r="E54">
         <v>1033.975087020412</v>
@@ -5709,45 +7468,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M54">
-        <v>391.7882275572568</v>
+        <v>353.7057194294528</v>
       </c>
       <c r="N54">
-        <v>424.87843910941</v>
+        <v>462.960947237214</v>
       </c>
       <c r="O54">
-        <v>112.5927863639936</v>
+        <v>122.6846510178617</v>
       </c>
       <c r="P54">
-        <v>312.2856527454163</v>
+        <v>340.2762962193523</v>
       </c>
       <c r="Q54">
-        <v>612.2856527454163</v>
+        <v>640.2762962193523</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1267529247657611</v>
+        <v>0.1267008792327043</v>
       </c>
       <c r="T54">
         <v>1.868380582741438</v>
       </c>
       <c r="U54">
-        <v>0.06789999999999999</v>
+        <v>0.06129999999999999</v>
       </c>
       <c r="V54">
         <v>0.265</v>
       </c>
       <c r="W54">
-        <v>0.04990649999999999</v>
+        <v>0.04505549999999999</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.084459432991302</v>
+        <v>2.308887365417772</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +7517,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08671441938129992</v>
+        <v>0.0841184843079866</v>
       </c>
       <c r="C55">
-        <v>7252.59096523351</v>
+        <v>8112.836361730662</v>
       </c>
       <c r="D55">
-        <v>12804.63097331514</v>
+        <v>13664.87636981229</v>
       </c>
       <c r="E55">
         <v>1144.93810604082</v>
@@ -5791,45 +7550,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M55">
-        <v>399.3226165487425</v>
+        <v>360.5077524954038</v>
       </c>
       <c r="N55">
-        <v>417.3440501179242</v>
+        <v>456.1589141712629</v>
       </c>
       <c r="O55">
-        <v>110.5961732812499</v>
+        <v>120.8821122553847</v>
       </c>
       <c r="P55">
-        <v>306.7478768366743</v>
+        <v>335.2768019158783</v>
       </c>
       <c r="Q55">
-        <v>606.7478768366743</v>
+        <v>635.2768019158782</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1282212220878722</v>
+        <v>0.1281682325701843</v>
       </c>
       <c r="T55">
         <v>1.902268650581624</v>
       </c>
       <c r="U55">
-        <v>0.06789999999999999</v>
+        <v>0.06129999999999999</v>
       </c>
       <c r="V55">
         <v>0.265</v>
       </c>
       <c r="W55">
-        <v>0.04990649999999999</v>
+        <v>0.04505549999999999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.045130009727315</v>
+        <v>2.265323452862719</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +7599,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08663605487503449</v>
+        <v>0.08510300658427518</v>
       </c>
       <c r="C56">
-        <v>7166.200069725168</v>
+        <v>7659.574461326654</v>
       </c>
       <c r="D56">
-        <v>12829.2030968272</v>
+        <v>13322.57748842869</v>
       </c>
       <c r="E56">
         <v>1255.901125061228</v>
@@ -5873,37 +7632,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M56">
-        <v>406.8570055402282</v>
+        <v>384.0873940372405</v>
       </c>
       <c r="N56">
-        <v>409.8096611264385</v>
+        <v>432.5792726294262</v>
       </c>
       <c r="O56">
-        <v>108.5995601985062</v>
+        <v>114.6335072467979</v>
       </c>
       <c r="P56">
-        <v>301.2101009279323</v>
+        <v>317.9457653826283</v>
       </c>
       <c r="Q56">
-        <v>601.2101009279323</v>
+        <v>617.9457653826282</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1297533584239881</v>
+        <v>0.1296993838788591</v>
       </c>
       <c r="T56">
         <v>1.93763011267573</v>
       </c>
       <c r="U56">
-        <v>0.06789999999999999</v>
+        <v>0.06409999999999999</v>
       </c>
       <c r="V56">
         <v>0.265</v>
       </c>
       <c r="W56">
-        <v>0.04990649999999999</v>
+        <v>0.04711349999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +7670,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.007257231769402</v>
+        <v>2.126252200267432</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +7681,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09221719036876908</v>
+        <v>0.08499678886056372</v>
       </c>
       <c r="C57">
-        <v>5512.672320026713</v>
+        <v>7584.713732721524</v>
       </c>
       <c r="D57">
-        <v>11286.63836614916</v>
+        <v>13358.67977884397</v>
       </c>
       <c r="E57">
         <v>1366.864144081636</v>
@@ -5955,45 +7714,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M57">
-        <v>499.8329191774282</v>
+        <v>391.2001235564487</v>
       </c>
       <c r="N57">
-        <v>316.8337474892385</v>
+        <v>425.4665431102181</v>
       </c>
       <c r="O57">
-        <v>83.96094308464822</v>
+        <v>112.7486339242078</v>
       </c>
       <c r="P57">
-        <v>232.8728044045903</v>
+        <v>312.7179091860103</v>
       </c>
       <c r="Q57">
-        <v>532.8728044045903</v>
+        <v>612.7179091860103</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1313535897083757</v>
+        <v>0.1312985863568083</v>
       </c>
       <c r="T57">
         <v>1.974563195307352</v>
       </c>
       <c r="U57">
-        <v>0.0819</v>
+        <v>0.06409999999999999</v>
       </c>
       <c r="V57">
         <v>0.265</v>
       </c>
       <c r="W57">
-        <v>0.0601965</v>
+        <v>0.04711349999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.633879313132576</v>
+        <v>2.087593069353479</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +7763,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09224172586250365</v>
+        <v>0.08489057113685231</v>
       </c>
       <c r="C58">
-        <v>5395.746489767616</v>
+        <v>7510.049199925097</v>
       </c>
       <c r="D58">
-        <v>11280.67555491047</v>
+        <v>13394.97826506795</v>
       </c>
       <c r="E58">
         <v>1477.827163102044</v>
@@ -6037,45 +7796,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M58">
-        <v>508.9207904351996</v>
+        <v>398.3128530756568</v>
       </c>
       <c r="N58">
-        <v>307.7458762314671</v>
+        <v>418.35381359101</v>
       </c>
       <c r="O58">
-        <v>81.55265720133879</v>
+        <v>110.8637606016176</v>
       </c>
       <c r="P58">
-        <v>226.1932190301283</v>
+        <v>307.4900529893923</v>
       </c>
       <c r="Q58">
-        <v>526.1932190301284</v>
+        <v>607.4900529893923</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1330265587784174</v>
+        <v>0.1329704798564825</v>
       </c>
       <c r="T58">
         <v>2.013175054422229</v>
       </c>
       <c r="U58">
-        <v>0.0819</v>
+        <v>0.06409999999999999</v>
       </c>
       <c r="V58">
         <v>0.265</v>
       </c>
       <c r="W58">
-        <v>0.0601965</v>
+        <v>0.04711349999999999</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.604702896826637</v>
+        <v>2.050314621686452</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +7845,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09226626135623822</v>
+        <v>0.08478435341314086</v>
       </c>
       <c r="C59">
-        <v>5278.82695657282</v>
+        <v>7435.582466617104</v>
       </c>
       <c r="D59">
-        <v>11274.71904073608</v>
+        <v>13431.47455078037</v>
       </c>
       <c r="E59">
         <v>1588.790182122453</v>
@@ -6119,45 +7878,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M59">
-        <v>518.0086616929711</v>
+        <v>405.425582594865</v>
       </c>
       <c r="N59">
-        <v>298.6580049736956</v>
+        <v>411.2410840718017</v>
       </c>
       <c r="O59">
-        <v>79.14437131802934</v>
+        <v>108.9788872790275</v>
       </c>
       <c r="P59">
-        <v>219.5136336556662</v>
+        <v>302.2621967927743</v>
       </c>
       <c r="Q59">
-        <v>519.5136336556662</v>
+        <v>602.2621967927743</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1347773403633447</v>
+        <v>0.1347201358445137</v>
       </c>
       <c r="T59">
         <v>2.053582813961055</v>
       </c>
       <c r="U59">
-        <v>0.0819</v>
+        <v>0.06409999999999999</v>
       </c>
       <c r="V59">
         <v>0.265</v>
       </c>
       <c r="W59">
-        <v>0.0601965</v>
+        <v>0.04711349999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.576550214426169</v>
+        <v>2.014344189727041</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +7927,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.09229079684997279</v>
+        <v>0.08800327568942942</v>
       </c>
       <c r="C60">
-        <v>5161.913710472507</v>
+        <v>6300.175919727631</v>
       </c>
       <c r="D60">
-        <v>11268.76881365618</v>
+        <v>12407.0310229113</v>
       </c>
       <c r="E60">
         <v>1699.75320114286</v>
@@ -6201,45 +7960,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M60">
-        <v>527.0965329507425</v>
+        <v>462.7379819189057</v>
       </c>
       <c r="N60">
-        <v>289.5701337159243</v>
+        <v>353.928684747761</v>
       </c>
       <c r="O60">
-        <v>76.73608543471994</v>
+        <v>93.79110145815667</v>
       </c>
       <c r="P60">
-        <v>212.8340482812043</v>
+        <v>260.1375832896043</v>
       </c>
       <c r="Q60">
-        <v>512.8340482812043</v>
+        <v>560.1375832896043</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1366114924999352</v>
+        <v>0.1365531087843558</v>
       </c>
       <c r="T60">
         <v>2.095914752525538</v>
       </c>
       <c r="U60">
-        <v>0.0819</v>
+        <v>0.07189999999999999</v>
       </c>
       <c r="V60">
         <v>0.265</v>
       </c>
       <c r="W60">
-        <v>0.0601965</v>
+        <v>0.05284649999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.549368314177443</v>
+        <v>1.76485764855539</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +8009,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.0923153323437074</v>
+        <v>0.08964562296571799</v>
       </c>
       <c r="C61">
-        <v>5045.006741517889</v>
+        <v>5724.476577466059</v>
       </c>
       <c r="D61">
-        <v>11262.82486372197</v>
+        <v>11942.29469967014</v>
       </c>
       <c r="E61">
         <v>1810.716220163268</v>
@@ -6283,37 +8042,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M61">
-        <v>536.1844042085139</v>
+        <v>496.248813663069</v>
       </c>
       <c r="N61">
-        <v>280.4822624581528</v>
+        <v>320.4178530035978</v>
       </c>
       <c r="O61">
-        <v>74.32779955141051</v>
+        <v>84.91073104595341</v>
       </c>
       <c r="P61">
-        <v>206.1544629067423</v>
+        <v>235.5071219576444</v>
       </c>
       <c r="Q61">
-        <v>506.1544629067423</v>
+        <v>535.5071219576444</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.138535115472457</v>
+        <v>0.1384754950383366</v>
       </c>
       <c r="T61">
         <v>2.140311663702924</v>
       </c>
       <c r="U61">
-        <v>0.0819</v>
+        <v>0.07579999999999999</v>
       </c>
       <c r="V61">
         <v>0.265</v>
       </c>
       <c r="W61">
-        <v>0.0601965</v>
+        <v>0.05571299999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +8080,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.52310783427613</v>
+        <v>1.645679836770647</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +8091,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1157093587579313</v>
+        <v>0.08962540024200656</v>
       </c>
       <c r="C62">
-        <v>1165.12312242408</v>
+        <v>5619.024192116041</v>
       </c>
       <c r="D62">
-        <v>7493.904263648565</v>
+        <v>11947.80533334053</v>
       </c>
       <c r="E62">
         <v>1921.679239183676</v>
@@ -6365,45 +8124,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M62">
-        <v>871.5035513862849</v>
+        <v>504.6598105048159</v>
       </c>
       <c r="N62">
-        <v>-54.83688471961818</v>
+        <v>312.0068561618509</v>
       </c>
       <c r="O62">
-        <v>-14.53177445069882</v>
+        <v>82.68181688289049</v>
       </c>
       <c r="P62">
-        <v>-40.30511026891936</v>
+        <v>229.3250392789604</v>
       </c>
       <c r="Q62">
-        <v>259.6948897310807</v>
+        <v>529.3250392789604</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1416821339446159</v>
+        <v>0.1404940006050164</v>
       </c>
       <c r="T62">
-        <v>2.212944347746442</v>
+        <v>2.186928420439178</v>
       </c>
       <c r="U62">
-        <v>0.1309</v>
+        <v>0.07579999999999999</v>
       </c>
       <c r="V62">
-        <v>0.2483256279591938</v>
+        <v>0.265</v>
       </c>
       <c r="W62">
-        <v>0.09839417530014152</v>
+        <v>0.05571299999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.9370778413554481</v>
+        <v>1.618251839491136</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +8173,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1165603587579313</v>
+        <v>0.08960517751829512</v>
       </c>
       <c r="C63">
-        <v>964.0346060163338</v>
+        <v>5513.576894750073</v>
       </c>
       <c r="D63">
-        <v>7403.778766261226</v>
+        <v>11953.32105499497</v>
       </c>
       <c r="E63">
         <v>2032.642258204084</v>
@@ -6447,45 +8206,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M63">
-        <v>886.0286105760564</v>
+        <v>513.0708073465628</v>
       </c>
       <c r="N63">
-        <v>-69.36194390938965</v>
+        <v>303.595859320104</v>
       </c>
       <c r="O63">
-        <v>-18.38091513598826</v>
+        <v>80.45290271982755</v>
       </c>
       <c r="P63">
-        <v>-50.98102877340139</v>
+        <v>223.1429566002764</v>
       </c>
       <c r="Q63">
-        <v>249.0189712265986</v>
+        <v>523.1429566002764</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1441406501996061</v>
+        <v>0.1426160192776798</v>
       </c>
       <c r="T63">
-        <v>2.269686510509172</v>
+        <v>2.235935780084985</v>
       </c>
       <c r="U63">
-        <v>0.1309</v>
+        <v>0.07579999999999999</v>
       </c>
       <c r="V63">
-        <v>0.2442547160254365</v>
+        <v>0.265</v>
       </c>
       <c r="W63">
-        <v>0.09892705767227036</v>
+        <v>0.05571299999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.921715909529949</v>
+        <v>1.591723120810954</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +8255,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1174113587579313</v>
+        <v>0.08958495479458367</v>
       </c>
       <c r="C64">
-        <v>765.0881184600703</v>
+        <v>5408.134692418032</v>
       </c>
       <c r="D64">
-        <v>7315.795297725372</v>
+        <v>11958.84187168333</v>
       </c>
       <c r="E64">
         <v>2143.605277224493</v>
@@ -6529,45 +8288,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M64">
-        <v>900.5536697658279</v>
+        <v>521.4818041883098</v>
       </c>
       <c r="N64">
-        <v>-83.88700309916112</v>
+        <v>295.184862478357</v>
       </c>
       <c r="O64">
-        <v>-22.2300558212777</v>
+        <v>78.22398855676461</v>
       </c>
       <c r="P64">
-        <v>-61.65694727788342</v>
+        <v>216.9608739215924</v>
       </c>
       <c r="Q64">
-        <v>238.3430527221166</v>
+        <v>516.9608739215923</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1467285620469641</v>
+        <v>0.1448497231436413</v>
       </c>
       <c r="T64">
-        <v>2.329415102890992</v>
+        <v>2.287522474448991</v>
       </c>
       <c r="U64">
-        <v>0.1309</v>
+        <v>0.07579999999999999</v>
       </c>
       <c r="V64">
-        <v>0.2403151238314778</v>
+        <v>0.265</v>
       </c>
       <c r="W64">
-        <v>0.09944275029045954</v>
+        <v>0.05571299999999999</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.9068495238923691</v>
+        <v>1.566050167249487</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +8337,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1182623587579313</v>
+        <v>0.08956473207087225</v>
       </c>
       <c r="C65">
-        <v>568.2081916122179</v>
+        <v>5302.697592182824</v>
       </c>
       <c r="D65">
-        <v>7229.878389897927</v>
+        <v>11964.36779046853</v>
       </c>
       <c r="E65">
         <v>2254.568296244901</v>
@@ -6611,45 +8370,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M65">
-        <v>915.0787289555993</v>
+        <v>529.8928010300567</v>
       </c>
       <c r="N65">
-        <v>-98.41206228893259</v>
+        <v>286.77386563661</v>
       </c>
       <c r="O65">
-        <v>-26.07919650656714</v>
+        <v>75.99507439370166</v>
       </c>
       <c r="P65">
-        <v>-72.33286578236545</v>
+        <v>210.7787912429084</v>
       </c>
       <c r="Q65">
-        <v>227.6671342176346</v>
+        <v>510.7787912429084</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1494563610212064</v>
+        <v>0.1472041677591142</v>
       </c>
       <c r="T65">
-        <v>2.392372267833992</v>
+        <v>2.341897638778619</v>
       </c>
       <c r="U65">
-        <v>0.1309</v>
+        <v>0.07579999999999999</v>
       </c>
       <c r="V65">
-        <v>0.236500598056375</v>
+        <v>0.265</v>
       </c>
       <c r="W65">
-        <v>0.0999420717144205</v>
+        <v>0.05571299999999999</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8924550870051885</v>
+        <v>1.541192228086797</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +8419,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1191133587579313</v>
+        <v>0.08954450934716081</v>
       </c>
       <c r="C66">
-        <v>373.3228613781293</v>
+        <v>5197.26560112043</v>
       </c>
       <c r="D66">
-        <v>7145.956078684247</v>
+        <v>11969.89881842655</v>
       </c>
       <c r="E66">
         <v>2365.531315265309</v>
@@ -6693,45 +8452,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M66">
-        <v>929.6037881453707</v>
+        <v>538.3037978718037</v>
       </c>
       <c r="N66">
-        <v>-112.9371214787039</v>
+        <v>278.3628687948631</v>
       </c>
       <c r="O66">
-        <v>-29.92833719185655</v>
+        <v>73.76616023063872</v>
       </c>
       <c r="P66">
-        <v>-83.0087842868474</v>
+        <v>204.5967085642243</v>
       </c>
       <c r="Q66">
-        <v>216.9912157131526</v>
+        <v>504.5967085642243</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1523357043829066</v>
+        <v>0.1496894148532245</v>
       </c>
       <c r="T66">
-        <v>2.458827053051603</v>
+        <v>2.399293645571005</v>
       </c>
       <c r="U66">
-        <v>0.1309</v>
+        <v>0.07579999999999999</v>
       </c>
       <c r="V66">
-        <v>0.2328052762117441</v>
+        <v>0.265</v>
       </c>
       <c r="W66">
-        <v>0.1004257893438827</v>
+        <v>0.05571299999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8785104762707325</v>
+        <v>1.51711109952294</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +8501,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1199643587579313</v>
+        <v>0.09630833662344938</v>
       </c>
       <c r="C67">
-        <v>180.363466675316</v>
+        <v>3483.352781434843</v>
       </c>
       <c r="D67">
-        <v>7063.959703001841</v>
+        <v>10366.94901776137</v>
       </c>
       <c r="E67">
         <v>2476.494334285717</v>
@@ -6775,45 +8534,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M67">
-        <v>944.128847335142</v>
+        <v>649.1336612693873</v>
       </c>
       <c r="N67">
-        <v>-127.4621806684753</v>
+        <v>167.5330053972795</v>
       </c>
       <c r="O67">
-        <v>-33.77747787714596</v>
+        <v>44.39624643027906</v>
       </c>
       <c r="P67">
-        <v>-93.68470279132934</v>
+        <v>123.1367589670004</v>
       </c>
       <c r="Q67">
-        <v>206.3152972086706</v>
+        <v>423.1367589670004</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1553795816509896</v>
+        <v>0.1523166760669983</v>
       </c>
       <c r="T67">
-        <v>2.529079254567363</v>
+        <v>2.459969424180099</v>
       </c>
       <c r="U67">
-        <v>0.1309</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
-        <v>0.2292236565777173</v>
+        <v>0.265</v>
       </c>
       <c r="W67">
-        <v>0.1008946233539768</v>
+        <v>0.06615</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8649949304819521</v>
+        <v>1.258087071112084</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +8583,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1208153587579313</v>
+        <v>0.111976748660716</v>
       </c>
       <c r="C68">
-        <v>-10.73553791910217</v>
+        <v>917.847463692442</v>
       </c>
       <c r="D68">
-        <v>6983.823717427832</v>
+        <v>7912.406719039377</v>
       </c>
       <c r="E68">
         <v>2587.457353306126</v>
@@ -6857,37 +8616,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M68">
-        <v>958.6539065249136</v>
+        <v>868.5741276841464</v>
       </c>
       <c r="N68">
-        <v>-141.9872398582469</v>
+        <v>-51.9074610174797</v>
       </c>
       <c r="O68">
-        <v>-37.62661856243543</v>
+        <v>-13.75547716963212</v>
       </c>
       <c r="P68">
-        <v>-104.3606212958115</v>
+        <v>-38.15198384784758</v>
       </c>
       <c r="Q68">
-        <v>195.6393787041885</v>
+        <v>261.8480161521524</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1586025105230776</v>
+        <v>0.1564830690606795</v>
       </c>
       <c r="T68">
-        <v>2.603463938525227</v>
+        <v>2.556190971378281</v>
       </c>
       <c r="U68">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.2257505708719943</v>
+        <v>0.2491631511563579</v>
       </c>
       <c r="W68">
-        <v>0.1013492502728559</v>
+        <v>0.08904925027285596</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +8654,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8518889466867708</v>
+        <v>0.9402383062504072</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +8665,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1216663587579313</v>
+        <v>0.112704748660716</v>
       </c>
       <c r="C69">
-        <v>-200.0367569115697</v>
+        <v>720.7884319559316</v>
       </c>
       <c r="D69">
-        <v>6905.485517455772</v>
+        <v>7826.310706323274</v>
       </c>
       <c r="E69">
         <v>2698.420372326534</v>
@@ -6939,37 +8698,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M69">
-        <v>973.178965714685</v>
+        <v>881.7343417399669</v>
       </c>
       <c r="N69">
-        <v>-156.5122990480182</v>
+        <v>-65.06767507330017</v>
       </c>
       <c r="O69">
-        <v>-41.47575924772483</v>
+        <v>-17.24293389442455</v>
       </c>
       <c r="P69">
-        <v>-115.0365398002934</v>
+        <v>-47.82474117887562</v>
       </c>
       <c r="Q69">
-        <v>184.9634601997066</v>
+        <v>252.1752588211244</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1620207684177162</v>
+        <v>0.1598371014564577</v>
       </c>
       <c r="T69">
-        <v>2.682356785147203</v>
+        <v>2.633651303844289</v>
       </c>
       <c r="U69">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.2223811593664421</v>
+        <v>0.2454442981540242</v>
       </c>
       <c r="W69">
-        <v>0.1017903062389327</v>
+        <v>0.08949030623893274</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +8736,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8391741862884609</v>
+        <v>0.9262048986944309</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +8747,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1225173587579313</v>
+        <v>0.113432748660716</v>
       </c>
       <c r="C70">
-        <v>-387.6000170051539</v>
+        <v>525.5828779649955</v>
       </c>
       <c r="D70">
-        <v>6828.885276382596</v>
+        <v>7742.068171352746</v>
       </c>
       <c r="E70">
         <v>2809.383391346942</v>
@@ -7021,37 +8780,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M70">
-        <v>987.7040249044564</v>
+        <v>894.8945557957873</v>
       </c>
       <c r="N70">
-        <v>-171.0373582377897</v>
+        <v>-78.22788912912051</v>
       </c>
       <c r="O70">
-        <v>-45.32489993301427</v>
+        <v>-20.73039061921694</v>
       </c>
       <c r="P70">
-        <v>-125.7124583047754</v>
+        <v>-57.49749850990358</v>
       </c>
       <c r="Q70">
-        <v>174.2875416952246</v>
+        <v>242.5025014900964</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1656526674307699</v>
+        <v>0.163400760876972</v>
       </c>
       <c r="T70">
-        <v>2.766180434683053</v>
+        <v>2.715952907089423</v>
       </c>
       <c r="U70">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2191108481992886</v>
+        <v>0.2418348231811709</v>
       </c>
       <c r="W70">
-        <v>0.1022183899707131</v>
+        <v>0.08991838997071314</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +8818,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8268333894312776</v>
+        <v>0.9125842384195129</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +8829,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1233683587579313</v>
+        <v>0.114160748660716</v>
       </c>
       <c r="C71">
-        <v>-573.4825194754749</v>
+        <v>332.1715865197448</v>
       </c>
       <c r="D71">
-        <v>6753.965792932683</v>
+        <v>7659.619898927903</v>
       </c>
       <c r="E71">
         <v>2920.34641036735</v>
@@ -7103,37 +8862,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M71">
-        <v>1002.229084094228</v>
+        <v>908.0547698516076</v>
       </c>
       <c r="N71">
-        <v>-185.5624174275611</v>
+        <v>-91.38810318494086</v>
       </c>
       <c r="O71">
-        <v>-49.17404061830369</v>
+        <v>-24.21784734400933</v>
       </c>
       <c r="P71">
-        <v>-136.3883768092574</v>
+        <v>-67.17025584093153</v>
       </c>
       <c r="Q71">
-        <v>163.6116231907426</v>
+        <v>232.8297441590685</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1695188825091818</v>
+        <v>0.1671943338084872</v>
       </c>
       <c r="T71">
-        <v>2.855412061608314</v>
+        <v>2.803564291189082</v>
       </c>
       <c r="U71">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.2159353286601685</v>
+        <v>0.2383299706712989</v>
       </c>
       <c r="W71">
-        <v>0.102634065478384</v>
+        <v>0.09033406547838396</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +8900,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8148502968308243</v>
+        <v>0.8993583798916939</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +8911,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1242193587579313</v>
+        <v>0.114888748660716</v>
       </c>
       <c r="C72">
-        <v>-757.7389826252556</v>
+        <v>140.4978382631862</v>
       </c>
       <c r="D72">
-        <v>6680.672348803311</v>
+        <v>7578.909169691753</v>
       </c>
       <c r="E72">
         <v>3031.309429387758</v>
@@ -7185,37 +8944,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M72">
-        <v>1016.754143283999</v>
+        <v>921.2149839074281</v>
       </c>
       <c r="N72">
-        <v>-200.0874766173325</v>
+        <v>-104.5483172407613</v>
       </c>
       <c r="O72">
-        <v>-53.02318130359312</v>
+        <v>-27.70530406880175</v>
       </c>
       <c r="P72">
-        <v>-147.0642953137394</v>
+        <v>-76.84301317195957</v>
       </c>
       <c r="Q72">
-        <v>152.9357046862606</v>
+        <v>223.1569868280404</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1736428452594879</v>
+        <v>0.1712408116021035</v>
       </c>
       <c r="T72">
-        <v>2.950592463661924</v>
+        <v>2.897016434228718</v>
       </c>
       <c r="U72">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.2128505382507375</v>
+        <v>0.234925256804566</v>
       </c>
       <c r="W72">
-        <v>0.1030378645429784</v>
+        <v>0.09073786454297848</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +8982,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8032095783046697</v>
+        <v>0.8865104030360982</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +8993,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1879911275510533</v>
+        <v>0.115616748660716</v>
       </c>
       <c r="C73">
-        <v>-3864.938825617121</v>
+        <v>-49.49272044326972</v>
       </c>
       <c r="D73">
-        <v>3684.435524831853</v>
+        <v>7499.881630005704</v>
       </c>
       <c r="E73">
         <v>3142.272448408165</v>
@@ -7267,45 +9026,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M73">
-        <v>1700.153184826889</v>
+        <v>934.3751979632484</v>
       </c>
       <c r="N73">
-        <v>-883.486518160222</v>
+        <v>-117.7085312965817</v>
       </c>
       <c r="O73">
-        <v>-234.1239273124588</v>
+        <v>-31.19276079359414</v>
       </c>
       <c r="P73">
-        <v>-649.3625908477632</v>
+        <v>-86.51577050298752</v>
       </c>
       <c r="Q73">
-        <v>-349.3625908477632</v>
+        <v>213.4842294970125</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1871607667964427</v>
+        <v>0.1755663568297622</v>
       </c>
       <c r="T73">
-        <v>3.262583935146731</v>
+        <v>2.996913552650398</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.1272924514085491</v>
+        <v>0.2316164503706989</v>
       </c>
       <c r="W73">
-        <v>0.1883302889860351</v>
+        <v>0.09113028898603512</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.4803488732398078</v>
+        <v>0.8740243410215053</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +9075,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1896911275510533</v>
+        <v>0.116344748660716</v>
       </c>
       <c r="C74">
-        <v>-4019.431563938615</v>
+        <v>-237.8521995872161</v>
       </c>
       <c r="D74">
-        <v>3640.905805530767</v>
+        <v>7422.485169882166</v>
       </c>
       <c r="E74">
         <v>3253.235467428573</v>
@@ -7349,45 +9108,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M74">
-        <v>1724.099004331493</v>
+        <v>947.5354120190688</v>
       </c>
       <c r="N74">
-        <v>-907.432337664826</v>
+        <v>-130.868745352402</v>
       </c>
       <c r="O74">
-        <v>-240.4695694811789</v>
+        <v>-34.68021751838653</v>
       </c>
       <c r="P74">
-        <v>-666.9627681836471</v>
+        <v>-96.18852783401547</v>
       </c>
       <c r="Q74">
-        <v>-366.9627681836471</v>
+        <v>203.8114721659845</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1922093656106014</v>
+        <v>0.1802008695736823</v>
       </c>
       <c r="T74">
-        <v>3.3791047899734</v>
+        <v>3.103946179530769</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.1255245006945415</v>
+        <v>0.2283995552266614</v>
       </c>
       <c r="W74">
-        <v>0.188711812750118</v>
+        <v>0.09151181275011797</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.4736773611114772</v>
+        <v>0.8618851140628734</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +9157,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1913911275510533</v>
+        <v>0.117072748660716</v>
       </c>
       <c r="C75">
-        <v>-4172.907749616323</v>
+        <v>-424.630580091678</v>
       </c>
       <c r="D75">
-        <v>3598.392638873467</v>
+        <v>7346.669808398112</v>
       </c>
       <c r="E75">
         <v>3364.198486448981</v>
@@ -7431,45 +9190,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M75">
-        <v>1748.044823836097</v>
+        <v>960.6956260748892</v>
       </c>
       <c r="N75">
-        <v>-931.3781571694301</v>
+        <v>-144.0289594082225</v>
       </c>
       <c r="O75">
-        <v>-246.815211649899</v>
+        <v>-38.16767424317896</v>
       </c>
       <c r="P75">
-        <v>-684.5629455195311</v>
+        <v>-105.8612851650435</v>
       </c>
       <c r="Q75">
-        <v>-384.5629455195311</v>
+        <v>194.1387148349565</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1976319347072903</v>
+        <v>0.1851786795578927</v>
       </c>
       <c r="T75">
-        <v>3.504256819231673</v>
+        <v>3.218907149143019</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.1238049869863971</v>
+        <v>0.2252707941961592</v>
       </c>
       <c r="W75">
-        <v>0.1890828838083355</v>
+        <v>0.09188288380833554</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.4671886301373473</v>
+        <v>0.8500784686647517</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +9239,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1930911275510533</v>
+        <v>0.117800748660716</v>
       </c>
       <c r="C76">
-        <v>-4325.402581094101</v>
+        <v>-609.8758214500285</v>
       </c>
       <c r="D76">
-        <v>3556.860826416097</v>
+        <v>7272.387586060169</v>
       </c>
       <c r="E76">
         <v>3475.161505469389</v>
@@ -7513,45 +9272,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M76">
-        <v>1771.990643340701</v>
+        <v>973.8558401307096</v>
       </c>
       <c r="N76">
-        <v>-955.3239766740342</v>
+        <v>-157.1891734640428</v>
       </c>
       <c r="O76">
-        <v>-253.1608538186191</v>
+        <v>-41.65513096797135</v>
       </c>
       <c r="P76">
-        <v>-702.1631228554151</v>
+        <v>-115.5340424960715</v>
       </c>
       <c r="Q76">
-        <v>-402.1631228554151</v>
+        <v>184.4659575039285</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2034716245037246</v>
+        <v>0.1905393980024271</v>
       </c>
       <c r="T76">
-        <v>3.639035927663661</v>
+        <v>3.342711270263905</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.122131946621716</v>
+        <v>0.2222265942745895</v>
       </c>
       <c r="W76">
-        <v>0.1894439259190337</v>
+        <v>0.09224392591903369</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.4608752702706265</v>
+        <v>0.8385909217909038</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +9321,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1947911275510533</v>
+        <v>0.118528748660716</v>
       </c>
       <c r="C77">
-        <v>-4476.949650348208</v>
+        <v>-793.633962896507</v>
       </c>
       <c r="D77">
-        <v>3516.276776182397</v>
+        <v>7199.592463634099</v>
       </c>
       <c r="E77">
         <v>3586.124524489797</v>
@@ -7595,45 +9354,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M77">
-        <v>1795.936462845305</v>
+        <v>987.0160541865299</v>
       </c>
       <c r="N77">
-        <v>-979.2697961786382</v>
+        <v>-170.3493875198632</v>
       </c>
       <c r="O77">
-        <v>-259.5064959873391</v>
+        <v>-45.14258769276374</v>
       </c>
       <c r="P77">
-        <v>-719.7633001912991</v>
+        <v>-125.2067998270994</v>
       </c>
       <c r="Q77">
-        <v>-419.7633001912991</v>
+        <v>174.7932001729006</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2097784894838736</v>
+        <v>0.1963289739225241</v>
       </c>
       <c r="T77">
-        <v>3.784597364770208</v>
+        <v>3.476419721074461</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.1205035206667598</v>
+        <v>0.219263573017595</v>
       </c>
       <c r="W77">
-        <v>0.1897953402401132</v>
+        <v>0.09259534024011323</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.4547302666670181</v>
+        <v>0.8274097095003584</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +9403,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1964911275510533</v>
+        <v>0.119256748660716</v>
       </c>
       <c r="C78">
-        <v>-4627.58103350296</v>
+        <v>-975.9492185607442</v>
       </c>
       <c r="D78">
-        <v>3476.608412048054</v>
+        <v>7128.24022699027</v>
       </c>
       <c r="E78">
         <v>3697.087543510205</v>
@@ -7677,45 +9436,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M78">
-        <v>1819.882282349909</v>
+        <v>1000.17626824235</v>
       </c>
       <c r="N78">
-        <v>-1003.215615683242</v>
+        <v>-183.5096015756836</v>
       </c>
       <c r="O78">
-        <v>-265.8521381560592</v>
+        <v>-48.63004441755616</v>
       </c>
       <c r="P78">
-        <v>-737.363477527183</v>
+        <v>-134.8795571581275</v>
       </c>
       <c r="Q78">
-        <v>-437.363477527183</v>
+        <v>165.1204428418725</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2166109265457016</v>
+        <v>0.2026010145026293</v>
       </c>
       <c r="T78">
-        <v>3.942288921635634</v>
+        <v>3.621270542785897</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V78">
-        <v>0.1189179480264077</v>
+        <v>0.2163785260042056</v>
       </c>
       <c r="W78">
-        <v>0.1901375068159012</v>
+        <v>0.09293750681590122</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.4487469736845573</v>
+        <v>0.8165227396385115</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +9485,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1981911275510533</v>
+        <v>0.119984748660716</v>
       </c>
       <c r="C79">
-        <v>-4777.327375381203</v>
+        <v>-1156.864067019606</v>
       </c>
       <c r="D79">
-        <v>3437.825089190219</v>
+        <v>7058.288397551815</v>
       </c>
       <c r="E79">
         <v>3808.050562530613</v>
@@ -7759,45 +9518,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M79">
-        <v>1843.828101854513</v>
+        <v>1013.336482298171</v>
       </c>
       <c r="N79">
-        <v>-1027.161435187846</v>
+        <v>-196.669815631504</v>
       </c>
       <c r="O79">
-        <v>-272.1977803247792</v>
+        <v>-52.11750114234856</v>
       </c>
       <c r="P79">
-        <v>-754.9636548630669</v>
+        <v>-144.5523144891554</v>
       </c>
       <c r="Q79">
-        <v>-454.9636548630669</v>
+        <v>155.4476855108446</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2240374885694278</v>
+        <v>0.2094184499157871</v>
       </c>
       <c r="T79">
-        <v>4.113692787793704</v>
+        <v>3.778717088124415</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.1186</v>
       </c>
       <c r="V79">
-        <v>0.1173735590909998</v>
+        <v>0.2135684152768782</v>
       </c>
       <c r="W79">
-        <v>0.1904707859481623</v>
+        <v>0.09327078594816225</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4429190909094333</v>
+        <v>0.8059185482146348</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +9567,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1998911275510533</v>
+        <v>0.1878607006484145</v>
       </c>
       <c r="C80">
-        <v>-4926.217968457988</v>
+        <v>-4640.244948269557</v>
       </c>
       <c r="D80">
-        <v>3399.897515133843</v>
+        <v>3685.870535322275</v>
       </c>
       <c r="E80">
         <v>3919.013581551023</v>
@@ -7841,37 +9600,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M80">
-        <v>1867.773921359117</v>
+        <v>1737.94718910524</v>
       </c>
       <c r="N80">
-        <v>-1051.107254692451</v>
+        <v>-921.2805224385731</v>
       </c>
       <c r="O80">
-        <v>-278.5434224934994</v>
+        <v>-244.1393384462219</v>
       </c>
       <c r="P80">
-        <v>-772.5638321989512</v>
+        <v>-677.1411839923512</v>
       </c>
       <c r="Q80">
-        <v>-472.5638321989512</v>
+        <v>-377.1411839923512</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2321391925953109</v>
+        <v>0.2306372521287709</v>
       </c>
       <c r="T80">
-        <v>4.300678823602509</v>
+        <v>4.268758709671384</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1158687698718844</v>
+        <v>0.1245243054698837</v>
       </c>
       <c r="W80">
-        <v>0.1907955194616474</v>
+        <v>0.1757955194616474</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +9638,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4372406410259789</v>
+        <v>0.4699030395089953</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +9649,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2015911275510534</v>
+        <v>0.1894107006484145</v>
       </c>
       <c r="C81">
-        <v>-5074.280826644998</v>
+        <v>-4790.989817137883</v>
       </c>
       <c r="D81">
-        <v>3362.797675967241</v>
+        <v>3646.088685474357</v>
       </c>
       <c r="E81">
         <v>4029.976600571431</v>
@@ -7923,37 +9682,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M81">
-        <v>1891.719740863721</v>
+        <v>1760.228563324538</v>
       </c>
       <c r="N81">
-        <v>-1075.053074197055</v>
+        <v>-943.5618966578709</v>
       </c>
       <c r="O81">
-        <v>-284.8890646622195</v>
+        <v>-250.0439026143358</v>
       </c>
       <c r="P81">
-        <v>-790.1640095348353</v>
+        <v>-693.5179940435351</v>
       </c>
       <c r="Q81">
-        <v>-490.1640095348353</v>
+        <v>-393.5179940435351</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2410124874808019</v>
+        <v>0.2394390260396647</v>
       </c>
       <c r="T81">
-        <v>4.505473053297868</v>
+        <v>4.47203293394145</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1144020765823669</v>
+        <v>0.1229480484386194</v>
       </c>
       <c r="W81">
-        <v>0.1911120318735252</v>
+        <v>0.1761120318735252</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +9720,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4317059493674222</v>
+        <v>0.4639548997683751</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +9731,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2032911275510533</v>
+        <v>0.1909607006484145</v>
       </c>
       <c r="C82">
-        <v>-5221.54275429625</v>
+        <v>-4940.885119050567</v>
       </c>
       <c r="D82">
-        <v>3326.498767336397</v>
+        <v>3607.15640258208</v>
       </c>
       <c r="E82">
         <v>4140.939619591839</v>
@@ -8005,37 +9764,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M82">
-        <v>1915.665560368325</v>
+        <v>1782.509937543836</v>
       </c>
       <c r="N82">
-        <v>-1098.998893701659</v>
+        <v>-965.8432708771688</v>
       </c>
       <c r="O82">
-        <v>-291.2347068309396</v>
+        <v>-255.9484667824497</v>
       </c>
       <c r="P82">
-        <v>-807.7641868707192</v>
+        <v>-709.8948040947191</v>
       </c>
       <c r="Q82">
-        <v>-507.7641868707192</v>
+        <v>-409.8948040947191</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.250773111854842</v>
+        <v>0.249120977341648</v>
       </c>
       <c r="T82">
-        <v>4.730746705962761</v>
+        <v>4.695634580638522</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1129720506250873</v>
+        <v>0.1214111978331367</v>
       </c>
       <c r="W82">
-        <v>0.1914206314751062</v>
+        <v>0.1764206314751061</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +9802,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4263096250003294</v>
+        <v>0.4581554635212705</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +9813,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2049911275510533</v>
+        <v>0.1925107006484145</v>
       </c>
       <c r="C83">
-        <v>-5368.02941079236</v>
+        <v>-5089.95778105742</v>
       </c>
       <c r="D83">
-        <v>3290.975129860695</v>
+        <v>3569.046759595635</v>
       </c>
       <c r="E83">
         <v>4251.902638612247</v>
@@ -8087,37 +9846,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M83">
-        <v>1939.61137987293</v>
+        <v>1804.791311763134</v>
       </c>
       <c r="N83">
-        <v>-1122.944713206263</v>
+        <v>-988.1246450964668</v>
       </c>
       <c r="O83">
-        <v>-297.5803489996596</v>
+        <v>-261.8530309505637</v>
       </c>
       <c r="P83">
-        <v>-825.3643642066031</v>
+        <v>-726.2716141459031</v>
       </c>
       <c r="Q83">
-        <v>-525.3643642066031</v>
+        <v>-426.2716141459031</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2615611703735178</v>
+        <v>0.259822081412261</v>
       </c>
       <c r="T83">
-        <v>4.979733374697643</v>
+        <v>4.942773242777393</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1115773339507035</v>
+        <v>0.1199122941561843</v>
       </c>
       <c r="W83">
-        <v>0.1917216113334382</v>
+        <v>0.1767216113334382</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +9884,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4210465432102019</v>
+        <v>0.4524992232308843</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +9895,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2066911275510533</v>
+        <v>0.1940607006484145</v>
       </c>
       <c r="C84">
-        <v>-5513.76537103035</v>
+        <v>-5238.2336041667</v>
       </c>
       <c r="D84">
-        <v>3256.202188643113</v>
+        <v>3531.733955506763</v>
       </c>
       <c r="E84">
         <v>4362.865657632655</v>
@@ -8169,37 +9928,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M84">
-        <v>1963.557199377534</v>
+        <v>1827.072685982431</v>
       </c>
       <c r="N84">
-        <v>-1146.890532710867</v>
+        <v>-1010.406019315765</v>
       </c>
       <c r="O84">
-        <v>-303.9259911683797</v>
+        <v>-267.7575951186777</v>
       </c>
       <c r="P84">
-        <v>-842.9645415424872</v>
+        <v>-742.648424197087</v>
       </c>
       <c r="Q84">
-        <v>-542.9645415424872</v>
+        <v>-442.648424197087</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2735479020609355</v>
+        <v>0.2717121970462755</v>
       </c>
       <c r="T84">
-        <v>5.256385228847513</v>
+        <v>5.217371756265025</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1102166347561827</v>
+        <v>0.1184499491054992</v>
       </c>
       <c r="W84">
-        <v>0.1920152502196158</v>
+        <v>0.1770152502196158</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +9966,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.415911829268614</v>
+        <v>0.4469809400207516</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +9977,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2083911275510534</v>
+        <v>0.1956107006484145</v>
       </c>
       <c r="C85">
-        <v>-5658.774182118687</v>
+        <v>-5385.737321597448</v>
       </c>
       <c r="D85">
-        <v>3222.156396575184</v>
+        <v>3495.193257096423</v>
       </c>
       <c r="E85">
         <v>4473.828676653063</v>
@@ -8251,37 +10010,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M85">
-        <v>1987.503018882138</v>
+        <v>1849.354060201729</v>
       </c>
       <c r="N85">
-        <v>-1170.836352215471</v>
+        <v>-1032.687393535063</v>
       </c>
       <c r="O85">
-        <v>-310.2716333370998</v>
+        <v>-273.6621592867916</v>
       </c>
       <c r="P85">
-        <v>-860.5647188783712</v>
+        <v>-759.0252342482711</v>
       </c>
       <c r="Q85">
-        <v>-560.5647188783712</v>
+        <v>-459.0252342482711</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2869448374762847</v>
+        <v>0.2850011498137035</v>
       </c>
       <c r="T85">
-        <v>5.56558435995619</v>
+        <v>5.524275977221792</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.10888872349406</v>
+        <v>0.117022841284951</v>
       </c>
       <c r="W85">
-        <v>0.1923018134699818</v>
+        <v>0.1773018134699818</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +10048,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4109008433738115</v>
+        <v>0.4415956274903811</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +10059,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2100911275510533</v>
+        <v>0.1971607006484145</v>
       </c>
       <c r="C86">
-        <v>-5803.07841655242</v>
+        <v>-5532.492653452636</v>
       </c>
       <c r="D86">
-        <v>3188.815181161859</v>
+        <v>3459.400944261643</v>
       </c>
       <c r="E86">
         <v>4584.791695673471</v>
@@ -8333,37 +10092,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M86">
-        <v>2011.448838386742</v>
+        <v>1871.635434421027</v>
       </c>
       <c r="N86">
-        <v>-1194.782171720075</v>
+        <v>-1054.968767754361</v>
       </c>
       <c r="O86">
-        <v>-316.6172755058199</v>
+        <v>-279.5667234549056</v>
       </c>
       <c r="P86">
-        <v>-878.1648962142551</v>
+        <v>-775.4020442994552</v>
       </c>
       <c r="Q86">
-        <v>-578.1648962142551</v>
+        <v>-475.4020442994552</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3020163898185524</v>
+        <v>0.2999512216770598</v>
       </c>
       <c r="T86">
-        <v>5.913433382453449</v>
+        <v>5.86954322579815</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1075924291667498</v>
+        <v>0.1156297122220349</v>
       </c>
       <c r="W86">
-        <v>0.1925815537858154</v>
+        <v>0.1775815537858154</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +10130,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4060091666669804</v>
+        <v>0.4363385366869241</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +10141,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2117911275510533</v>
+        <v>0.1987107006484145</v>
       </c>
       <c r="C87">
-        <v>-5946.699722120752</v>
+        <v>-5678.522358067105</v>
       </c>
       <c r="D87">
-        <v>3156.156894613935</v>
+        <v>3424.334258667583</v>
       </c>
       <c r="E87">
         <v>4695.754714693879</v>
@@ -8415,37 +10174,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M87">
-        <v>2035.394657891346</v>
+        <v>1893.916808640325</v>
       </c>
       <c r="N87">
-        <v>-1218.727991224679</v>
+        <v>-1077.250141973658</v>
       </c>
       <c r="O87">
-        <v>-322.9629176745399</v>
+        <v>-285.4712876230195</v>
       </c>
       <c r="P87">
-        <v>-895.7650735501389</v>
+        <v>-791.778854350639</v>
       </c>
       <c r="Q87">
-        <v>-595.7650735501389</v>
+        <v>-491.778854350639</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3190974824731226</v>
+        <v>0.3168946364555305</v>
       </c>
       <c r="T87">
-        <v>6.307662274617013</v>
+        <v>6.260846107518027</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1063266358824351</v>
+        <v>0.1142693626664816</v>
       </c>
       <c r="W87">
-        <v>0.1928547119765705</v>
+        <v>0.1778547119765705</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +10212,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4012325882356043</v>
+        <v>0.4312051421376663</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +10223,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2134911275510533</v>
+        <v>0.2002607006484145</v>
       </c>
       <c r="C88">
-        <v>-6089.658868778921</v>
+        <v>-5823.848280263877</v>
       </c>
       <c r="D88">
-        <v>3124.160766976174</v>
+        <v>3389.971355491218</v>
       </c>
       <c r="E88">
         <v>4806.717733714287</v>
@@ -8497,37 +10256,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M88">
-        <v>2059.34047739595</v>
+        <v>1916.198182859623</v>
       </c>
       <c r="N88">
-        <v>-1242.673810729283</v>
+        <v>-1099.531516192956</v>
       </c>
       <c r="O88">
-        <v>-329.30855984326</v>
+        <v>-291.3758517911335</v>
       </c>
       <c r="P88">
-        <v>-913.365250886023</v>
+        <v>-808.1556644018228</v>
       </c>
       <c r="Q88">
-        <v>-613.365250886023</v>
+        <v>-508.1556644018228</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3386187312212027</v>
+        <v>0.336258539059497</v>
       </c>
       <c r="T88">
-        <v>6.758209579946799</v>
+        <v>6.708049400912173</v>
       </c>
       <c r="U88">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.105090279651244</v>
+        <v>0.1129406491471039</v>
       </c>
       <c r="W88">
-        <v>0.1931215176512615</v>
+        <v>0.1781215176512616</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +10294,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3965670930235623</v>
+        <v>0.4261911288569957</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +10305,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2151911275510533</v>
+        <v>0.2018107006484145</v>
       </c>
       <c r="C89">
-        <v>-6231.975792697676</v>
+        <v>-5968.491396733835</v>
       </c>
       <c r="D89">
-        <v>3092.806862077827</v>
+        <v>3356.291258041668</v>
       </c>
       <c r="E89">
         <v>4917.680752734695</v>
@@ -8579,37 +10338,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M89">
-        <v>2083.286296900554</v>
+        <v>1938.479557078921</v>
       </c>
       <c r="N89">
-        <v>-1266.619630233887</v>
+        <v>-1121.812890412254</v>
       </c>
       <c r="O89">
-        <v>-335.65420201198</v>
+        <v>-297.2804159592474</v>
       </c>
       <c r="P89">
-        <v>-930.9654282219069</v>
+        <v>-824.5324744530069</v>
       </c>
       <c r="Q89">
-        <v>-630.9654282219069</v>
+        <v>-524.5324744530069</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3611432490074491</v>
+        <v>0.3586015036025352</v>
       </c>
       <c r="T89">
-        <v>7.278071855327322</v>
+        <v>7.224053200982339</v>
       </c>
       <c r="U89">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1038823454023791</v>
+        <v>0.1116424807661027</v>
       </c>
       <c r="W89">
-        <v>0.1933821898621666</v>
+        <v>0.1783821898621666</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +10376,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3920088505750156</v>
+        <v>0.421292380249444</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +10387,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2168911275510534</v>
+        <v>0.2033607006484145</v>
       </c>
       <c r="C90">
-        <v>-6373.669637686623</v>
+        <v>-6112.471858736889</v>
       </c>
       <c r="D90">
-        <v>3062.076036109288</v>
+        <v>3323.273815059022</v>
       </c>
       <c r="E90">
         <v>5028.643771755103</v>
@@ -8661,37 +10420,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M90">
-        <v>2107.232116405158</v>
+        <v>1960.760931298219</v>
       </c>
       <c r="N90">
-        <v>-1290.565449738491</v>
+        <v>-1144.094264631552</v>
       </c>
       <c r="O90">
-        <v>-341.9998441807001</v>
+        <v>-303.1849801273614</v>
       </c>
       <c r="P90">
-        <v>-948.5656055577908</v>
+        <v>-840.909284504191</v>
       </c>
       <c r="Q90">
-        <v>-648.5656055577908</v>
+        <v>-540.909284504191</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3874218530914033</v>
+        <v>0.3846682955694132</v>
       </c>
       <c r="T90">
-        <v>7.884577843271268</v>
+        <v>7.826057634397536</v>
       </c>
       <c r="U90">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1027018642046248</v>
+        <v>0.1103738162119424</v>
       </c>
       <c r="W90">
-        <v>0.193636937704642</v>
+        <v>0.178636937704642</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +10458,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3875542045457541</v>
+        <v>0.4165049668375186</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +10469,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2185911275510533</v>
+        <v>0.2049107006484145</v>
       </c>
       <c r="C91">
-        <v>-6514.758794172322</v>
+        <v>-6255.80903230724</v>
       </c>
       <c r="D91">
-        <v>3031.949898643997</v>
+        <v>3290.899660509079</v>
       </c>
       <c r="E91">
         <v>5139.60679077551</v>
@@ -8743,37 +10502,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M91">
-        <v>2131.177935909762</v>
+        <v>1983.042305517517</v>
       </c>
       <c r="N91">
-        <v>-1314.511269243095</v>
+        <v>-1166.37563885085</v>
       </c>
       <c r="O91">
-        <v>-348.3454863494202</v>
+        <v>-309.0895442954753</v>
       </c>
       <c r="P91">
-        <v>-966.1657828936749</v>
+        <v>-857.2860945553749</v>
       </c>
       <c r="Q91">
-        <v>-666.1657828936749</v>
+        <v>-557.2860945553749</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4184783851906217</v>
+        <v>0.4154745042575418</v>
       </c>
       <c r="T91">
-        <v>8.601357647205019</v>
+        <v>8.537517419342768</v>
       </c>
       <c r="U91">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1015479106742358</v>
+        <v>0.109133660973606</v>
       </c>
       <c r="W91">
-        <v>0.1938859608764999</v>
+        <v>0.1788859608764999</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +10540,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3831996629216444</v>
+        <v>0.4118251357494566</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +10551,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2202911275510533</v>
+        <v>0.2064607006484145</v>
       </c>
       <c r="C92">
-        <v>-6655.260935897904</v>
+        <v>-6398.521536131349</v>
       </c>
       <c r="D92">
-        <v>3002.410775938823</v>
+        <v>3259.150175705377</v>
       </c>
       <c r="E92">
         <v>5250.569809795918</v>
@@ -8825,37 +10584,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M92">
-        <v>2155.123755414366</v>
+        <v>2005.323679736815</v>
       </c>
       <c r="N92">
-        <v>-1338.457088747699</v>
+        <v>-1188.657013070148</v>
       </c>
       <c r="O92">
-        <v>-354.6911285181403</v>
+        <v>-314.9941084635892</v>
       </c>
       <c r="P92">
-        <v>-983.7659602295589</v>
+        <v>-873.6629046065588</v>
       </c>
       <c r="Q92">
-        <v>-683.7659602295589</v>
+        <v>-573.6629046065588</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.455746223709684</v>
+        <v>0.452441954683296</v>
       </c>
       <c r="T92">
-        <v>9.461493411925522</v>
+        <v>9.391269161277044</v>
       </c>
       <c r="U92">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1004196005556332</v>
+        <v>0.1079210647405659</v>
       </c>
       <c r="W92">
-        <v>0.1941294502000944</v>
+        <v>0.1791294502000944</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +10622,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3789418888891818</v>
+        <v>0.407249300907796</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +10633,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2219911275510533</v>
+        <v>0.2080107006484145</v>
       </c>
       <c r="C93">
-        <v>-6795.19305449807</v>
+        <v>-6540.627277254247</v>
       </c>
       <c r="D93">
-        <v>2973.441676359067</v>
+        <v>3228.007453602889</v>
       </c>
       <c r="E93">
         <v>5361.532828816328</v>
@@ -8907,37 +10666,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M93">
-        <v>2179.06957491897</v>
+        <v>2027.605053956113</v>
       </c>
       <c r="N93">
-        <v>-1362.402908252304</v>
+        <v>-1210.938387289446</v>
       </c>
       <c r="O93">
-        <v>-361.0367706868605</v>
+        <v>-320.8986726317033</v>
       </c>
       <c r="P93">
-        <v>-1001.366137565443</v>
+        <v>-890.039714657743</v>
       </c>
       <c r="Q93">
-        <v>-701.3661375654431</v>
+        <v>-590.039714657743</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.501295804121871</v>
+        <v>0.497624394092551</v>
       </c>
       <c r="T93">
-        <v>10.51277045769502</v>
+        <v>10.43474351253005</v>
       </c>
       <c r="U93">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.0993160884616152</v>
+        <v>0.1067351189741861</v>
       </c>
       <c r="W93">
-        <v>0.1943675881099834</v>
+        <v>0.1793675881099834</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +10704,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3747776923079819</v>
+        <v>0.4027740338648531</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +10715,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2236911275510534</v>
+        <v>0.2095607006484145</v>
       </c>
       <c r="C94">
-        <v>-6934.571492091614</v>
+        <v>-6682.143484758053</v>
       </c>
       <c r="D94">
-        <v>2945.02625778593</v>
+        <v>3197.454265119491</v>
       </c>
       <c r="E94">
         <v>5472.495847836736</v>
@@ -8989,37 +10748,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M94">
-        <v>2203.015394423574</v>
+        <v>2049.886428175411</v>
       </c>
       <c r="N94">
-        <v>-1386.348727756908</v>
+        <v>-1233.219761508744</v>
       </c>
       <c r="O94">
-        <v>-367.3824128555806</v>
+        <v>-326.8032367998172</v>
       </c>
       <c r="P94">
-        <v>-1018.966314901327</v>
+        <v>-906.4165247089269</v>
       </c>
       <c r="Q94">
-        <v>-718.9663149013271</v>
+        <v>-606.4165247089269</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5582327796371052</v>
+        <v>0.5541024433541201</v>
       </c>
       <c r="T94">
-        <v>11.82686676490691</v>
+        <v>11.73908645159631</v>
       </c>
       <c r="U94">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09823656576094547</v>
+        <v>0.1055749546375102</v>
       </c>
       <c r="W94">
-        <v>0.194600549108788</v>
+        <v>0.1796005491087879</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +10786,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3707040217394169</v>
+        <v>0.3983960552358873</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +10797,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2253911275510533</v>
+        <v>0.2111107006484145</v>
       </c>
       <c r="C95">
-        <v>-7073.41197202285</v>
+        <v>-6823.086741545863</v>
       </c>
       <c r="D95">
-        <v>2917.148796875102</v>
+        <v>3167.474027352089</v>
       </c>
       <c r="E95">
         <v>5583.458866857144</v>
@@ -9071,37 +10830,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M95">
-        <v>2226.961213928178</v>
+        <v>2072.167802394709</v>
       </c>
       <c r="N95">
-        <v>-1410.294547261512</v>
+        <v>-1255.501135728042</v>
       </c>
       <c r="O95">
-        <v>-373.7280550243007</v>
+        <v>-332.7078009679312</v>
       </c>
       <c r="P95">
-        <v>-1036.566492237211</v>
+        <v>-922.7933347601108</v>
       </c>
       <c r="Q95">
-        <v>-736.5664922372112</v>
+        <v>-622.7933347601108</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.631437462442406</v>
+        <v>0.6267170781189944</v>
       </c>
       <c r="T95">
-        <v>13.51641915989361</v>
+        <v>13.41609880182435</v>
       </c>
       <c r="U95">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09718025860222562</v>
+        <v>0.1044397400715154</v>
       </c>
       <c r="W95">
-        <v>0.1948285001936397</v>
+        <v>0.1798285001936397</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +10868,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3667179569895307</v>
+        <v>0.3941122266849638</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +10879,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2270911275510533</v>
+        <v>0.2126607006484145</v>
       </c>
       <c r="C96">
-        <v>-7211.72962787341</v>
+        <v>-6963.473014354116</v>
       </c>
       <c r="D96">
-        <v>2889.794160044951</v>
+        <v>3138.050773564245</v>
       </c>
       <c r="E96">
         <v>5694.421885877552</v>
@@ -9153,37 +10912,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M96">
-        <v>2250.907033432783</v>
+        <v>2094.449176614007</v>
       </c>
       <c r="N96">
-        <v>-1434.240366766116</v>
+        <v>-1277.78250994734</v>
       </c>
       <c r="O96">
-        <v>-380.0736971930207</v>
+        <v>-338.6123651360451</v>
       </c>
       <c r="P96">
-        <v>-1054.166669573095</v>
+        <v>-939.1701448112949</v>
       </c>
       <c r="Q96">
-        <v>-754.1666695730951</v>
+        <v>-639.1701448112949</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.729043706182807</v>
+        <v>0.7235365911388271</v>
       </c>
       <c r="T96">
-        <v>15.76915568654255</v>
+        <v>15.65211526879509</v>
       </c>
       <c r="U96">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09614642606390408</v>
+        <v>0.1033286790069248</v>
       </c>
       <c r="W96">
-        <v>0.1950516012554095</v>
+        <v>0.1800516012554095</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +10950,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3628167021279399</v>
+        <v>0.3899195434223578</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +10961,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2287911275510534</v>
+        <v>0.2142107006484145</v>
       </c>
       <c r="C97">
-        <v>-7349.53903085692</v>
+        <v>-7103.317682107634</v>
       </c>
       <c r="D97">
-        <v>2862.947776081849</v>
+        <v>3109.169124831134</v>
       </c>
       <c r="E97">
         <v>5805.38490489796</v>
@@ -9235,37 +10994,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M97">
-        <v>2274.852852937387</v>
+        <v>2116.730550833305</v>
       </c>
       <c r="N97">
-        <v>-1458.18618627072</v>
+        <v>-1300.063884166638</v>
       </c>
       <c r="O97">
-        <v>-386.4193393617408</v>
+        <v>-344.5169293041591</v>
       </c>
       <c r="P97">
-        <v>-1071.766846908979</v>
+        <v>-955.546954862479</v>
       </c>
       <c r="Q97">
-        <v>-771.766846908979</v>
+        <v>-655.546954862479</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8656924474193688</v>
+        <v>0.8590839093665927</v>
       </c>
       <c r="T97">
-        <v>18.92298682385107</v>
+        <v>18.78253832255411</v>
       </c>
       <c r="U97">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.09513435842112614</v>
+        <v>0.1022410087015888</v>
       </c>
       <c r="W97">
-        <v>0.195270005452721</v>
+        <v>0.180270005452721</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +11032,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3589975789476458</v>
+        <v>0.3858151271758067</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +11043,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2304911275510534</v>
+        <v>0.2157607006484145</v>
       </c>
       <c r="C98">
-        <v>-7486.854215700743</v>
+        <v>-7242.63556272312</v>
       </c>
       <c r="D98">
-        <v>2836.595610258433</v>
+        <v>3080.814263236057</v>
       </c>
       <c r="E98">
         <v>5916.347923918368</v>
@@ -9317,37 +11076,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M98">
-        <v>2298.798672441991</v>
+        <v>2139.011925052603</v>
       </c>
       <c r="N98">
-        <v>-1482.132005775324</v>
+        <v>-1322.345258385936</v>
       </c>
       <c r="O98">
-        <v>-392.7649815304609</v>
+        <v>-350.421493472273</v>
       </c>
       <c r="P98">
-        <v>-1089.367024244863</v>
+        <v>-971.9237649136629</v>
       </c>
       <c r="Q98">
-        <v>-789.3670242448629</v>
+        <v>-671.9237649136629</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.070665559274209</v>
+        <v>1.062404886708239</v>
       </c>
       <c r="T98">
-        <v>23.65373352981378</v>
+        <v>23.47817290319259</v>
       </c>
       <c r="U98">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.09414337552090607</v>
+        <v>0.1011759981942806</v>
       </c>
       <c r="W98">
-        <v>0.1954838595625885</v>
+        <v>0.1804838595625885</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +11114,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3552580208336078</v>
+        <v>0.3817962196010587</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +11125,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2321911275510534</v>
+        <v>0.2173107006484145</v>
       </c>
       <c r="C99">
-        <v>-7623.688705111386</v>
+        <v>-7381.440938459247</v>
       </c>
       <c r="D99">
-        <v>2810.724139868199</v>
+        <v>3052.971906520337</v>
       </c>
       <c r="E99">
         <v>6027.310942938776</v>
@@ -9399,37 +11158,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M99">
-        <v>2322.744491946595</v>
+        <v>2161.293299271901</v>
       </c>
       <c r="N99">
-        <v>-1506.077825279928</v>
+        <v>-1344.626632605234</v>
       </c>
       <c r="O99">
-        <v>-399.110623699181</v>
+        <v>-356.326057640387</v>
       </c>
       <c r="P99">
-        <v>-1106.967201580747</v>
+        <v>-988.3005749648469</v>
       </c>
       <c r="Q99">
-        <v>-806.9672015807471</v>
+        <v>-688.3005749648469</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.412287412365612</v>
+        <v>1.401273182277652</v>
       </c>
       <c r="T99">
-        <v>31.53831137308505</v>
+        <v>31.30423053759012</v>
       </c>
       <c r="U99">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.09317282525780395</v>
+        <v>0.1001329466665045</v>
       </c>
       <c r="W99">
-        <v>0.1956933043093659</v>
+        <v>0.1806933043093659</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +11196,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3515955670105809</v>
+        <v>0.3778601761000169</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +11207,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2338911275510533</v>
+        <v>0.2188607006484145</v>
       </c>
       <c r="C100">
-        <v>-7760.055532913146</v>
+        <v>-7519.747579904482</v>
       </c>
       <c r="D100">
-        <v>2785.320331086847</v>
+        <v>3025.62828409551</v>
       </c>
       <c r="E100">
         <v>6138.273961959184</v>
@@ -9481,37 +11240,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M100">
-        <v>2346.690311451198</v>
+        <v>2183.574673491199</v>
       </c>
       <c r="N100">
-        <v>-1530.023644784532</v>
+        <v>-1366.908006824532</v>
       </c>
       <c r="O100">
-        <v>-405.4562658679009</v>
+        <v>-362.230621808501</v>
       </c>
       <c r="P100">
-        <v>-1124.567378916631</v>
+        <v>-1004.677385016031</v>
       </c>
       <c r="Q100">
-        <v>-824.5673789166308</v>
+        <v>-704.6773850160309</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.095531118548418</v>
+        <v>2.079009773416477</v>
       </c>
       <c r="T100">
-        <v>47.30746705962756</v>
+        <v>46.95634580638517</v>
       </c>
       <c r="U100">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09222208214292842</v>
+        <v>0.09911118190460136</v>
       </c>
       <c r="W100">
-        <v>0.1958984746735561</v>
+        <v>0.180898474673556</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,7 +11278,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3480078571431261</v>
+        <v>0.3740044600173635</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +11289,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2355911275510534</v>
+        <v>0.2204107006484145</v>
       </c>
       <c r="C101">
-        <v>-7895.967265943244</v>
+        <v>-7657.568768687297</v>
       </c>
       <c r="D101">
-        <v>2760.371617077157</v>
+        <v>2998.770114333103</v>
       </c>
       <c r="E101">
         <v>6249.236980979592</v>
@@ -9563,37 +11322,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M101">
-        <v>2370.636130955802</v>
+        <v>2205.856047710497</v>
       </c>
       <c r="N101">
-        <v>-1553.969464289136</v>
+        <v>-1389.18938104383</v>
       </c>
       <c r="O101">
-        <v>-411.8019080366209</v>
+        <v>-368.1351859766149</v>
       </c>
       <c r="P101">
-        <v>-1142.167556252515</v>
+        <v>-1021.054195067215</v>
       </c>
       <c r="Q101">
-        <v>-842.1675562525147</v>
+        <v>-721.0541950672149</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.145262237096835</v>
+        <v>4.112219546832955</v>
       </c>
       <c r="T101">
-        <v>94.61493411925512</v>
+        <v>93.91269161277035</v>
       </c>
       <c r="U101">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V101">
-        <v>0.09129054595966651</v>
+        <v>0.09811005885505993</v>
       </c>
       <c r="W101">
-        <v>0.196099500181904</v>
+        <v>0.181099500181904</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9601,7 +11360,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3444926262628926</v>
+        <v>0.3702266371889054</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/canada/canada_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_healthcare_products.xlsx
@@ -3031,7 +3031,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3168,22 +3168,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09083876366469271</v>
+        <v>0.09063111594098126</v>
       </c>
       <c r="C2">
-        <v>11954.92638300392</v>
+        <v>11897.81206033641</v>
       </c>
       <c r="D2">
-        <v>11625.92638300392</v>
+        <v>11679.77507935682</v>
       </c>
       <c r="E2">
-        <v>-4736.101902040808</v>
+        <v>-4625.1388830204</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>110.9630190204081</v>
       </c>
       <c r="G2">
         <v>329</v>
@@ -3204,28 +3204,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.581439856726526</v>
       </c>
       <c r="N2">
-        <v>816.6666666666667</v>
+        <v>811.0852268099402</v>
       </c>
       <c r="O2">
-        <v>216.4166666666667</v>
+        <v>214.9375851046342</v>
       </c>
       <c r="P2">
-        <v>600.25</v>
+        <v>596.147641705306</v>
       </c>
       <c r="Q2">
-        <v>900.25</v>
+        <v>896.147641705306</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09083876366469271</v>
+        <v>0.09117314236462754</v>
       </c>
       <c r="T2">
-        <v>1.040156204727314</v>
+        <v>1.04787857655029</v>
       </c>
       <c r="U2">
         <v>0.05029999999999999</v>
@@ -3242,7 +3242,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>146.3182776541886</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09063111594098126</v>
+        <v>0.09042346821726982</v>
       </c>
       <c r="C3">
-        <v>11897.81206033641</v>
+        <v>11841.19888917815</v>
       </c>
       <c r="D3">
-        <v>11679.77507935682</v>
+        <v>11734.12492721897</v>
       </c>
       <c r="E3">
-        <v>-4625.1388830204</v>
+        <v>-4514.175863999993</v>
       </c>
       <c r="F3">
-        <v>110.9630190204081</v>
+        <v>221.9260380408162</v>
       </c>
       <c r="G3">
         <v>329</v>
@@ -3286,28 +3286,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M3">
-        <v>5.581439856726526</v>
+        <v>11.16287971345305</v>
       </c>
       <c r="N3">
-        <v>811.0852268099402</v>
+        <v>805.5037869532136</v>
       </c>
       <c r="O3">
-        <v>214.9375851046342</v>
+        <v>213.4585035426016</v>
       </c>
       <c r="P3">
-        <v>596.147641705306</v>
+        <v>592.045283410612</v>
       </c>
       <c r="Q3">
-        <v>896.147641705306</v>
+        <v>892.045283410612</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09117314236462754</v>
+        <v>0.09151434511966308</v>
       </c>
       <c r="T3">
-        <v>1.04787857655029</v>
+        <v>1.055758547798224</v>
       </c>
       <c r="U3">
         <v>0.05029999999999999</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.3182776541886</v>
+        <v>73.15913882709432</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09042346821726982</v>
+        <v>0.09021582049355839</v>
       </c>
       <c r="C4">
-        <v>11841.19888917815</v>
+        <v>11785.09389830643</v>
       </c>
       <c r="D4">
-        <v>11734.12492721897</v>
+        <v>11788.98295536765</v>
       </c>
       <c r="E4">
-        <v>-4514.175863999993</v>
+        <v>-4403.212844979585</v>
       </c>
       <c r="F4">
-        <v>221.9260380408162</v>
+        <v>332.8890570612243</v>
       </c>
       <c r="G4">
         <v>329</v>
@@ -3368,28 +3368,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M4">
-        <v>11.16287971345305</v>
+        <v>16.74431957017958</v>
       </c>
       <c r="N4">
-        <v>805.5037869532136</v>
+        <v>799.9223470964872</v>
       </c>
       <c r="O4">
-        <v>213.4585035426016</v>
+        <v>211.9794219805691</v>
       </c>
       <c r="P4">
-        <v>592.045283410612</v>
+        <v>587.9429251159181</v>
       </c>
       <c r="Q4">
-        <v>892.045283410612</v>
+        <v>887.9429251159181</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09151434511966308</v>
+        <v>0.09186258298304989</v>
       </c>
       <c r="T4">
-        <v>1.055758547798224</v>
+        <v>1.063800992680136</v>
       </c>
       <c r="U4">
         <v>0.05029999999999999</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.15913882709432</v>
+        <v>48.77275921806289</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09021582049355839</v>
+        <v>0.09000817276984695</v>
       </c>
       <c r="C5">
-        <v>11785.09389830643</v>
+        <v>11729.50424855644</v>
       </c>
       <c r="D5">
-        <v>11788.98295536765</v>
+        <v>11844.35632463807</v>
       </c>
       <c r="E5">
-        <v>-4403.212844979585</v>
+        <v>-4292.249825959176</v>
       </c>
       <c r="F5">
-        <v>332.8890570612243</v>
+        <v>443.8520760816323</v>
       </c>
       <c r="G5">
         <v>329</v>
@@ -3450,28 +3450,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M5">
-        <v>16.74431957017958</v>
+        <v>22.3257594269061</v>
       </c>
       <c r="N5">
-        <v>799.9223470964872</v>
+        <v>794.3409072397607</v>
       </c>
       <c r="O5">
-        <v>211.9794219805691</v>
+        <v>210.5003404185366</v>
       </c>
       <c r="P5">
-        <v>587.9429251159181</v>
+        <v>583.8405668212241</v>
       </c>
       <c r="Q5">
-        <v>887.9429251159181</v>
+        <v>883.8405668212241</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09186258298304989</v>
+        <v>0.0922180758019239</v>
       </c>
       <c r="T5">
-        <v>1.063800992680136</v>
+        <v>1.072010988497088</v>
       </c>
       <c r="U5">
         <v>0.05029999999999999</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.77275921806289</v>
+        <v>36.57956941354716</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09000817276984695</v>
+        <v>0.08980052504613553</v>
       </c>
       <c r="C6">
-        <v>11729.50424855644</v>
+        <v>11674.4372359373</v>
       </c>
       <c r="D6">
-        <v>11844.35632463807</v>
+        <v>11900.25233103934</v>
       </c>
       <c r="E6">
-        <v>-4292.249825959176</v>
+        <v>-4181.286806938768</v>
       </c>
       <c r="F6">
-        <v>443.8520760816323</v>
+        <v>554.8150951020405</v>
       </c>
       <c r="G6">
         <v>329</v>
@@ -3532,28 +3532,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M6">
-        <v>22.3257594269061</v>
+        <v>27.90719928363263</v>
       </c>
       <c r="N6">
-        <v>794.3409072397607</v>
+        <v>788.7594673830341</v>
       </c>
       <c r="O6">
-        <v>210.5003404185366</v>
+        <v>209.0212588565041</v>
       </c>
       <c r="P6">
-        <v>583.8405668212241</v>
+        <v>579.7382085265301</v>
       </c>
       <c r="Q6">
-        <v>883.8405668212241</v>
+        <v>879.7382085265301</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0922180758019239</v>
+        <v>0.09258105268014266</v>
       </c>
       <c r="T6">
-        <v>1.072010988497088</v>
+        <v>1.080393826331239</v>
       </c>
       <c r="U6">
         <v>0.05029999999999999</v>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.57956941354716</v>
+        <v>29.26365553083773</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08980052504613553</v>
+        <v>0.08959287732242409</v>
       </c>
       <c r="C7">
-        <v>11674.4372359373</v>
+        <v>11619.9002948368</v>
       </c>
       <c r="D7">
-        <v>11900.25233103934</v>
+        <v>11956.67840895925</v>
       </c>
       <c r="E7">
-        <v>-4181.286806938768</v>
+        <v>-4070.32378791836</v>
       </c>
       <c r="F7">
-        <v>554.8150951020405</v>
+        <v>665.7781141224485</v>
       </c>
       <c r="G7">
         <v>329</v>
@@ -3614,28 +3614,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M7">
-        <v>27.90719928363263</v>
+        <v>33.48863914035915</v>
       </c>
       <c r="N7">
-        <v>788.7594673830341</v>
+        <v>783.1780275263076</v>
       </c>
       <c r="O7">
-        <v>209.0212588565041</v>
+        <v>207.5421772944715</v>
       </c>
       <c r="P7">
-        <v>579.7382085265301</v>
+        <v>575.635850231836</v>
       </c>
       <c r="Q7">
-        <v>879.7382085265301</v>
+        <v>875.635850231836</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09258105268014266</v>
+        <v>0.09295175247066392</v>
       </c>
       <c r="T7">
-        <v>1.080393826331239</v>
+        <v>1.088955022417181</v>
       </c>
       <c r="U7">
         <v>0.05029999999999999</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.26365553083773</v>
+        <v>24.38637960903144</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08959287732242409</v>
+        <v>0.08938522959871266</v>
       </c>
       <c r="C8">
-        <v>11619.9002948368</v>
+        <v>11565.90100131764</v>
       </c>
       <c r="D8">
-        <v>11956.67840895925</v>
+        <v>12013.6421344605</v>
       </c>
       <c r="E8">
-        <v>-4070.32378791836</v>
+        <v>-3959.360768897952</v>
       </c>
       <c r="F8">
-        <v>665.7781141224485</v>
+        <v>776.7411331428565</v>
       </c>
       <c r="G8">
         <v>329</v>
@@ -3696,28 +3696,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M8">
-        <v>33.48863914035915</v>
+        <v>39.07007899708567</v>
       </c>
       <c r="N8">
-        <v>783.1780275263076</v>
+        <v>777.596587669581</v>
       </c>
       <c r="O8">
-        <v>207.5421772944715</v>
+        <v>206.063095732439</v>
       </c>
       <c r="P8">
-        <v>575.635850231836</v>
+        <v>571.533491937142</v>
       </c>
       <c r="Q8">
-        <v>875.635850231836</v>
+        <v>871.533491937142</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09295175247066392</v>
+        <v>0.09333042429969103</v>
       </c>
       <c r="T8">
-        <v>1.088955022417181</v>
+        <v>1.097700330246906</v>
       </c>
       <c r="U8">
         <v>0.05029999999999999</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.38637960903144</v>
+        <v>20.90261109345553</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08938522959871266</v>
+        <v>0.08917758187500122</v>
       </c>
       <c r="C9">
-        <v>11565.90100131764</v>
+        <v>11512.44707650846</v>
       </c>
       <c r="D9">
-        <v>12013.6421344605</v>
+        <v>12071.15122867172</v>
       </c>
       <c r="E9">
-        <v>-3959.360768897952</v>
+        <v>-3848.397749877544</v>
       </c>
       <c r="F9">
-        <v>776.7411331428566</v>
+        <v>887.7041521632647</v>
       </c>
       <c r="G9">
         <v>329</v>
@@ -3778,28 +3778,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M9">
-        <v>39.07007899708568</v>
+        <v>44.65151885381221</v>
       </c>
       <c r="N9">
-        <v>777.596587669581</v>
+        <v>772.0151478128546</v>
       </c>
       <c r="O9">
-        <v>206.063095732439</v>
+        <v>204.5840141704065</v>
       </c>
       <c r="P9">
-        <v>571.533491937142</v>
+        <v>567.4311336424481</v>
       </c>
       <c r="Q9">
-        <v>871.533491937142</v>
+        <v>867.4311336424481</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09333042429969103</v>
+        <v>0.09371732812500132</v>
       </c>
       <c r="T9">
-        <v>1.097700330246906</v>
+        <v>1.106635753464234</v>
       </c>
       <c r="U9">
         <v>0.05029999999999999</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.90261109345552</v>
+        <v>18.28978470677358</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08917758187500122</v>
+        <v>0.08896993415128977</v>
       </c>
       <c r="C10">
-        <v>11512.44707650846</v>
+        <v>11459.54639009264</v>
       </c>
       <c r="D10">
-        <v>12071.15122867172</v>
+        <v>12129.21356127631</v>
       </c>
       <c r="E10">
-        <v>-3848.397749877544</v>
+        <v>-3737.434730857136</v>
       </c>
       <c r="F10">
-        <v>887.7041521632647</v>
+        <v>998.6671711836727</v>
       </c>
       <c r="G10">
         <v>329</v>
@@ -3860,28 +3860,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M10">
-        <v>44.65151885381221</v>
+        <v>50.23295871053873</v>
       </c>
       <c r="N10">
-        <v>772.0151478128546</v>
+        <v>766.433707956128</v>
       </c>
       <c r="O10">
-        <v>204.5840141704065</v>
+        <v>203.1049326083739</v>
       </c>
       <c r="P10">
-        <v>567.4311336424481</v>
+        <v>563.3287753477541</v>
       </c>
       <c r="Q10">
-        <v>867.4311336424481</v>
+        <v>863.3287753477541</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09371732812500132</v>
+        <v>0.09411273533108766</v>
       </c>
       <c r="T10">
-        <v>1.106635753464234</v>
+        <v>1.115767559609415</v>
       </c>
       <c r="U10">
         <v>0.05029999999999999</v>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.28978470677358</v>
+        <v>16.25758640602096</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08896993415128977</v>
+        <v>0.08876228642757833</v>
       </c>
       <c r="C11">
-        <v>11459.54639009264</v>
+        <v>11407.20696389833</v>
       </c>
       <c r="D11">
-        <v>12129.21356127631</v>
+        <v>12187.83715410242</v>
       </c>
       <c r="E11">
-        <v>-3737.434730857136</v>
+        <v>-3626.471711836728</v>
       </c>
       <c r="F11">
-        <v>998.6671711836727</v>
+        <v>1109.630190204081</v>
       </c>
       <c r="G11">
         <v>329</v>
@@ -3942,28 +3942,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M11">
-        <v>50.23295871053873</v>
+        <v>55.81439856726525</v>
       </c>
       <c r="N11">
-        <v>766.433707956128</v>
+        <v>760.8522680994015</v>
       </c>
       <c r="O11">
-        <v>203.1049326083739</v>
+        <v>201.6258510463414</v>
       </c>
       <c r="P11">
-        <v>563.3287753477541</v>
+        <v>559.2264170530601</v>
       </c>
       <c r="Q11">
-        <v>863.3287753477541</v>
+        <v>859.2264170530601</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09411273533108766</v>
+        <v>0.09451692936397593</v>
       </c>
       <c r="T11">
-        <v>1.115767559609415</v>
+        <v>1.125102294780045</v>
       </c>
       <c r="U11">
         <v>0.05029999999999999</v>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.25758640602096</v>
+        <v>14.63182776541887</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08876228642757833</v>
+        <v>0.08855463870386691</v>
       </c>
       <c r="C12">
-        <v>11407.20696389833</v>
+        <v>11355.43697559311</v>
       </c>
       <c r="D12">
-        <v>12187.83715410242</v>
+        <v>12247.0301848176</v>
       </c>
       <c r="E12">
-        <v>-3626.471711836728</v>
+        <v>-3515.50869281632</v>
       </c>
       <c r="F12">
-        <v>1109.630190204081</v>
+        <v>1220.593209224489</v>
       </c>
       <c r="G12">
         <v>329</v>
@@ -4024,28 +4024,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M12">
-        <v>55.81439856726526</v>
+        <v>61.39583842399178</v>
       </c>
       <c r="N12">
-        <v>760.8522680994015</v>
+        <v>755.270828242675</v>
       </c>
       <c r="O12">
-        <v>201.6258510463414</v>
+        <v>200.1467694843089</v>
       </c>
       <c r="P12">
-        <v>559.2264170530601</v>
+        <v>555.1240587583661</v>
       </c>
       <c r="Q12">
-        <v>859.2264170530601</v>
+        <v>855.1240587583661</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09451692936397593</v>
+        <v>0.09493020640883923</v>
       </c>
       <c r="T12">
-        <v>1.125102294780045</v>
+        <v>1.134646799280352</v>
       </c>
       <c r="U12">
         <v>0.05029999999999999</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.63182776541887</v>
+        <v>13.30166160492624</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08855463870386691</v>
+        <v>0.08834699098015547</v>
       </c>
       <c r="C13">
-        <v>11355.43697559311</v>
+        <v>11304.24476248678</v>
       </c>
       <c r="D13">
-        <v>12247.0301848176</v>
+        <v>12306.80099073168</v>
       </c>
       <c r="E13">
-        <v>-3515.50869281632</v>
+        <v>-3404.545673795911</v>
       </c>
       <c r="F13">
-        <v>1220.593209224489</v>
+        <v>1331.556228244897</v>
       </c>
       <c r="G13">
         <v>329</v>
@@ -4106,28 +4106,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M13">
-        <v>61.39583842399178</v>
+        <v>66.97727828071831</v>
       </c>
       <c r="N13">
-        <v>755.270828242675</v>
+        <v>749.6893883859484</v>
       </c>
       <c r="O13">
-        <v>200.1467694843089</v>
+        <v>198.6676879222763</v>
       </c>
       <c r="P13">
-        <v>555.1240587583661</v>
+        <v>551.021700463672</v>
       </c>
       <c r="Q13">
-        <v>855.1240587583661</v>
+        <v>851.021700463672</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09493020640883923</v>
+        <v>0.09535287611381303</v>
       </c>
       <c r="T13">
-        <v>1.134646799280352</v>
+        <v>1.144408224337484</v>
       </c>
       <c r="U13">
         <v>0.05029999999999999</v>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.30166160492624</v>
+        <v>12.19318980451572</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08834699098015547</v>
+        <v>0.08813934325644404</v>
       </c>
       <c r="C14">
-        <v>11304.24476248678</v>
+        <v>11253.63882544605</v>
       </c>
       <c r="D14">
-        <v>12306.80099073168</v>
+        <v>12367.15807271136</v>
       </c>
       <c r="E14">
-        <v>-3404.545673795911</v>
+        <v>-3293.582654775503</v>
       </c>
       <c r="F14">
-        <v>1331.556228244897</v>
+        <v>1442.519247265305</v>
       </c>
       <c r="G14">
         <v>329</v>
@@ -4188,28 +4188,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M14">
-        <v>66.97727828071831</v>
+        <v>72.55871813744483</v>
       </c>
       <c r="N14">
-        <v>749.6893883859484</v>
+        <v>744.1079485292219</v>
       </c>
       <c r="O14">
-        <v>198.6676879222763</v>
+        <v>197.1886063602438</v>
       </c>
       <c r="P14">
-        <v>551.021700463672</v>
+        <v>546.9193421689781</v>
       </c>
       <c r="Q14">
-        <v>851.021700463672</v>
+        <v>846.9193421689781</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09535287611381303</v>
+        <v>0.09578526236372878</v>
       </c>
       <c r="T14">
-        <v>1.144408224337484</v>
+        <v>1.154394049970642</v>
       </c>
       <c r="U14">
         <v>0.05029999999999999</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.19318980451572</v>
+        <v>11.25525212724528</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08813934325644404</v>
+        <v>0.0879316955327326</v>
       </c>
       <c r="C15">
-        <v>11253.63882544605</v>
+        <v>11203.6278329251</v>
       </c>
       <c r="D15">
-        <v>12367.15807271136</v>
+        <v>12428.11009921081</v>
       </c>
       <c r="E15">
-        <v>-3293.582654775503</v>
+        <v>-3182.619635755095</v>
       </c>
       <c r="F15">
-        <v>1442.519247265305</v>
+        <v>1553.482266285713</v>
       </c>
       <c r="G15">
         <v>329</v>
@@ -4270,28 +4270,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M15">
-        <v>72.55871813744483</v>
+        <v>78.14015799417136</v>
       </c>
       <c r="N15">
-        <v>744.1079485292219</v>
+        <v>738.5265086724954</v>
       </c>
       <c r="O15">
-        <v>197.1886063602438</v>
+        <v>195.7095247982113</v>
       </c>
       <c r="P15">
-        <v>546.9193421689781</v>
+        <v>542.8169838742841</v>
       </c>
       <c r="Q15">
-        <v>846.9193421689781</v>
+        <v>842.8169838742841</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09578526236372878</v>
+        <v>0.0962277041078286</v>
       </c>
       <c r="T15">
-        <v>1.154394049970642</v>
+        <v>1.164612104106896</v>
       </c>
       <c r="U15">
         <v>0.05029999999999999</v>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.25525212724528</v>
+        <v>10.45130554672776</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0879316955327326</v>
+        <v>0.08772404780902116</v>
       </c>
       <c r="C16">
-        <v>11203.6278329251</v>
+        <v>11154.22062511577</v>
       </c>
       <c r="D16">
-        <v>12428.11009921081</v>
+        <v>12489.66591042189</v>
       </c>
       <c r="E16">
-        <v>-3182.619635755095</v>
+        <v>-3071.656616734687</v>
       </c>
       <c r="F16">
-        <v>1553.482266285713</v>
+        <v>1664.445285306121</v>
       </c>
       <c r="G16">
         <v>329</v>
@@ -4352,28 +4352,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M16">
-        <v>78.14015799417136</v>
+        <v>83.72159785089789</v>
       </c>
       <c r="N16">
-        <v>738.5265086724954</v>
+        <v>732.9450688157689</v>
       </c>
       <c r="O16">
-        <v>195.7095247982113</v>
+        <v>194.2304432361788</v>
       </c>
       <c r="P16">
-        <v>542.8169838742841</v>
+        <v>538.7146255795901</v>
       </c>
       <c r="Q16">
-        <v>842.8169838742841</v>
+        <v>838.7146255795901</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0962277041078286</v>
+        <v>0.09668055624590724</v>
       </c>
       <c r="T16">
-        <v>1.164612104106896</v>
+        <v>1.175070583046357</v>
       </c>
       <c r="U16">
         <v>0.05029999999999999</v>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.45130554672776</v>
+        <v>9.754551843612576</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08772404780902116</v>
+        <v>0.08751640008530971</v>
       </c>
       <c r="C17">
-        <v>11154.22062511577</v>
+        <v>11105.42621822182</v>
       </c>
       <c r="D17">
-        <v>12489.66591042189</v>
+        <v>12551.83452254835</v>
       </c>
       <c r="E17">
-        <v>-3071.656616734687</v>
+        <v>-2960.693597714279</v>
       </c>
       <c r="F17">
-        <v>1664.445285306121</v>
+        <v>1775.408304326529</v>
       </c>
       <c r="G17">
         <v>329</v>
@@ -4434,28 +4434,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M17">
-        <v>83.72159785089788</v>
+        <v>89.30303770762441</v>
       </c>
       <c r="N17">
-        <v>732.9450688157689</v>
+        <v>727.3636289590423</v>
       </c>
       <c r="O17">
-        <v>194.2304432361788</v>
+        <v>192.7513616741462</v>
       </c>
       <c r="P17">
-        <v>538.7146255795901</v>
+        <v>534.6122672848961</v>
       </c>
       <c r="Q17">
-        <v>838.7146255795901</v>
+        <v>834.6122672848961</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09668055624590724</v>
+        <v>0.09714419057774967</v>
       </c>
       <c r="T17">
-        <v>1.175070583046357</v>
+        <v>1.185778073389138</v>
       </c>
       <c r="U17">
         <v>0.05029999999999999</v>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.754551843612578</v>
+        <v>9.144892353386791</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08751640008530971</v>
+        <v>0.0874961773615983</v>
       </c>
       <c r="C18">
-        <v>11105.42621822182</v>
+        <v>11000.55086233224</v>
       </c>
       <c r="D18">
-        <v>12551.83452254835</v>
+        <v>12557.92218567918</v>
       </c>
       <c r="E18">
-        <v>-2960.693597714279</v>
+        <v>-2849.730578693871</v>
       </c>
       <c r="F18">
-        <v>1775.408304326529</v>
+        <v>1886.371323346938</v>
       </c>
       <c r="G18">
         <v>329</v>
@@ -4516,45 +4516,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M18">
-        <v>89.30303770762441</v>
+        <v>97.71403454937135</v>
       </c>
       <c r="N18">
-        <v>727.3636289590423</v>
+        <v>718.9526321172954</v>
       </c>
       <c r="O18">
-        <v>192.7513616741462</v>
+        <v>190.5224475110833</v>
       </c>
       <c r="P18">
-        <v>534.6122672848961</v>
+        <v>528.4301846062122</v>
       </c>
       <c r="Q18">
-        <v>834.6122672848961</v>
+        <v>828.4301846062122</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09714419057774967</v>
+        <v>0.09761899682120277</v>
       </c>
       <c r="T18">
-        <v>1.185778073389138</v>
+        <v>1.196743575547408</v>
       </c>
       <c r="U18">
-        <v>0.05029999999999999</v>
+        <v>0.05179999999999999</v>
       </c>
       <c r="V18">
         <v>0.265</v>
       </c>
       <c r="W18">
-        <v>0.03697049999999999</v>
+        <v>0.038073</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.144892353386791</v>
+        <v>8.357721287764807</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0874961773615983</v>
+        <v>0.08729955463788686</v>
       </c>
       <c r="C19">
-        <v>11000.55086233224</v>
+        <v>10949.08662313851</v>
       </c>
       <c r="D19">
-        <v>12557.92218567918</v>
+        <v>12617.42096550585</v>
       </c>
       <c r="E19">
-        <v>-2849.730578693871</v>
+        <v>-2738.767559673463</v>
       </c>
       <c r="F19">
-        <v>1886.371323346938</v>
+        <v>1997.334342367346</v>
       </c>
       <c r="G19">
         <v>329</v>
@@ -4598,28 +4598,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M19">
-        <v>97.71403454937135</v>
+        <v>103.4619189346285</v>
       </c>
       <c r="N19">
-        <v>718.9526321172954</v>
+        <v>713.2047477320383</v>
       </c>
       <c r="O19">
-        <v>190.5224475110833</v>
+        <v>188.9992581489902</v>
       </c>
       <c r="P19">
-        <v>528.4301846062122</v>
+        <v>524.2054895830481</v>
       </c>
       <c r="Q19">
-        <v>828.4301846062122</v>
+        <v>824.2054895830481</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09761899682120277</v>
+        <v>0.09810538370474008</v>
       </c>
       <c r="T19">
-        <v>1.196743575547408</v>
+        <v>1.207976528977831</v>
       </c>
       <c r="U19">
         <v>0.05179999999999999</v>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.357721287764807</v>
+        <v>7.89340343844454</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08729955463788686</v>
+        <v>0.08710293191417542</v>
       </c>
       <c r="C20">
-        <v>10949.08662313851</v>
+        <v>10898.18887216266</v>
       </c>
       <c r="D20">
-        <v>12617.42096550585</v>
+        <v>12677.48623355042</v>
       </c>
       <c r="E20">
-        <v>-2738.767559673463</v>
+        <v>-2627.804540653055</v>
       </c>
       <c r="F20">
-        <v>1997.334342367345</v>
+        <v>2108.297361387753</v>
       </c>
       <c r="G20">
         <v>329</v>
@@ -4680,28 +4680,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M20">
-        <v>103.4619189346285</v>
+        <v>109.2098033198856</v>
       </c>
       <c r="N20">
-        <v>713.2047477320383</v>
+        <v>707.4568633467811</v>
       </c>
       <c r="O20">
-        <v>188.9992581489902</v>
+        <v>187.476068786897</v>
       </c>
       <c r="P20">
-        <v>524.2054895830481</v>
+        <v>519.9807945598841</v>
       </c>
       <c r="Q20">
-        <v>824.2054895830481</v>
+        <v>819.9807945598841</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09810538370474008</v>
+        <v>0.0986037801409573</v>
       </c>
       <c r="T20">
-        <v>1.207976528977831</v>
+        <v>1.219486839283079</v>
       </c>
       <c r="U20">
         <v>0.05179999999999999</v>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.89340343844454</v>
+        <v>7.477961152210618</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08710293191417542</v>
+        <v>0.08690630919046401</v>
       </c>
       <c r="C21">
-        <v>10898.18887216266</v>
+        <v>10847.86573840914</v>
       </c>
       <c r="D21">
-        <v>12677.48623355042</v>
+        <v>12738.1261188173</v>
       </c>
       <c r="E21">
-        <v>-2627.804540653055</v>
+        <v>-2516.841521632647</v>
       </c>
       <c r="F21">
-        <v>2108.297361387753</v>
+        <v>2219.260380408162</v>
       </c>
       <c r="G21">
         <v>329</v>
@@ -4762,28 +4762,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M21">
-        <v>109.2098033198856</v>
+        <v>114.9576877051428</v>
       </c>
       <c r="N21">
-        <v>707.4568633467811</v>
+        <v>701.7089789615239</v>
       </c>
       <c r="O21">
-        <v>187.476068786897</v>
+        <v>185.9528794248039</v>
       </c>
       <c r="P21">
-        <v>519.9807945598841</v>
+        <v>515.7560995367201</v>
       </c>
       <c r="Q21">
-        <v>819.9807945598841</v>
+        <v>815.7560995367201</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0986037801409573</v>
+        <v>0.09911463648808</v>
       </c>
       <c r="T21">
-        <v>1.219486839283079</v>
+        <v>1.231284907345958</v>
       </c>
       <c r="U21">
         <v>0.05179999999999999</v>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.477961152210618</v>
+        <v>7.104063094600086</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08690630919046401</v>
+        <v>0.08670968646675255</v>
       </c>
       <c r="C22">
-        <v>10847.86573840914</v>
+        <v>10798.1255071629</v>
       </c>
       <c r="D22">
-        <v>12738.1261188173</v>
+        <v>12799.34890659147</v>
       </c>
       <c r="E22">
-        <v>-2516.841521632647</v>
+        <v>-2405.878502612239</v>
       </c>
       <c r="F22">
-        <v>2219.260380408162</v>
+        <v>2330.22339942857</v>
       </c>
       <c r="G22">
         <v>329</v>
@@ -4844,28 +4844,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M22">
-        <v>114.9576877051428</v>
+        <v>120.7055720903999</v>
       </c>
       <c r="N22">
-        <v>701.7089789615239</v>
+        <v>695.9610945762669</v>
       </c>
       <c r="O22">
-        <v>185.9528794248039</v>
+        <v>184.4296900627107</v>
       </c>
       <c r="P22">
-        <v>515.7560995367201</v>
+        <v>511.5314045135561</v>
       </c>
       <c r="Q22">
-        <v>815.7560995367201</v>
+        <v>811.5314045135561</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09911463648808</v>
+        <v>0.09963842590728171</v>
       </c>
       <c r="T22">
-        <v>1.231284907345958</v>
+        <v>1.243381660676252</v>
       </c>
       <c r="U22">
         <v>0.05179999999999999</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.104063094600086</v>
+        <v>6.765774375809606</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08670968646675255</v>
+        <v>0.08678795374304112</v>
       </c>
       <c r="C23">
-        <v>10798.1255071629</v>
+        <v>10662.7218882661</v>
       </c>
       <c r="D23">
-        <v>12799.34890659147</v>
+        <v>12774.90830671508</v>
       </c>
       <c r="E23">
-        <v>-2405.878502612239</v>
+        <v>-2294.915483591831</v>
       </c>
       <c r="F23">
-        <v>2330.22339942857</v>
+        <v>2441.186418448978</v>
       </c>
       <c r="G23">
         <v>329</v>
@@ -4926,45 +4926,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M23">
-        <v>120.7055720903999</v>
+        <v>130.6034733870203</v>
       </c>
       <c r="N23">
-        <v>695.9610945762669</v>
+        <v>686.0631932796464</v>
       </c>
       <c r="O23">
-        <v>184.4296900627107</v>
+        <v>181.8067462191063</v>
       </c>
       <c r="P23">
-        <v>511.5314045135561</v>
+        <v>504.2564470605401</v>
       </c>
       <c r="Q23">
-        <v>811.5314045135561</v>
+        <v>804.25644706054</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09963842590728171</v>
+        <v>0.1001756458244117</v>
       </c>
       <c r="T23">
-        <v>1.243381660676252</v>
+        <v>1.255788587168861</v>
       </c>
       <c r="U23">
-        <v>0.05179999999999999</v>
+        <v>0.05349999999999999</v>
       </c>
       <c r="V23">
         <v>0.265</v>
       </c>
       <c r="W23">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.765774375809606</v>
+        <v>6.253024100259719</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08678795374304112</v>
+        <v>0.08660382601932969</v>
       </c>
       <c r="C24">
-        <v>10662.7218882661</v>
+        <v>10609.40578662112</v>
       </c>
       <c r="D24">
-        <v>12774.90830671508</v>
+        <v>12832.5552240905</v>
       </c>
       <c r="E24">
-        <v>-2294.915483591831</v>
+        <v>-2183.952464571422</v>
       </c>
       <c r="F24">
-        <v>2441.186418448978</v>
+        <v>2552.149437469386</v>
       </c>
       <c r="G24">
         <v>329</v>
@@ -5008,28 +5008,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M24">
-        <v>130.6034733870203</v>
+        <v>136.5399949046121</v>
       </c>
       <c r="N24">
-        <v>686.0631932796464</v>
+        <v>680.1266717620546</v>
       </c>
       <c r="O24">
-        <v>181.8067462191063</v>
+        <v>180.2335680169445</v>
       </c>
       <c r="P24">
-        <v>504.2564470605401</v>
+        <v>499.8931037451101</v>
       </c>
       <c r="Q24">
-        <v>804.25644706054</v>
+        <v>799.8931037451101</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1001756458244117</v>
+        <v>0.100726819505623</v>
       </c>
       <c r="T24">
-        <v>1.255788587168861</v>
+        <v>1.268517771492447</v>
       </c>
       <c r="U24">
         <v>0.05349999999999999</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.253024100259719</v>
+        <v>5.981153487204947</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08660382601932969</v>
+        <v>0.08641969829561826</v>
       </c>
       <c r="C25">
-        <v>10609.40578662112</v>
+        <v>10556.61230804429</v>
       </c>
       <c r="D25">
-        <v>12832.5552240905</v>
+        <v>12890.72476453408</v>
       </c>
       <c r="E25">
-        <v>-2183.952464571422</v>
+        <v>-2072.989445551014</v>
       </c>
       <c r="F25">
-        <v>2552.149437469386</v>
+        <v>2663.112456489794</v>
       </c>
       <c r="G25">
         <v>329</v>
@@ -5090,28 +5090,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M25">
-        <v>136.5399949046121</v>
+        <v>142.476516422204</v>
       </c>
       <c r="N25">
-        <v>680.1266717620546</v>
+        <v>674.1901502444628</v>
       </c>
       <c r="O25">
-        <v>180.2335680169445</v>
+        <v>178.6603898147826</v>
       </c>
       <c r="P25">
-        <v>499.8931037451101</v>
+        <v>495.5297604296801</v>
       </c>
       <c r="Q25">
-        <v>799.8931037451101</v>
+        <v>795.5297604296801</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.100726819505623</v>
+        <v>0.1012924977573924</v>
       </c>
       <c r="T25">
-        <v>1.268517771492447</v>
+        <v>1.281581934350865</v>
       </c>
       <c r="U25">
         <v>0.05349999999999999</v>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.981153487204947</v>
+        <v>5.731938758571409</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08641969829561826</v>
+        <v>0.08638257057190681</v>
       </c>
       <c r="C26">
-        <v>10556.61230804429</v>
+        <v>10457.44260967246</v>
       </c>
       <c r="D26">
-        <v>12890.72476453408</v>
+        <v>12902.51808518266</v>
       </c>
       <c r="E26">
-        <v>-2072.989445551014</v>
+        <v>-1962.026426530606</v>
       </c>
       <c r="F26">
-        <v>2663.112456489794</v>
+        <v>2774.075475510202</v>
       </c>
       <c r="G26">
         <v>329</v>
@@ -5172,45 +5172,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M26">
-        <v>142.476516422204</v>
+        <v>150.6322983202039</v>
       </c>
       <c r="N26">
-        <v>674.1901502444628</v>
+        <v>666.0343683464628</v>
       </c>
       <c r="O26">
-        <v>178.6603898147826</v>
+        <v>176.4991076118126</v>
       </c>
       <c r="P26">
-        <v>495.5297604296801</v>
+        <v>489.5352607346501</v>
       </c>
       <c r="Q26">
-        <v>795.5297604296801</v>
+        <v>789.5352607346501</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1012924977573924</v>
+        <v>0.1018732607625424</v>
       </c>
       <c r="T26">
-        <v>1.281581934350865</v>
+        <v>1.294994474885506</v>
       </c>
       <c r="U26">
-        <v>0.05349999999999999</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="V26">
         <v>0.265</v>
       </c>
       <c r="W26">
-        <v>0.0393225</v>
+        <v>0.03991049999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.731938758571409</v>
+        <v>5.421590693190195</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08638257057190681</v>
+        <v>0.08620432284819537</v>
       </c>
       <c r="C27">
-        <v>10457.44260967246</v>
+        <v>10403.40034359896</v>
       </c>
       <c r="D27">
-        <v>12902.51808518266</v>
+        <v>12959.43883812957</v>
       </c>
       <c r="E27">
-        <v>-1962.026426530606</v>
+        <v>-1851.063407510198</v>
       </c>
       <c r="F27">
-        <v>2774.075475510202</v>
+        <v>2885.03849453061</v>
       </c>
       <c r="G27">
         <v>329</v>
@@ -5254,28 +5254,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M27">
-        <v>150.6322983202039</v>
+        <v>156.6575902530121</v>
       </c>
       <c r="N27">
-        <v>666.0343683464628</v>
+        <v>660.0090764136546</v>
       </c>
       <c r="O27">
-        <v>176.4991076118126</v>
+        <v>174.9024052496185</v>
       </c>
       <c r="P27">
-        <v>489.5352607346501</v>
+        <v>485.1066711640361</v>
       </c>
       <c r="Q27">
-        <v>789.5352607346501</v>
+        <v>785.1066711640361</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1018732607625424</v>
+        <v>0.1024697200651289</v>
       </c>
       <c r="T27">
-        <v>1.294994474885506</v>
+        <v>1.308769516515679</v>
       </c>
       <c r="U27">
         <v>0.05429999999999999</v>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.421590693190195</v>
+        <v>5.213067974221341</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08620432284819537</v>
+        <v>0.08602607512448393</v>
       </c>
       <c r="C28">
-        <v>10403.40034359896</v>
+        <v>10349.86252617542</v>
       </c>
       <c r="D28">
-        <v>12959.43883812957</v>
+        <v>13016.86403972644</v>
       </c>
       <c r="E28">
-        <v>-1851.063407510198</v>
+        <v>-1740.10038848979</v>
       </c>
       <c r="F28">
-        <v>2885.03849453061</v>
+        <v>2996.001513551018</v>
       </c>
       <c r="G28">
         <v>329</v>
@@ -5336,28 +5336,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M28">
-        <v>156.6575902530121</v>
+        <v>162.6828821858203</v>
       </c>
       <c r="N28">
-        <v>660.0090764136546</v>
+        <v>653.9837844808465</v>
       </c>
       <c r="O28">
-        <v>174.9024052496185</v>
+        <v>173.3057028874243</v>
       </c>
       <c r="P28">
-        <v>485.1066711640361</v>
+        <v>480.6780815934221</v>
       </c>
       <c r="Q28">
-        <v>785.1066711640361</v>
+        <v>780.6780815934221</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1024697200651289</v>
+        <v>0.1030825207184711</v>
       </c>
       <c r="T28">
-        <v>1.308769516515679</v>
+        <v>1.322921956546678</v>
       </c>
       <c r="U28">
         <v>0.05429999999999999</v>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.213067974221341</v>
+        <v>5.019991382583513</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08602607512448393</v>
+        <v>0.0858478274007725</v>
       </c>
       <c r="C29">
-        <v>10349.86252617542</v>
+        <v>10296.83589310982</v>
       </c>
       <c r="D29">
-        <v>13016.86403972644</v>
+        <v>13074.80042568124</v>
       </c>
       <c r="E29">
-        <v>-1740.10038848979</v>
+        <v>-1629.137369469382</v>
       </c>
       <c r="F29">
-        <v>2996.001513551018</v>
+        <v>3106.964532571426</v>
       </c>
       <c r="G29">
         <v>329</v>
@@ -5418,28 +5418,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M29">
-        <v>162.6828821858203</v>
+        <v>168.7081741186284</v>
       </c>
       <c r="N29">
-        <v>653.9837844808465</v>
+        <v>647.9584925480383</v>
       </c>
       <c r="O29">
-        <v>173.3057028874243</v>
+        <v>171.7090005252302</v>
       </c>
       <c r="P29">
-        <v>480.6780815934221</v>
+        <v>476.2494920228081</v>
       </c>
       <c r="Q29">
-        <v>780.6780815934221</v>
+        <v>776.2494920228081</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1030825207184711</v>
+        <v>0.103712343612184</v>
       </c>
       <c r="T29">
-        <v>1.322921956546678</v>
+        <v>1.337467519911872</v>
       </c>
       <c r="U29">
         <v>0.05429999999999999</v>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.019991382583513</v>
+        <v>4.840705976062674</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0858478274007725</v>
+        <v>0.08566957967706107</v>
       </c>
       <c r="C30">
-        <v>10296.83589310982</v>
+        <v>10244.32730056533</v>
       </c>
       <c r="D30">
-        <v>13074.80042568124</v>
+        <v>13133.25485215717</v>
       </c>
       <c r="E30">
-        <v>-1629.137369469382</v>
+        <v>-1518.174350448974</v>
       </c>
       <c r="F30">
-        <v>3106.964532571426</v>
+        <v>3217.927551591835</v>
       </c>
       <c r="G30">
         <v>329</v>
@@ -5500,28 +5500,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M30">
-        <v>168.7081741186284</v>
+        <v>174.7334660514366</v>
       </c>
       <c r="N30">
-        <v>647.9584925480383</v>
+        <v>641.9332006152301</v>
       </c>
       <c r="O30">
-        <v>171.7090005252302</v>
+        <v>170.112298163036</v>
       </c>
       <c r="P30">
-        <v>476.2494920228081</v>
+        <v>471.8209024521941</v>
       </c>
       <c r="Q30">
-        <v>776.2494920228081</v>
+        <v>771.8209024521941</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.103712343612184</v>
+        <v>0.1043599079958607</v>
       </c>
       <c r="T30">
-        <v>1.337467519911872</v>
+        <v>1.352422817456367</v>
       </c>
       <c r="U30">
         <v>0.05429999999999999</v>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.840705976062674</v>
+        <v>4.673785080336375</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08566957967706107</v>
+        <v>0.08549133195334963</v>
       </c>
       <c r="C31">
-        <v>10244.32730056533</v>
+        <v>10192.34372786511</v>
       </c>
       <c r="D31">
-        <v>13133.25485215717</v>
+        <v>13192.23429847735</v>
       </c>
       <c r="E31">
-        <v>-1518.174350448974</v>
+        <v>-1407.211331428566</v>
       </c>
       <c r="F31">
-        <v>3217.927551591834</v>
+        <v>3328.890570612242</v>
       </c>
       <c r="G31">
         <v>329</v>
@@ -5582,28 +5582,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M31">
-        <v>174.7334660514366</v>
+        <v>180.7587579842447</v>
       </c>
       <c r="N31">
-        <v>641.9332006152301</v>
+        <v>635.907908682422</v>
       </c>
       <c r="O31">
-        <v>170.112298163036</v>
+        <v>168.5155958008418</v>
       </c>
       <c r="P31">
-        <v>471.8209024521941</v>
+        <v>467.3923128815802</v>
       </c>
       <c r="Q31">
-        <v>771.8209024521941</v>
+        <v>767.3923128815802</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1043599079958607</v>
+        <v>0.1050259742190709</v>
       </c>
       <c r="T31">
-        <v>1.352422817456367</v>
+        <v>1.367805409216418</v>
       </c>
       <c r="U31">
         <v>0.05429999999999999</v>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.673785080336375</v>
+        <v>4.517992244325162</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08549133195334963</v>
+        <v>0.08531308422963818</v>
       </c>
       <c r="C32">
-        <v>10192.34372786511</v>
+        <v>10140.89228027015</v>
       </c>
       <c r="D32">
-        <v>13192.23429847735</v>
+        <v>13251.7458699028</v>
       </c>
       <c r="E32">
-        <v>-1407.211331428566</v>
+        <v>-1296.248312408158</v>
       </c>
       <c r="F32">
-        <v>3328.890570612242</v>
+        <v>3439.853589632651</v>
       </c>
       <c r="G32">
         <v>329</v>
@@ -5664,28 +5664,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M32">
-        <v>180.7587579842447</v>
+        <v>186.7840499170529</v>
       </c>
       <c r="N32">
-        <v>635.907908682422</v>
+        <v>629.8826167496138</v>
       </c>
       <c r="O32">
-        <v>168.5155958008418</v>
+        <v>166.9188934386477</v>
       </c>
       <c r="P32">
-        <v>467.3923128815802</v>
+        <v>462.9637233109661</v>
       </c>
       <c r="Q32">
-        <v>767.3923128815802</v>
+        <v>762.9637233109661</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1050259742190709</v>
+        <v>0.1057113467096206</v>
       </c>
       <c r="T32">
-        <v>1.367805409216418</v>
+        <v>1.383633873201399</v>
       </c>
       <c r="U32">
         <v>0.05429999999999999</v>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.517992244325162</v>
+        <v>4.37225055902435</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08531308422963818</v>
+        <v>0.08537003650592676</v>
       </c>
       <c r="C33">
-        <v>10140.89228027015</v>
+        <v>10010.85631720594</v>
       </c>
       <c r="D33">
-        <v>13251.7458699028</v>
+        <v>13232.672925859</v>
       </c>
       <c r="E33">
-        <v>-1296.248312408158</v>
+        <v>-1185.28529338775</v>
       </c>
       <c r="F33">
-        <v>3439.853589632651</v>
+        <v>3550.816608653059</v>
       </c>
       <c r="G33">
         <v>329</v>
@@ -5746,45 +5746,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M33">
-        <v>186.7840499170529</v>
+        <v>196.3601584585141</v>
       </c>
       <c r="N33">
-        <v>629.8826167496138</v>
+        <v>620.3065082081526</v>
       </c>
       <c r="O33">
-        <v>166.9188934386477</v>
+        <v>164.3812246751605</v>
       </c>
       <c r="P33">
-        <v>462.9637233109661</v>
+        <v>455.9252835329922</v>
       </c>
       <c r="Q33">
-        <v>762.9637233109661</v>
+        <v>755.9252835329921</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1057113467096206</v>
+        <v>0.1064168772145982</v>
       </c>
       <c r="T33">
-        <v>1.383633873201399</v>
+        <v>1.399927880244762</v>
       </c>
       <c r="U33">
-        <v>0.05429999999999999</v>
+        <v>0.05529999999999999</v>
       </c>
       <c r="V33">
         <v>0.265</v>
       </c>
       <c r="W33">
-        <v>0.03991049999999999</v>
+        <v>0.04064549999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.37225055902435</v>
+        <v>4.159024280066506</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08537003650592676</v>
+        <v>0.08519913878221531</v>
       </c>
       <c r="C34">
-        <v>10010.85631720594</v>
+        <v>9957.291346760849</v>
       </c>
       <c r="D34">
-        <v>13232.672925859</v>
+        <v>13290.07097443432</v>
       </c>
       <c r="E34">
-        <v>-1185.28529338775</v>
+        <v>-1074.322274367341</v>
       </c>
       <c r="F34">
-        <v>3550.816608653059</v>
+        <v>3661.779627673467</v>
       </c>
       <c r="G34">
         <v>329</v>
@@ -5828,28 +5828,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M34">
-        <v>196.3601584585141</v>
+        <v>202.4964134103427</v>
       </c>
       <c r="N34">
-        <v>620.3065082081526</v>
+        <v>614.170253256324</v>
       </c>
       <c r="O34">
-        <v>164.3812246751605</v>
+        <v>162.7551171129259</v>
       </c>
       <c r="P34">
-        <v>455.9252835329922</v>
+        <v>451.4151361433982</v>
       </c>
       <c r="Q34">
-        <v>755.9252835329921</v>
+        <v>751.4151361433982</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1064168772145982</v>
+        <v>0.1071434683316647</v>
       </c>
       <c r="T34">
-        <v>1.399927880244762</v>
+        <v>1.416708275558076</v>
       </c>
       <c r="U34">
         <v>0.05529999999999999</v>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.159024280066506</v>
+        <v>4.032993241276611</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08519913878221531</v>
+        <v>0.08502824105850387</v>
       </c>
       <c r="C35">
-        <v>9957.291346760849</v>
+        <v>9904.226485195602</v>
       </c>
       <c r="D35">
-        <v>13290.07097443432</v>
+        <v>13347.96913188948</v>
       </c>
       <c r="E35">
-        <v>-1074.322274367341</v>
+        <v>-963.3592553469334</v>
       </c>
       <c r="F35">
-        <v>3661.779627673467</v>
+        <v>3772.742646693875</v>
       </c>
       <c r="G35">
         <v>329</v>
@@ -5910,28 +5910,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M35">
-        <v>202.4964134103427</v>
+        <v>208.6326683621713</v>
       </c>
       <c r="N35">
-        <v>614.170253256324</v>
+        <v>608.0339983044955</v>
       </c>
       <c r="O35">
-        <v>162.7551171129259</v>
+        <v>161.1290095506913</v>
       </c>
       <c r="P35">
-        <v>451.4151361433982</v>
+        <v>446.9049887538042</v>
       </c>
       <c r="Q35">
-        <v>751.4151361433982</v>
+        <v>746.9049887538042</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1071434683316647</v>
+        <v>0.1078920773613695</v>
       </c>
       <c r="T35">
-        <v>1.416708275558076</v>
+        <v>1.433997167699065</v>
       </c>
       <c r="U35">
         <v>0.05529999999999999</v>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.032993241276611</v>
+        <v>3.91437579300377</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08502824105850387</v>
+        <v>0.08485734333479245</v>
       </c>
       <c r="C36">
-        <v>9904.226485195602</v>
+        <v>9851.668297278447</v>
       </c>
       <c r="D36">
-        <v>13347.96913188948</v>
+        <v>13406.37396299273</v>
       </c>
       <c r="E36">
-        <v>-963.3592553469334</v>
+        <v>-852.396236326525</v>
       </c>
       <c r="F36">
-        <v>3772.742646693875</v>
+        <v>3883.705665714283</v>
       </c>
       <c r="G36">
         <v>329</v>
@@ -5992,28 +5992,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M36">
-        <v>208.6326683621713</v>
+        <v>214.7689233139999</v>
       </c>
       <c r="N36">
-        <v>608.0339983044955</v>
+        <v>601.8977433526669</v>
       </c>
       <c r="O36">
-        <v>161.1290095506913</v>
+        <v>159.5029019884567</v>
       </c>
       <c r="P36">
-        <v>446.9049887538042</v>
+        <v>442.3948413642102</v>
       </c>
       <c r="Q36">
-        <v>746.9049887538042</v>
+        <v>742.3948413642102</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1078920773613695</v>
+        <v>0.1086637205150653</v>
       </c>
       <c r="T36">
-        <v>1.433997167699065</v>
+        <v>1.451818025752086</v>
       </c>
       <c r="U36">
         <v>0.05529999999999999</v>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.91437579300377</v>
+        <v>3.802536484632233</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08485734333479245</v>
+        <v>0.084686445611081</v>
       </c>
       <c r="C37">
-        <v>9851.668297278447</v>
+        <v>9799.623463180729</v>
       </c>
       <c r="D37">
-        <v>13406.37396299273</v>
+        <v>13465.29214791542</v>
       </c>
       <c r="E37">
-        <v>-852.396236326525</v>
+        <v>-741.4332173061171</v>
       </c>
       <c r="F37">
-        <v>3883.705665714283</v>
+        <v>3994.668684734691</v>
       </c>
       <c r="G37">
         <v>329</v>
@@ -6074,28 +6074,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M37">
-        <v>214.7689233139999</v>
+        <v>220.9051782658284</v>
       </c>
       <c r="N37">
-        <v>601.8977433526669</v>
+        <v>595.7614884008383</v>
       </c>
       <c r="O37">
-        <v>159.5029019884567</v>
+        <v>157.8767944262221</v>
       </c>
       <c r="P37">
-        <v>442.3948413642102</v>
+        <v>437.8846939746161</v>
       </c>
       <c r="Q37">
-        <v>742.3948413642102</v>
+        <v>737.8846939746161</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1086637205150653</v>
+        <v>0.1094594775173141</v>
       </c>
       <c r="T37">
-        <v>1.451818025752086</v>
+        <v>1.470195785619263</v>
       </c>
       <c r="U37">
         <v>0.05529999999999999</v>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.802536484632233</v>
+        <v>3.696910471170227</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08468644561108102</v>
+        <v>0.08451554788736958</v>
       </c>
       <c r="C38">
-        <v>9799.623463180727</v>
+        <v>9748.098781023917</v>
       </c>
       <c r="D38">
-        <v>13465.29214791542</v>
+        <v>13524.73048477902</v>
       </c>
       <c r="E38">
-        <v>-741.4332173061175</v>
+        <v>-630.4701982857096</v>
       </c>
       <c r="F38">
-        <v>3994.668684734691</v>
+        <v>4105.631703755099</v>
       </c>
       <c r="G38">
         <v>329</v>
@@ -6156,28 +6156,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M38">
-        <v>220.9051782658284</v>
+        <v>227.041433217657</v>
       </c>
       <c r="N38">
-        <v>595.7614884008383</v>
+        <v>589.6252334490098</v>
       </c>
       <c r="O38">
-        <v>157.8767944262221</v>
+        <v>156.2506868639876</v>
       </c>
       <c r="P38">
-        <v>437.8846939746161</v>
+        <v>433.3745465850222</v>
       </c>
       <c r="Q38">
-        <v>737.8846939746161</v>
+        <v>733.3745465850222</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1094594775173141</v>
+        <v>0.1102804966466184</v>
       </c>
       <c r="T38">
-        <v>1.470195785619263</v>
+        <v>1.489156966434605</v>
       </c>
       <c r="U38">
         <v>0.05529999999999999</v>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.696910471170227</v>
+        <v>3.596993971949411</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08451554788736958</v>
+        <v>0.08434465016365814</v>
       </c>
       <c r="C39">
-        <v>9748.098781023917</v>
+        <v>9697.10116949445</v>
       </c>
       <c r="D39">
-        <v>13524.73048477902</v>
+        <v>13584.69589226996</v>
       </c>
       <c r="E39">
-        <v>-630.4701982857096</v>
+        <v>-519.5071792653016</v>
       </c>
       <c r="F39">
-        <v>4105.631703755099</v>
+        <v>4216.594722775507</v>
       </c>
       <c r="G39">
         <v>329</v>
@@ -6238,28 +6238,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M39">
-        <v>227.041433217657</v>
+        <v>233.1776881694855</v>
       </c>
       <c r="N39">
-        <v>589.6252334490098</v>
+        <v>583.4889784971813</v>
       </c>
       <c r="O39">
-        <v>156.2506868639876</v>
+        <v>154.624579301753</v>
       </c>
       <c r="P39">
-        <v>433.3745465850222</v>
+        <v>428.8643991954282</v>
       </c>
       <c r="Q39">
-        <v>733.3745465850222</v>
+        <v>728.8643991954282</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1102804966466184</v>
+        <v>0.1111280002639647</v>
       </c>
       <c r="T39">
-        <v>1.489156966434605</v>
+        <v>1.50872979824399</v>
       </c>
       <c r="U39">
         <v>0.05529999999999999</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.596993971949411</v>
+        <v>3.502336235845479</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08434465016365814</v>
+        <v>0.08417375243994671</v>
       </c>
       <c r="C40">
-        <v>9697.10116949445</v>
+        <v>9646.637670528382</v>
       </c>
       <c r="D40">
-        <v>13584.69589226996</v>
+        <v>13645.1954123243</v>
       </c>
       <c r="E40">
-        <v>-519.5071792653016</v>
+        <v>-408.5441602448927</v>
       </c>
       <c r="F40">
-        <v>4216.594722775507</v>
+        <v>4327.557741795916</v>
       </c>
       <c r="G40">
         <v>329</v>
@@ -6320,28 +6320,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M40">
-        <v>233.1776881694855</v>
+        <v>239.3139431213141</v>
       </c>
       <c r="N40">
-        <v>583.4889784971813</v>
+        <v>577.3527235453527</v>
       </c>
       <c r="O40">
-        <v>154.624579301753</v>
+        <v>152.9984717395185</v>
       </c>
       <c r="P40">
-        <v>428.8643991954282</v>
+        <v>424.3542518058342</v>
       </c>
       <c r="Q40">
-        <v>728.8643991954282</v>
+        <v>724.3542518058342</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1111280002639647</v>
+        <v>0.1120032908851585</v>
       </c>
       <c r="T40">
-        <v>1.50872979824399</v>
+        <v>1.528944362243847</v>
       </c>
       <c r="U40">
         <v>0.05529999999999999</v>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.502336235845479</v>
+        <v>3.412532742618672</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08417375243994671</v>
+        <v>0.08400285471623527</v>
       </c>
       <c r="C41">
-        <v>9646.637670528382</v>
+        <v>9596.715452068172</v>
       </c>
       <c r="D41">
-        <v>13645.1954123243</v>
+        <v>13706.2362128845</v>
       </c>
       <c r="E41">
-        <v>-408.5441602448927</v>
+        <v>-297.5811412244848</v>
       </c>
       <c r="F41">
-        <v>4327.557741795916</v>
+        <v>4438.520760816324</v>
       </c>
       <c r="G41">
         <v>329</v>
@@ -6402,28 +6402,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M41">
-        <v>239.3139431213141</v>
+        <v>245.4501980731427</v>
       </c>
       <c r="N41">
-        <v>577.3527235453527</v>
+        <v>571.216468593524</v>
       </c>
       <c r="O41">
-        <v>152.9984717395185</v>
+        <v>151.3723641772839</v>
       </c>
       <c r="P41">
-        <v>424.3542518058342</v>
+        <v>419.8441044162402</v>
       </c>
       <c r="Q41">
-        <v>724.3542518058342</v>
+        <v>719.8441044162402</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1120032908851585</v>
+        <v>0.1129077578603921</v>
       </c>
       <c r="T41">
-        <v>1.528944362243847</v>
+        <v>1.549832745043698</v>
       </c>
       <c r="U41">
         <v>0.05529999999999999</v>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.412532742618672</v>
+        <v>3.327219424053204</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08400285471623527</v>
+        <v>0.08383195699252384</v>
       </c>
       <c r="C42">
-        <v>9596.715452068172</v>
+        <v>9547.341810893706</v>
       </c>
       <c r="D42">
-        <v>13706.2362128845</v>
+        <v>13767.82559073044</v>
       </c>
       <c r="E42">
-        <v>-297.5811412244848</v>
+        <v>-186.6181222040768</v>
       </c>
       <c r="F42">
-        <v>4438.520760816324</v>
+        <v>4549.483779836732</v>
       </c>
       <c r="G42">
         <v>329</v>
@@ -6484,28 +6484,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M42">
-        <v>245.4501980731427</v>
+        <v>251.5864530249712</v>
       </c>
       <c r="N42">
-        <v>571.216468593524</v>
+        <v>565.0802136416955</v>
       </c>
       <c r="O42">
-        <v>151.3723641772839</v>
+        <v>149.7462566150493</v>
       </c>
       <c r="P42">
-        <v>419.8441044162402</v>
+        <v>415.3339570266462</v>
       </c>
       <c r="Q42">
-        <v>719.8441044162402</v>
+        <v>715.3339570266462</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1129077578603921</v>
+        <v>0.1138428847330913</v>
       </c>
       <c r="T42">
-        <v>1.549832745043698</v>
+        <v>1.571429208616426</v>
       </c>
       <c r="U42">
         <v>0.05529999999999999</v>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.327219424053204</v>
+        <v>3.246067730783615</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08383195699252384</v>
+        <v>0.0836610592688124</v>
       </c>
       <c r="C43">
-        <v>9547.341810893706</v>
+        <v>9498.524175530067</v>
       </c>
       <c r="D43">
-        <v>13767.82559073044</v>
+        <v>13829.97097438721</v>
       </c>
       <c r="E43">
-        <v>-186.6181222040768</v>
+        <v>-75.65510318366887</v>
       </c>
       <c r="F43">
-        <v>4549.483779836732</v>
+        <v>4660.44679885714</v>
       </c>
       <c r="G43">
         <v>329</v>
@@ -6566,28 +6566,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M43">
-        <v>251.5864530249712</v>
+        <v>257.7227079767998</v>
       </c>
       <c r="N43">
-        <v>565.0802136416955</v>
+        <v>558.943958689867</v>
       </c>
       <c r="O43">
-        <v>149.7462566150493</v>
+        <v>148.1201490528148</v>
       </c>
       <c r="P43">
-        <v>415.3339570266462</v>
+        <v>410.8238096370522</v>
       </c>
       <c r="Q43">
-        <v>715.3339570266462</v>
+        <v>710.8238096370522</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1138428847330913</v>
+        <v>0.1148102573600214</v>
       </c>
       <c r="T43">
-        <v>1.571429208616426</v>
+        <v>1.593770377829594</v>
       </c>
       <c r="U43">
         <v>0.05529999999999999</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.246067730783615</v>
+        <v>3.168780403860195</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0836610592688124</v>
+        <v>0.08349016154510097</v>
       </c>
       <c r="C44">
-        <v>9498.524175530067</v>
+        <v>9450.270109234354</v>
       </c>
       <c r="D44">
-        <v>13829.97097438721</v>
+        <v>13892.6799271119</v>
       </c>
       <c r="E44">
-        <v>-75.65510318366887</v>
+        <v>35.30791583673908</v>
       </c>
       <c r="F44">
-        <v>4660.44679885714</v>
+        <v>4771.409817877548</v>
       </c>
       <c r="G44">
         <v>329</v>
@@ -6648,28 +6648,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M44">
-        <v>257.7227079767998</v>
+        <v>263.8589629286283</v>
       </c>
       <c r="N44">
-        <v>558.943958689867</v>
+        <v>552.8077037380384</v>
       </c>
       <c r="O44">
-        <v>148.1201490528148</v>
+        <v>146.4940414905802</v>
       </c>
       <c r="P44">
-        <v>410.8238096370522</v>
+        <v>406.3136622474582</v>
       </c>
       <c r="Q44">
-        <v>710.8238096370522</v>
+        <v>706.3136622474583</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1148102573600214</v>
+        <v>0.1158115728861421</v>
       </c>
       <c r="T44">
-        <v>1.593770377829594</v>
+        <v>1.616895447716907</v>
       </c>
       <c r="U44">
         <v>0.05529999999999999</v>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.168780403860195</v>
+        <v>3.095087836328563</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08349016154510097</v>
+        <v>0.08331926382138954</v>
       </c>
       <c r="C45">
-        <v>9450.270109234354</v>
+        <v>9402.587313064198</v>
       </c>
       <c r="D45">
-        <v>13892.6799271119</v>
+        <v>13955.96014996215</v>
       </c>
       <c r="E45">
-        <v>35.30791583673908</v>
+        <v>146.270934857147</v>
       </c>
       <c r="F45">
-        <v>4771.409817877548</v>
+        <v>4882.372836897955</v>
       </c>
       <c r="G45">
         <v>329</v>
@@ -6730,28 +6730,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M45">
-        <v>263.8589629286283</v>
+        <v>269.9952178804569</v>
       </c>
       <c r="N45">
-        <v>552.8077037380384</v>
+        <v>546.6714487862098</v>
       </c>
       <c r="O45">
-        <v>146.4940414905802</v>
+        <v>144.8679339283456</v>
       </c>
       <c r="P45">
-        <v>406.3136622474582</v>
+        <v>401.8035148578642</v>
       </c>
       <c r="Q45">
-        <v>706.3136622474583</v>
+        <v>701.8035148578642</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1158115728861421</v>
+        <v>0.1168486496810527</v>
       </c>
       <c r="T45">
-        <v>1.616895447716907</v>
+        <v>1.640846412957338</v>
       </c>
       <c r="U45">
         <v>0.05529999999999999</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.095087836328563</v>
+        <v>3.024744930957459</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08331926382138954</v>
+        <v>0.08397524109767809</v>
       </c>
       <c r="C46">
-        <v>9402.587313064198</v>
+        <v>9051.814604204774</v>
       </c>
       <c r="D46">
-        <v>13955.96014996215</v>
+        <v>13716.15046012314</v>
       </c>
       <c r="E46">
-        <v>146.270934857147</v>
+        <v>257.233953877555</v>
       </c>
       <c r="F46">
-        <v>4882.372836897955</v>
+        <v>4993.335855918363</v>
       </c>
       <c r="G46">
         <v>329</v>
@@ -6812,45 +6812,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M46">
-        <v>269.9952178804569</v>
+        <v>288.6148124720814</v>
       </c>
       <c r="N46">
-        <v>546.6714487862098</v>
+        <v>528.0518541945853</v>
       </c>
       <c r="O46">
-        <v>144.8679339283456</v>
+        <v>139.9337413615651</v>
       </c>
       <c r="P46">
-        <v>401.8035148578642</v>
+        <v>388.1181128330202</v>
       </c>
       <c r="Q46">
-        <v>701.8035148578642</v>
+        <v>688.1181128330202</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1168486496810527</v>
+        <v>0.1179234383594147</v>
       </c>
       <c r="T46">
-        <v>1.640846412957338</v>
+        <v>1.665668322388331</v>
       </c>
       <c r="U46">
-        <v>0.05529999999999999</v>
+        <v>0.05779999999999999</v>
       </c>
       <c r="V46">
         <v>0.265</v>
       </c>
       <c r="W46">
-        <v>0.04064549999999999</v>
+        <v>0.04248299999999999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.024744930957459</v>
+        <v>2.829607599387039</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08397524109767809</v>
+        <v>0.08382271837396665</v>
       </c>
       <c r="C47">
-        <v>9051.814604204774</v>
+        <v>8995.871970797991</v>
       </c>
       <c r="D47">
-        <v>13716.15046012314</v>
+        <v>13771.17084573676</v>
       </c>
       <c r="E47">
-        <v>257.233953877555</v>
+        <v>368.1969728979639</v>
       </c>
       <c r="F47">
-        <v>4993.335855918363</v>
+        <v>5104.298874938772</v>
       </c>
       <c r="G47">
         <v>329</v>
@@ -6894,28 +6894,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M47">
-        <v>288.6148124720814</v>
+        <v>295.028474971461</v>
       </c>
       <c r="N47">
-        <v>528.0518541945853</v>
+        <v>521.6381916952057</v>
       </c>
       <c r="O47">
-        <v>139.9337413615651</v>
+        <v>138.2341207992295</v>
       </c>
       <c r="P47">
-        <v>388.1181128330202</v>
+        <v>383.4040708959762</v>
       </c>
       <c r="Q47">
-        <v>688.1181128330202</v>
+        <v>683.4040708959762</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1179234383594147</v>
+        <v>0.1190380340258642</v>
       </c>
       <c r="T47">
-        <v>1.665668322388331</v>
+        <v>1.691409561798249</v>
       </c>
       <c r="U47">
         <v>0.05779999999999999</v>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.829607599387039</v>
+        <v>2.768094390704712</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08382271837396665</v>
+        <v>0.08367019565025523</v>
       </c>
       <c r="C48">
-        <v>8995.871970797991</v>
+        <v>8940.372528081367</v>
       </c>
       <c r="D48">
-        <v>13771.17084573676</v>
+        <v>13826.63442204055</v>
       </c>
       <c r="E48">
-        <v>368.1969728979639</v>
+        <v>479.1599919183718</v>
       </c>
       <c r="F48">
-        <v>5104.298874938772</v>
+        <v>5215.26189395918</v>
       </c>
       <c r="G48">
         <v>329</v>
@@ -6976,28 +6976,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M48">
-        <v>295.028474971461</v>
+        <v>301.4421374708406</v>
       </c>
       <c r="N48">
-        <v>521.6381916952057</v>
+        <v>515.2245291958261</v>
       </c>
       <c r="O48">
-        <v>138.2341207992295</v>
+        <v>136.5345002368939</v>
       </c>
       <c r="P48">
-        <v>383.4040708959762</v>
+        <v>378.6900289589322</v>
       </c>
       <c r="Q48">
-        <v>683.4040708959762</v>
+        <v>678.6900289589322</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1190380340258642</v>
+        <v>0.1201946899061419</v>
       </c>
       <c r="T48">
-        <v>1.691409561798249</v>
+        <v>1.718122168733071</v>
       </c>
       <c r="U48">
         <v>0.05779999999999999</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.768094390704712</v>
+        <v>2.709198765370569</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08367019565025523</v>
+        <v>0.08351767292654379</v>
       </c>
       <c r="C49">
-        <v>8940.372528081367</v>
+        <v>8885.321652578379</v>
       </c>
       <c r="D49">
-        <v>13826.63442204055</v>
+        <v>13882.54656555797</v>
       </c>
       <c r="E49">
-        <v>479.1599919183718</v>
+        <v>590.1230109387798</v>
       </c>
       <c r="F49">
-        <v>5215.26189395918</v>
+        <v>5326.224912979588</v>
       </c>
       <c r="G49">
         <v>329</v>
@@ -7058,28 +7058,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M49">
-        <v>301.4421374708406</v>
+        <v>307.8557999702202</v>
       </c>
       <c r="N49">
-        <v>515.2245291958261</v>
+        <v>508.8108666964466</v>
       </c>
       <c r="O49">
-        <v>136.5345002368939</v>
+        <v>134.8348796745584</v>
       </c>
       <c r="P49">
-        <v>378.6900289589322</v>
+        <v>373.9759870218882</v>
       </c>
       <c r="Q49">
-        <v>678.6900289589322</v>
+        <v>673.9759870218882</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1201946899061419</v>
+        <v>0.1213958325510457</v>
       </c>
       <c r="T49">
-        <v>1.718122168733071</v>
+        <v>1.745862183626923</v>
       </c>
       <c r="U49">
         <v>0.05779999999999999</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.709198765370569</v>
+        <v>2.652757124425349</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08351767292654379</v>
+        <v>0.08336515020283235</v>
       </c>
       <c r="C50">
-        <v>8885.321652578379</v>
+        <v>8830.72480813193</v>
       </c>
       <c r="D50">
-        <v>13882.54656555797</v>
+        <v>13938.91274013193</v>
       </c>
       <c r="E50">
-        <v>590.1230109387798</v>
+        <v>701.0860299591877</v>
       </c>
       <c r="F50">
-        <v>5326.224912979588</v>
+        <v>5437.187931999996</v>
       </c>
       <c r="G50">
         <v>329</v>
@@ -7140,28 +7140,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M50">
-        <v>307.8557999702202</v>
+        <v>314.2694624695997</v>
       </c>
       <c r="N50">
-        <v>508.8108666964466</v>
+        <v>502.397204197067</v>
       </c>
       <c r="O50">
-        <v>134.8348796745584</v>
+        <v>133.1352591122228</v>
       </c>
       <c r="P50">
-        <v>373.9759870218882</v>
+        <v>369.2619450848442</v>
       </c>
       <c r="Q50">
-        <v>673.9759870218882</v>
+        <v>669.2619450848442</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1213958325510457</v>
+        <v>0.122644078829083</v>
       </c>
       <c r="T50">
-        <v>1.745862183626923</v>
+        <v>1.774690042242103</v>
       </c>
       <c r="U50">
         <v>0.05779999999999999</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.652757124425349</v>
+        <v>2.598619223926873</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08336515020283235</v>
+        <v>0.08321262747912091</v>
       </c>
       <c r="C51">
-        <v>8830.72480813193</v>
+        <v>8776.587547684278</v>
       </c>
       <c r="D51">
-        <v>13938.91274013193</v>
+        <v>13995.73849870468</v>
       </c>
       <c r="E51">
-        <v>701.0860299591877</v>
+        <v>812.0490489795957</v>
       </c>
       <c r="F51">
-        <v>5437.187931999996</v>
+        <v>5548.150951020404</v>
       </c>
       <c r="G51">
         <v>329</v>
@@ -7222,28 +7222,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M51">
-        <v>314.2694624695997</v>
+        <v>320.6831249689793</v>
       </c>
       <c r="N51">
-        <v>502.397204197067</v>
+        <v>495.9835416976874</v>
       </c>
       <c r="O51">
-        <v>133.1352591122228</v>
+        <v>131.4356385498872</v>
       </c>
       <c r="P51">
-        <v>369.2619450848442</v>
+        <v>364.5479031478002</v>
       </c>
       <c r="Q51">
-        <v>669.2619450848442</v>
+        <v>664.5479031478003</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.122644078829083</v>
+        <v>0.1239422549582418</v>
       </c>
       <c r="T51">
-        <v>1.774690042242103</v>
+        <v>1.80467101520189</v>
       </c>
       <c r="U51">
         <v>0.05779999999999999</v>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.598619223926873</v>
+        <v>2.546646839448336</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08321262747912091</v>
+        <v>0.08437207975540947</v>
       </c>
       <c r="C52">
-        <v>8776.587547684278</v>
+        <v>8244.92149777825</v>
       </c>
       <c r="D52">
-        <v>13995.73849870468</v>
+        <v>13575.03546781906</v>
       </c>
       <c r="E52">
-        <v>812.0490489795957</v>
+        <v>923.0120680000036</v>
       </c>
       <c r="F52">
-        <v>5548.150951020404</v>
+        <v>5659.113970040812</v>
       </c>
       <c r="G52">
         <v>329</v>
@@ -7304,45 +7304,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M52">
-        <v>320.6831249689793</v>
+        <v>346.9036863635017</v>
       </c>
       <c r="N52">
-        <v>495.9835416976874</v>
+        <v>469.762980303165</v>
       </c>
       <c r="O52">
-        <v>131.4356385498872</v>
+        <v>124.4871897803387</v>
       </c>
       <c r="P52">
-        <v>364.5479031478002</v>
+        <v>345.2757905228263</v>
       </c>
       <c r="Q52">
-        <v>664.5479031478003</v>
+        <v>645.2757905228264</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1239422549582418</v>
+        <v>0.1252934178681826</v>
       </c>
       <c r="T52">
-        <v>1.80467101520189</v>
+        <v>1.83587570134371</v>
       </c>
       <c r="U52">
-        <v>0.05779999999999999</v>
+        <v>0.06129999999999999</v>
       </c>
       <c r="V52">
         <v>0.265</v>
       </c>
       <c r="W52">
-        <v>0.04248299999999999</v>
+        <v>0.04505549999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.546646839448336</v>
+        <v>2.354159666700474</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08437207975540947</v>
+        <v>0.08424528203169804</v>
       </c>
       <c r="C53">
-        <v>8244.92149777825</v>
+        <v>8178.730776050451</v>
       </c>
       <c r="D53">
-        <v>13575.03546781906</v>
+        <v>13619.80776511167</v>
       </c>
       <c r="E53">
-        <v>923.0120680000036</v>
+        <v>1033.975087020412</v>
       </c>
       <c r="F53">
-        <v>5659.113970040812</v>
+        <v>5770.07698906122</v>
       </c>
       <c r="G53">
         <v>329</v>
@@ -7386,28 +7386,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M53">
-        <v>346.9036863635017</v>
+        <v>353.7057194294528</v>
       </c>
       <c r="N53">
-        <v>469.762980303165</v>
+        <v>462.960947237214</v>
       </c>
       <c r="O53">
-        <v>124.4871897803387</v>
+        <v>122.6846510178617</v>
       </c>
       <c r="P53">
-        <v>345.2757905228263</v>
+        <v>340.2762962193523</v>
       </c>
       <c r="Q53">
-        <v>645.2757905228264</v>
+        <v>640.2762962193523</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1252934178681826</v>
+        <v>0.1267008792327043</v>
       </c>
       <c r="T53">
-        <v>1.83587570134371</v>
+        <v>1.868380582741438</v>
       </c>
       <c r="U53">
         <v>0.06129999999999999</v>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.354159666700474</v>
+        <v>2.308887365417772</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08424528203169804</v>
+        <v>0.0841184843079866</v>
       </c>
       <c r="C54">
-        <v>8178.730776050451</v>
+        <v>8112.836361730662</v>
       </c>
       <c r="D54">
-        <v>13619.80776511167</v>
+        <v>13664.87636981229</v>
       </c>
       <c r="E54">
-        <v>1033.975087020412</v>
+        <v>1144.93810604082</v>
       </c>
       <c r="F54">
-        <v>5770.07698906122</v>
+        <v>5881.040008081629</v>
       </c>
       <c r="G54">
         <v>329</v>
@@ -7468,28 +7468,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M54">
-        <v>353.7057194294528</v>
+        <v>360.5077524954038</v>
       </c>
       <c r="N54">
-        <v>462.960947237214</v>
+        <v>456.1589141712629</v>
       </c>
       <c r="O54">
-        <v>122.6846510178617</v>
+        <v>120.8821122553847</v>
       </c>
       <c r="P54">
-        <v>340.2762962193523</v>
+        <v>335.2768019158783</v>
       </c>
       <c r="Q54">
-        <v>640.2762962193523</v>
+        <v>635.2768019158782</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1267008792327043</v>
+        <v>0.1281682325701843</v>
       </c>
       <c r="T54">
-        <v>1.868380582741438</v>
+        <v>1.902268650581624</v>
       </c>
       <c r="U54">
         <v>0.06129999999999999</v>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.308887365417772</v>
+        <v>2.265323452862719</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0841184843079866</v>
+        <v>0.08510300658427518</v>
       </c>
       <c r="C55">
-        <v>8112.836361730662</v>
+        <v>7659.574461326654</v>
       </c>
       <c r="D55">
-        <v>13664.87636981229</v>
+        <v>13322.57748842869</v>
       </c>
       <c r="E55">
-        <v>1144.93810604082</v>
+        <v>1255.901125061228</v>
       </c>
       <c r="F55">
-        <v>5881.040008081629</v>
+        <v>5992.003027102037</v>
       </c>
       <c r="G55">
         <v>329</v>
@@ -7550,45 +7550,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M55">
-        <v>360.5077524954038</v>
+        <v>384.0873940372405</v>
       </c>
       <c r="N55">
-        <v>456.1589141712629</v>
+        <v>432.5792726294262</v>
       </c>
       <c r="O55">
-        <v>120.8821122553847</v>
+        <v>114.6335072467979</v>
       </c>
       <c r="P55">
-        <v>335.2768019158783</v>
+        <v>317.9457653826283</v>
       </c>
       <c r="Q55">
-        <v>635.2768019158782</v>
+        <v>617.9457653826282</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1281682325701843</v>
+        <v>0.1296993838788591</v>
       </c>
       <c r="T55">
-        <v>1.902268650581624</v>
+        <v>1.93763011267573</v>
       </c>
       <c r="U55">
-        <v>0.06129999999999999</v>
+        <v>0.06409999999999999</v>
       </c>
       <c r="V55">
         <v>0.265</v>
       </c>
       <c r="W55">
-        <v>0.04505549999999999</v>
+        <v>0.04711349999999999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.265323452862719</v>
+        <v>2.126252200267432</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08510300658427518</v>
+        <v>0.08499678886056372</v>
       </c>
       <c r="C56">
-        <v>7659.574461326654</v>
+        <v>7584.713732721524</v>
       </c>
       <c r="D56">
-        <v>13322.57748842869</v>
+        <v>13358.67977884397</v>
       </c>
       <c r="E56">
-        <v>1255.901125061228</v>
+        <v>1366.864144081636</v>
       </c>
       <c r="F56">
-        <v>5992.003027102037</v>
+        <v>6102.966046122445</v>
       </c>
       <c r="G56">
         <v>329</v>
@@ -7632,28 +7632,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M56">
-        <v>384.0873940372405</v>
+        <v>391.2001235564487</v>
       </c>
       <c r="N56">
-        <v>432.5792726294262</v>
+        <v>425.4665431102181</v>
       </c>
       <c r="O56">
-        <v>114.6335072467979</v>
+        <v>112.7486339242078</v>
       </c>
       <c r="P56">
-        <v>317.9457653826283</v>
+        <v>312.7179091860103</v>
       </c>
       <c r="Q56">
-        <v>617.9457653826282</v>
+        <v>612.7179091860103</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1296993838788591</v>
+        <v>0.1312985863568083</v>
       </c>
       <c r="T56">
-        <v>1.93763011267573</v>
+        <v>1.974563195307352</v>
       </c>
       <c r="U56">
         <v>0.06409999999999999</v>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.126252200267432</v>
+        <v>2.087593069353479</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08499678886056372</v>
+        <v>0.08489057113685231</v>
       </c>
       <c r="C57">
-        <v>7584.713732721524</v>
+        <v>7510.049199925097</v>
       </c>
       <c r="D57">
-        <v>13358.67977884397</v>
+        <v>13394.97826506795</v>
       </c>
       <c r="E57">
-        <v>1366.864144081636</v>
+        <v>1477.827163102044</v>
       </c>
       <c r="F57">
-        <v>6102.966046122445</v>
+        <v>6213.929065142853</v>
       </c>
       <c r="G57">
         <v>329</v>
@@ -7714,28 +7714,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M57">
-        <v>391.2001235564487</v>
+        <v>398.3128530756568</v>
       </c>
       <c r="N57">
-        <v>425.4665431102181</v>
+        <v>418.35381359101</v>
       </c>
       <c r="O57">
-        <v>112.7486339242078</v>
+        <v>110.8637606016176</v>
       </c>
       <c r="P57">
-        <v>312.7179091860103</v>
+        <v>307.4900529893923</v>
       </c>
       <c r="Q57">
-        <v>612.7179091860103</v>
+        <v>607.4900529893923</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1312985863568083</v>
+        <v>0.1329704798564825</v>
       </c>
       <c r="T57">
-        <v>1.974563195307352</v>
+        <v>2.013175054422229</v>
       </c>
       <c r="U57">
         <v>0.06409999999999999</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.087593069353479</v>
+        <v>2.050314621686452</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08489057113685231</v>
+        <v>0.08478435341314086</v>
       </c>
       <c r="C58">
-        <v>7510.049199925097</v>
+        <v>7435.582466617104</v>
       </c>
       <c r="D58">
-        <v>13394.97826506795</v>
+        <v>13431.47455078037</v>
       </c>
       <c r="E58">
-        <v>1477.827163102044</v>
+        <v>1588.790182122453</v>
       </c>
       <c r="F58">
-        <v>6213.929065142853</v>
+        <v>6324.892084163262</v>
       </c>
       <c r="G58">
         <v>329</v>
@@ -7796,28 +7796,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M58">
-        <v>398.3128530756568</v>
+        <v>405.425582594865</v>
       </c>
       <c r="N58">
-        <v>418.35381359101</v>
+        <v>411.2410840718017</v>
       </c>
       <c r="O58">
-        <v>110.8637606016176</v>
+        <v>108.9788872790275</v>
       </c>
       <c r="P58">
-        <v>307.4900529893923</v>
+        <v>302.2621967927743</v>
       </c>
       <c r="Q58">
-        <v>607.4900529893923</v>
+        <v>602.2621967927743</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1329704798564825</v>
+        <v>0.1347201358445137</v>
       </c>
       <c r="T58">
-        <v>2.013175054422229</v>
+        <v>2.053582813961055</v>
       </c>
       <c r="U58">
         <v>0.06409999999999999</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.050314621686452</v>
+        <v>2.014344189727041</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08478435341314086</v>
+        <v>0.08800327568942942</v>
       </c>
       <c r="C59">
-        <v>7435.582466617104</v>
+        <v>6300.175919727631</v>
       </c>
       <c r="D59">
-        <v>13431.47455078037</v>
+        <v>12407.0310229113</v>
       </c>
       <c r="E59">
-        <v>1588.790182122453</v>
+        <v>1699.753201142861</v>
       </c>
       <c r="F59">
-        <v>6324.892084163262</v>
+        <v>6435.85510318367</v>
       </c>
       <c r="G59">
         <v>329</v>
@@ -7878,45 +7878,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M59">
-        <v>405.425582594865</v>
+        <v>462.7379819189058</v>
       </c>
       <c r="N59">
-        <v>411.2410840718017</v>
+        <v>353.9286847477609</v>
       </c>
       <c r="O59">
-        <v>108.9788872790275</v>
+        <v>93.79110145815666</v>
       </c>
       <c r="P59">
-        <v>302.2621967927743</v>
+        <v>260.1375832896043</v>
       </c>
       <c r="Q59">
-        <v>602.2621967927743</v>
+        <v>560.1375832896042</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1347201358445137</v>
+        <v>0.1365531087843558</v>
       </c>
       <c r="T59">
-        <v>2.053582813961055</v>
+        <v>2.095914752525539</v>
       </c>
       <c r="U59">
-        <v>0.06409999999999999</v>
+        <v>0.07189999999999999</v>
       </c>
       <c r="V59">
         <v>0.265</v>
       </c>
       <c r="W59">
-        <v>0.04711349999999999</v>
+        <v>0.05284649999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.014344189727041</v>
+        <v>1.76485764855539</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08800327568942942</v>
+        <v>0.08964562296571799</v>
       </c>
       <c r="C60">
-        <v>6300.175919727631</v>
+        <v>5724.476577466059</v>
       </c>
       <c r="D60">
-        <v>12407.0310229113</v>
+        <v>11942.29469967014</v>
       </c>
       <c r="E60">
-        <v>1699.75320114286</v>
+        <v>1810.716220163268</v>
       </c>
       <c r="F60">
-        <v>6435.855103183669</v>
+        <v>6546.818122204077</v>
       </c>
       <c r="G60">
         <v>329</v>
@@ -7960,45 +7960,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M60">
-        <v>462.7379819189057</v>
+        <v>496.248813663069</v>
       </c>
       <c r="N60">
-        <v>353.928684747761</v>
+        <v>320.4178530035978</v>
       </c>
       <c r="O60">
-        <v>93.79110145815667</v>
+        <v>84.91073104595341</v>
       </c>
       <c r="P60">
-        <v>260.1375832896043</v>
+        <v>235.5071219576444</v>
       </c>
       <c r="Q60">
-        <v>560.1375832896043</v>
+        <v>535.5071219576444</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1365531087843558</v>
+        <v>0.1384754950383366</v>
       </c>
       <c r="T60">
-        <v>2.095914752525538</v>
+        <v>2.140311663702924</v>
       </c>
       <c r="U60">
-        <v>0.07189999999999999</v>
+        <v>0.07579999999999999</v>
       </c>
       <c r="V60">
         <v>0.265</v>
       </c>
       <c r="W60">
-        <v>0.05284649999999999</v>
+        <v>0.05571299999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.76485764855539</v>
+        <v>1.645679836770647</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08964562296571799</v>
+        <v>0.08962540024200656</v>
       </c>
       <c r="C61">
-        <v>5724.476577466059</v>
+        <v>5619.024192116041</v>
       </c>
       <c r="D61">
-        <v>11942.29469967014</v>
+        <v>11947.80533334053</v>
       </c>
       <c r="E61">
-        <v>1810.716220163268</v>
+        <v>1921.679239183676</v>
       </c>
       <c r="F61">
-        <v>6546.818122204077</v>
+        <v>6657.781141224485</v>
       </c>
       <c r="G61">
         <v>329</v>
@@ -8042,28 +8042,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M61">
-        <v>496.248813663069</v>
+        <v>504.6598105048159</v>
       </c>
       <c r="N61">
-        <v>320.4178530035978</v>
+        <v>312.0068561618509</v>
       </c>
       <c r="O61">
-        <v>84.91073104595341</v>
+        <v>82.68181688289049</v>
       </c>
       <c r="P61">
-        <v>235.5071219576444</v>
+        <v>229.3250392789604</v>
       </c>
       <c r="Q61">
-        <v>535.5071219576444</v>
+        <v>529.3250392789604</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1384754950383366</v>
+        <v>0.1404940006050164</v>
       </c>
       <c r="T61">
-        <v>2.140311663702924</v>
+        <v>2.186928420439178</v>
       </c>
       <c r="U61">
         <v>0.07579999999999999</v>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.645679836770647</v>
+        <v>1.618251839491136</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08962540024200656</v>
+        <v>0.08960517751829512</v>
       </c>
       <c r="C62">
-        <v>5619.024192116041</v>
+        <v>5513.576894750073</v>
       </c>
       <c r="D62">
-        <v>11947.80533334053</v>
+        <v>11953.32105499497</v>
       </c>
       <c r="E62">
-        <v>1921.679239183676</v>
+        <v>2032.642258204084</v>
       </c>
       <c r="F62">
-        <v>6657.781141224485</v>
+        <v>6768.744160244893</v>
       </c>
       <c r="G62">
         <v>329</v>
@@ -8124,28 +8124,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M62">
-        <v>504.6598105048159</v>
+        <v>513.0708073465628</v>
       </c>
       <c r="N62">
-        <v>312.0068561618509</v>
+        <v>303.595859320104</v>
       </c>
       <c r="O62">
-        <v>82.68181688289049</v>
+        <v>80.45290271982755</v>
       </c>
       <c r="P62">
-        <v>229.3250392789604</v>
+        <v>223.1429566002764</v>
       </c>
       <c r="Q62">
-        <v>529.3250392789604</v>
+        <v>523.1429566002764</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1404940006050164</v>
+        <v>0.1426160192776798</v>
       </c>
       <c r="T62">
-        <v>2.186928420439178</v>
+        <v>2.235935780084985</v>
       </c>
       <c r="U62">
         <v>0.07579999999999999</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.618251839491136</v>
+        <v>1.591723120810954</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08960517751829512</v>
+        <v>0.08958495479458367</v>
       </c>
       <c r="C63">
-        <v>5513.576894750073</v>
+        <v>5408.134692418032</v>
       </c>
       <c r="D63">
-        <v>11953.32105499497</v>
+        <v>11958.84187168333</v>
       </c>
       <c r="E63">
-        <v>2032.642258204084</v>
+        <v>2143.605277224493</v>
       </c>
       <c r="F63">
-        <v>6768.744160244893</v>
+        <v>6879.707179265301</v>
       </c>
       <c r="G63">
         <v>329</v>
@@ -8206,28 +8206,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M63">
-        <v>513.0708073465628</v>
+        <v>521.4818041883098</v>
       </c>
       <c r="N63">
-        <v>303.595859320104</v>
+        <v>295.184862478357</v>
       </c>
       <c r="O63">
-        <v>80.45290271982755</v>
+        <v>78.22398855676461</v>
       </c>
       <c r="P63">
-        <v>223.1429566002764</v>
+        <v>216.9608739215924</v>
       </c>
       <c r="Q63">
-        <v>523.1429566002764</v>
+        <v>516.9608739215923</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1426160192776798</v>
+        <v>0.1448497231436413</v>
       </c>
       <c r="T63">
-        <v>2.235935780084985</v>
+        <v>2.287522474448991</v>
       </c>
       <c r="U63">
         <v>0.07579999999999999</v>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.591723120810954</v>
+        <v>1.566050167249487</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08958495479458367</v>
+        <v>0.08956473207087225</v>
       </c>
       <c r="C64">
-        <v>5408.134692418032</v>
+        <v>5302.697592182824</v>
       </c>
       <c r="D64">
-        <v>11958.84187168333</v>
+        <v>11964.36779046853</v>
       </c>
       <c r="E64">
-        <v>2143.605277224493</v>
+        <v>2254.568296244901</v>
       </c>
       <c r="F64">
-        <v>6879.707179265301</v>
+        <v>6990.670198285709</v>
       </c>
       <c r="G64">
         <v>329</v>
@@ -8288,28 +8288,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M64">
-        <v>521.4818041883098</v>
+        <v>529.8928010300567</v>
       </c>
       <c r="N64">
-        <v>295.184862478357</v>
+        <v>286.77386563661</v>
       </c>
       <c r="O64">
-        <v>78.22398855676461</v>
+        <v>75.99507439370166</v>
       </c>
       <c r="P64">
-        <v>216.9608739215924</v>
+        <v>210.7787912429084</v>
       </c>
       <c r="Q64">
-        <v>516.9608739215923</v>
+        <v>510.7787912429084</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1448497231436413</v>
+        <v>0.1472041677591142</v>
       </c>
       <c r="T64">
-        <v>2.287522474448991</v>
+        <v>2.341897638778619</v>
       </c>
       <c r="U64">
         <v>0.07579999999999999</v>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.566050167249487</v>
+        <v>1.541192228086797</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08956473207087225</v>
+        <v>0.08954450934716081</v>
       </c>
       <c r="C65">
-        <v>5302.697592182824</v>
+        <v>5197.26560112043</v>
       </c>
       <c r="D65">
-        <v>11964.36779046853</v>
+        <v>11969.89881842655</v>
       </c>
       <c r="E65">
-        <v>2254.568296244901</v>
+        <v>2365.531315265309</v>
       </c>
       <c r="F65">
-        <v>6990.670198285709</v>
+        <v>7101.633217306117</v>
       </c>
       <c r="G65">
         <v>329</v>
@@ -8370,28 +8370,28 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M65">
-        <v>529.8928010300567</v>
+        <v>538.3037978718037</v>
       </c>
       <c r="N65">
-        <v>286.77386563661</v>
+        <v>278.3628687948631</v>
       </c>
       <c r="O65">
-        <v>75.99507439370166</v>
+        <v>73.76616023063872</v>
       </c>
       <c r="P65">
-        <v>210.7787912429084</v>
+        <v>204.5967085642243</v>
       </c>
       <c r="Q65">
-        <v>510.7787912429084</v>
+        <v>504.5967085642243</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1472041677591142</v>
+        <v>0.1496894148532245</v>
       </c>
       <c r="T65">
-        <v>2.341897638778619</v>
+        <v>2.399293645571005</v>
       </c>
       <c r="U65">
         <v>0.07579999999999999</v>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.541192228086797</v>
+        <v>1.51711109952294</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08954450934716081</v>
+        <v>0.09630833662344938</v>
       </c>
       <c r="C66">
-        <v>5197.26560112043</v>
+        <v>3483.352781434843</v>
       </c>
       <c r="D66">
-        <v>11969.89881842655</v>
+        <v>10366.94901776137</v>
       </c>
       <c r="E66">
-        <v>2365.531315265309</v>
+        <v>2476.494334285717</v>
       </c>
       <c r="F66">
-        <v>7101.633217306117</v>
+        <v>7212.596236326525</v>
       </c>
       <c r="G66">
         <v>329</v>
@@ -8452,45 +8452,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M66">
-        <v>538.3037978718037</v>
+        <v>649.1336612693873</v>
       </c>
       <c r="N66">
-        <v>278.3628687948631</v>
+        <v>167.5330053972795</v>
       </c>
       <c r="O66">
-        <v>73.76616023063872</v>
+        <v>44.39624643027906</v>
       </c>
       <c r="P66">
-        <v>204.5967085642243</v>
+        <v>123.1367589670004</v>
       </c>
       <c r="Q66">
-        <v>504.5967085642243</v>
+        <v>423.1367589670004</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1496894148532245</v>
+        <v>0.1523166760669983</v>
       </c>
       <c r="T66">
-        <v>2.399293645571005</v>
+        <v>2.459969424180099</v>
       </c>
       <c r="U66">
-        <v>0.07579999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="V66">
         <v>0.265</v>
       </c>
       <c r="W66">
-        <v>0.05571299999999999</v>
+        <v>0.06615</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.51711109952294</v>
+        <v>1.258087071112084</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09630833662344938</v>
+        <v>0.111976748660716</v>
       </c>
       <c r="C67">
-        <v>3483.352781434843</v>
+        <v>917.847463692442</v>
       </c>
       <c r="D67">
-        <v>10366.94901776137</v>
+        <v>7912.406719039377</v>
       </c>
       <c r="E67">
-        <v>2476.494334285717</v>
+        <v>2587.457353306126</v>
       </c>
       <c r="F67">
-        <v>7212.596236326525</v>
+        <v>7323.559255346934</v>
       </c>
       <c r="G67">
         <v>329</v>
@@ -8534,45 +8534,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M67">
-        <v>649.1336612693873</v>
+        <v>868.5741276841464</v>
       </c>
       <c r="N67">
-        <v>167.5330053972795</v>
+        <v>-51.9074610174797</v>
       </c>
       <c r="O67">
-        <v>44.39624643027906</v>
+        <v>-13.75547716963212</v>
       </c>
       <c r="P67">
-        <v>123.1367589670004</v>
+        <v>-38.15198384784758</v>
       </c>
       <c r="Q67">
-        <v>423.1367589670004</v>
+        <v>261.8480161521524</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1523166760669983</v>
+        <v>0.1564830690606795</v>
       </c>
       <c r="T67">
-        <v>2.459969424180099</v>
+        <v>2.556190971378281</v>
       </c>
       <c r="U67">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.265</v>
+        <v>0.2491631511563579</v>
       </c>
       <c r="W67">
-        <v>0.06615</v>
+        <v>0.08904925027285596</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.258087071112084</v>
+        <v>0.9402383062504072</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.111976748660716</v>
+        <v>0.112704748660716</v>
       </c>
       <c r="C68">
-        <v>917.847463692442</v>
+        <v>720.7884319559316</v>
       </c>
       <c r="D68">
-        <v>7912.406719039377</v>
+        <v>7826.310706323274</v>
       </c>
       <c r="E68">
-        <v>2587.457353306126</v>
+        <v>2698.420372326534</v>
       </c>
       <c r="F68">
-        <v>7323.559255346934</v>
+        <v>7434.522274367342</v>
       </c>
       <c r="G68">
         <v>329</v>
@@ -8616,37 +8616,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M68">
-        <v>868.5741276841464</v>
+        <v>881.7343417399669</v>
       </c>
       <c r="N68">
-        <v>-51.9074610174797</v>
+        <v>-65.06767507330017</v>
       </c>
       <c r="O68">
-        <v>-13.75547716963212</v>
+        <v>-17.24293389442455</v>
       </c>
       <c r="P68">
-        <v>-38.15198384784758</v>
+        <v>-47.82474117887562</v>
       </c>
       <c r="Q68">
-        <v>261.8480161521524</v>
+        <v>252.1752588211244</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1564830690606795</v>
+        <v>0.1598371014564577</v>
       </c>
       <c r="T68">
-        <v>2.556190971378281</v>
+        <v>2.633651303844289</v>
       </c>
       <c r="U68">
         <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.2491631511563579</v>
+        <v>0.2454442981540242</v>
       </c>
       <c r="W68">
-        <v>0.08904925027285596</v>
+        <v>0.08949030623893274</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9402383062504072</v>
+        <v>0.9262048986944309</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.112704748660716</v>
+        <v>0.113432748660716</v>
       </c>
       <c r="C69">
-        <v>720.7884319559316</v>
+        <v>525.5828779649955</v>
       </c>
       <c r="D69">
-        <v>7826.310706323274</v>
+        <v>7742.068171352746</v>
       </c>
       <c r="E69">
-        <v>2698.420372326534</v>
+        <v>2809.383391346942</v>
       </c>
       <c r="F69">
-        <v>7434.522274367342</v>
+        <v>7545.48529338775</v>
       </c>
       <c r="G69">
         <v>329</v>
@@ -8698,37 +8698,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M69">
-        <v>881.7343417399669</v>
+        <v>894.8945557957873</v>
       </c>
       <c r="N69">
-        <v>-65.06767507330017</v>
+        <v>-78.22788912912051</v>
       </c>
       <c r="O69">
-        <v>-17.24293389442455</v>
+        <v>-20.73039061921694</v>
       </c>
       <c r="P69">
-        <v>-47.82474117887562</v>
+        <v>-57.49749850990358</v>
       </c>
       <c r="Q69">
-        <v>252.1752588211244</v>
+        <v>242.5025014900964</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1598371014564577</v>
+        <v>0.163400760876972</v>
       </c>
       <c r="T69">
-        <v>2.633651303844289</v>
+        <v>2.715952907089423</v>
       </c>
       <c r="U69">
         <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.2454442981540242</v>
+        <v>0.2418348231811709</v>
       </c>
       <c r="W69">
-        <v>0.08949030623893274</v>
+        <v>0.08991838997071314</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9262048986944309</v>
+        <v>0.9125842384195129</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.113432748660716</v>
+        <v>0.114160748660716</v>
       </c>
       <c r="C70">
-        <v>525.5828779649955</v>
+        <v>332.1715865197448</v>
       </c>
       <c r="D70">
-        <v>7742.068171352746</v>
+        <v>7659.619898927903</v>
       </c>
       <c r="E70">
-        <v>2809.383391346942</v>
+        <v>2920.34641036735</v>
       </c>
       <c r="F70">
-        <v>7545.48529338775</v>
+        <v>7656.448312408158</v>
       </c>
       <c r="G70">
         <v>329</v>
@@ -8780,37 +8780,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M70">
-        <v>894.8945557957873</v>
+        <v>908.0547698516076</v>
       </c>
       <c r="N70">
-        <v>-78.22788912912051</v>
+        <v>-91.38810318494086</v>
       </c>
       <c r="O70">
-        <v>-20.73039061921694</v>
+        <v>-24.21784734400933</v>
       </c>
       <c r="P70">
-        <v>-57.49749850990358</v>
+        <v>-67.17025584093153</v>
       </c>
       <c r="Q70">
-        <v>242.5025014900964</v>
+        <v>232.8297441590685</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.163400760876972</v>
+        <v>0.1671943338084872</v>
       </c>
       <c r="T70">
-        <v>2.715952907089423</v>
+        <v>2.803564291189082</v>
       </c>
       <c r="U70">
         <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2418348231811709</v>
+        <v>0.2383299706712989</v>
       </c>
       <c r="W70">
-        <v>0.08991838997071314</v>
+        <v>0.09033406547838396</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9125842384195129</v>
+        <v>0.8993583798916939</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.114160748660716</v>
+        <v>0.114888748660716</v>
       </c>
       <c r="C71">
-        <v>332.1715865197448</v>
+        <v>140.4978382631862</v>
       </c>
       <c r="D71">
-        <v>7659.619898927903</v>
+        <v>7578.909169691753</v>
       </c>
       <c r="E71">
-        <v>2920.34641036735</v>
+        <v>3031.309429387758</v>
       </c>
       <c r="F71">
-        <v>7656.448312408158</v>
+        <v>7767.411331428567</v>
       </c>
       <c r="G71">
         <v>329</v>
@@ -8862,37 +8862,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M71">
-        <v>908.0547698516076</v>
+        <v>921.2149839074281</v>
       </c>
       <c r="N71">
-        <v>-91.38810318494086</v>
+        <v>-104.5483172407613</v>
       </c>
       <c r="O71">
-        <v>-24.21784734400933</v>
+        <v>-27.70530406880175</v>
       </c>
       <c r="P71">
-        <v>-67.17025584093153</v>
+        <v>-76.84301317195957</v>
       </c>
       <c r="Q71">
-        <v>232.8297441590685</v>
+        <v>223.1569868280404</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1671943338084872</v>
+        <v>0.1712408116021035</v>
       </c>
       <c r="T71">
-        <v>2.803564291189082</v>
+        <v>2.897016434228718</v>
       </c>
       <c r="U71">
         <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.2383299706712989</v>
+        <v>0.234925256804566</v>
       </c>
       <c r="W71">
-        <v>0.09033406547838396</v>
+        <v>0.09073786454297848</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8993583798916939</v>
+        <v>0.8865104030360982</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.114888748660716</v>
+        <v>0.115616748660716</v>
       </c>
       <c r="C72">
-        <v>140.4978382631862</v>
+        <v>-49.49272044327063</v>
       </c>
       <c r="D72">
-        <v>7578.909169691753</v>
+        <v>7499.881630005704</v>
       </c>
       <c r="E72">
-        <v>3031.309429387758</v>
+        <v>3142.272448408166</v>
       </c>
       <c r="F72">
-        <v>7767.411331428567</v>
+        <v>7878.374350448975</v>
       </c>
       <c r="G72">
         <v>329</v>
@@ -8944,37 +8944,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M72">
-        <v>921.2149839074281</v>
+        <v>934.3751979632485</v>
       </c>
       <c r="N72">
-        <v>-104.5483172407613</v>
+        <v>-117.7085312965818</v>
       </c>
       <c r="O72">
-        <v>-27.70530406880175</v>
+        <v>-31.19276079359418</v>
       </c>
       <c r="P72">
-        <v>-76.84301317195957</v>
+        <v>-86.51577050298761</v>
       </c>
       <c r="Q72">
-        <v>223.1569868280404</v>
+        <v>213.4842294970124</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1712408116021035</v>
+        <v>0.1755663568297623</v>
       </c>
       <c r="T72">
-        <v>2.897016434228718</v>
+        <v>2.996913552650399</v>
       </c>
       <c r="U72">
         <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.234925256804566</v>
+        <v>0.2316164503706989</v>
       </c>
       <c r="W72">
-        <v>0.09073786454297848</v>
+        <v>0.09113028898603512</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8865104030360982</v>
+        <v>0.8740243410215052</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.115616748660716</v>
+        <v>0.116344748660716</v>
       </c>
       <c r="C73">
-        <v>-49.49272044326972</v>
+        <v>-237.8521995872161</v>
       </c>
       <c r="D73">
-        <v>7499.881630005704</v>
+        <v>7422.485169882166</v>
       </c>
       <c r="E73">
-        <v>3142.272448408165</v>
+        <v>3253.235467428573</v>
       </c>
       <c r="F73">
-        <v>7878.374350448974</v>
+        <v>7989.337369469382</v>
       </c>
       <c r="G73">
         <v>329</v>
@@ -9026,37 +9026,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M73">
-        <v>934.3751979632484</v>
+        <v>947.5354120190688</v>
       </c>
       <c r="N73">
-        <v>-117.7085312965817</v>
+        <v>-130.868745352402</v>
       </c>
       <c r="O73">
-        <v>-31.19276079359414</v>
+        <v>-34.68021751838653</v>
       </c>
       <c r="P73">
-        <v>-86.51577050298752</v>
+        <v>-96.18852783401547</v>
       </c>
       <c r="Q73">
-        <v>213.4842294970125</v>
+        <v>203.8114721659845</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1755663568297622</v>
+        <v>0.1802008695736823</v>
       </c>
       <c r="T73">
-        <v>2.996913552650398</v>
+        <v>3.103946179530769</v>
       </c>
       <c r="U73">
         <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.2316164503706989</v>
+        <v>0.2283995552266614</v>
       </c>
       <c r="W73">
-        <v>0.09113028898603512</v>
+        <v>0.09151181275011797</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8740243410215053</v>
+        <v>0.8618851140628734</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.116344748660716</v>
+        <v>0.117072748660716</v>
       </c>
       <c r="C74">
-        <v>-237.8521995872161</v>
+        <v>-424.630580091678</v>
       </c>
       <c r="D74">
-        <v>7422.485169882166</v>
+        <v>7346.669808398112</v>
       </c>
       <c r="E74">
-        <v>3253.235467428573</v>
+        <v>3364.198486448981</v>
       </c>
       <c r="F74">
-        <v>7989.337369469382</v>
+        <v>8100.30038848979</v>
       </c>
       <c r="G74">
         <v>329</v>
@@ -9108,37 +9108,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M74">
-        <v>947.5354120190688</v>
+        <v>960.6956260748892</v>
       </c>
       <c r="N74">
-        <v>-130.868745352402</v>
+        <v>-144.0289594082225</v>
       </c>
       <c r="O74">
-        <v>-34.68021751838653</v>
+        <v>-38.16767424317896</v>
       </c>
       <c r="P74">
-        <v>-96.18852783401547</v>
+        <v>-105.8612851650435</v>
       </c>
       <c r="Q74">
-        <v>203.8114721659845</v>
+        <v>194.1387148349565</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1802008695736823</v>
+        <v>0.1851786795578927</v>
       </c>
       <c r="T74">
-        <v>3.103946179530769</v>
+        <v>3.218907149143019</v>
       </c>
       <c r="U74">
         <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.2283995552266614</v>
+        <v>0.2252707941961592</v>
       </c>
       <c r="W74">
-        <v>0.09151181275011797</v>
+        <v>0.09188288380833554</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8618851140628734</v>
+        <v>0.8500784686647517</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.117072748660716</v>
+        <v>0.117800748660716</v>
       </c>
       <c r="C75">
-        <v>-424.630580091678</v>
+        <v>-609.8758214500285</v>
       </c>
       <c r="D75">
-        <v>7346.669808398112</v>
+        <v>7272.387586060169</v>
       </c>
       <c r="E75">
-        <v>3364.198486448981</v>
+        <v>3475.161505469389</v>
       </c>
       <c r="F75">
-        <v>8100.30038848979</v>
+        <v>8211.263407510198</v>
       </c>
       <c r="G75">
         <v>329</v>
@@ -9190,37 +9190,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M75">
-        <v>960.6956260748892</v>
+        <v>973.8558401307096</v>
       </c>
       <c r="N75">
-        <v>-144.0289594082225</v>
+        <v>-157.1891734640428</v>
       </c>
       <c r="O75">
-        <v>-38.16767424317896</v>
+        <v>-41.65513096797135</v>
       </c>
       <c r="P75">
-        <v>-105.8612851650435</v>
+        <v>-115.5340424960715</v>
       </c>
       <c r="Q75">
-        <v>194.1387148349565</v>
+        <v>184.4659575039285</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1851786795578927</v>
+        <v>0.1905393980024271</v>
       </c>
       <c r="T75">
-        <v>3.218907149143019</v>
+        <v>3.342711270263905</v>
       </c>
       <c r="U75">
         <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.2252707941961592</v>
+        <v>0.2222265942745895</v>
       </c>
       <c r="W75">
-        <v>0.09188288380833554</v>
+        <v>0.09224392591903369</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8500784686647517</v>
+        <v>0.8385909217909038</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.117800748660716</v>
+        <v>0.118528748660716</v>
       </c>
       <c r="C76">
-        <v>-609.8758214500285</v>
+        <v>-793.633962896507</v>
       </c>
       <c r="D76">
-        <v>7272.387586060169</v>
+        <v>7199.592463634099</v>
       </c>
       <c r="E76">
-        <v>3475.161505469389</v>
+        <v>3586.124524489797</v>
       </c>
       <c r="F76">
-        <v>8211.263407510198</v>
+        <v>8322.226426530606</v>
       </c>
       <c r="G76">
         <v>329</v>
@@ -9272,37 +9272,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M76">
-        <v>973.8558401307096</v>
+        <v>987.0160541865299</v>
       </c>
       <c r="N76">
-        <v>-157.1891734640428</v>
+        <v>-170.3493875198632</v>
       </c>
       <c r="O76">
-        <v>-41.65513096797135</v>
+        <v>-45.14258769276374</v>
       </c>
       <c r="P76">
-        <v>-115.5340424960715</v>
+        <v>-125.2067998270994</v>
       </c>
       <c r="Q76">
-        <v>184.4659575039285</v>
+        <v>174.7932001729006</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1905393980024271</v>
+        <v>0.1963289739225241</v>
       </c>
       <c r="T76">
-        <v>3.342711270263905</v>
+        <v>3.476419721074461</v>
       </c>
       <c r="U76">
         <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.2222265942745895</v>
+        <v>0.219263573017595</v>
       </c>
       <c r="W76">
-        <v>0.09224392591903369</v>
+        <v>0.09259534024011323</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8385909217909038</v>
+        <v>0.8274097095003584</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.118528748660716</v>
+        <v>0.119256748660716</v>
       </c>
       <c r="C77">
-        <v>-793.633962896507</v>
+        <v>-975.9492185607442</v>
       </c>
       <c r="D77">
-        <v>7199.592463634099</v>
+        <v>7128.24022699027</v>
       </c>
       <c r="E77">
-        <v>3586.124524489797</v>
+        <v>3697.087543510205</v>
       </c>
       <c r="F77">
-        <v>8322.226426530606</v>
+        <v>8433.189445551014</v>
       </c>
       <c r="G77">
         <v>329</v>
@@ -9354,37 +9354,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M77">
-        <v>987.0160541865299</v>
+        <v>1000.17626824235</v>
       </c>
       <c r="N77">
-        <v>-170.3493875198632</v>
+        <v>-183.5096015756836</v>
       </c>
       <c r="O77">
-        <v>-45.14258769276374</v>
+        <v>-48.63004441755616</v>
       </c>
       <c r="P77">
-        <v>-125.2067998270994</v>
+        <v>-134.8795571581275</v>
       </c>
       <c r="Q77">
-        <v>174.7932001729006</v>
+        <v>165.1204428418725</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1963289739225241</v>
+        <v>0.2026010145026293</v>
       </c>
       <c r="T77">
-        <v>3.476419721074461</v>
+        <v>3.621270542785897</v>
       </c>
       <c r="U77">
         <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.219263573017595</v>
+        <v>0.2163785260042056</v>
       </c>
       <c r="W77">
-        <v>0.09259534024011323</v>
+        <v>0.09293750681590122</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8274097095003584</v>
+        <v>0.8165227396385115</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.119256748660716</v>
+        <v>0.119984748660716</v>
       </c>
       <c r="C78">
-        <v>-975.9492185607442</v>
+        <v>-1156.864067019606</v>
       </c>
       <c r="D78">
-        <v>7128.24022699027</v>
+        <v>7058.288397551815</v>
       </c>
       <c r="E78">
-        <v>3697.087543510205</v>
+        <v>3808.050562530613</v>
       </c>
       <c r="F78">
-        <v>8433.189445551014</v>
+        <v>8544.152464571422</v>
       </c>
       <c r="G78">
         <v>329</v>
@@ -9436,37 +9436,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M78">
-        <v>1000.17626824235</v>
+        <v>1013.336482298171</v>
       </c>
       <c r="N78">
-        <v>-183.5096015756836</v>
+        <v>-196.669815631504</v>
       </c>
       <c r="O78">
-        <v>-48.63004441755616</v>
+        <v>-52.11750114234856</v>
       </c>
       <c r="P78">
-        <v>-134.8795571581275</v>
+        <v>-144.5523144891554</v>
       </c>
       <c r="Q78">
-        <v>165.1204428418725</v>
+        <v>155.4476855108446</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2026010145026293</v>
+        <v>0.2094184499157871</v>
       </c>
       <c r="T78">
-        <v>3.621270542785897</v>
+        <v>3.778717088124415</v>
       </c>
       <c r="U78">
         <v>0.1186</v>
       </c>
       <c r="V78">
-        <v>0.2163785260042056</v>
+        <v>0.2135684152768782</v>
       </c>
       <c r="W78">
-        <v>0.09293750681590122</v>
+        <v>0.09327078594816225</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8165227396385115</v>
+        <v>0.8059185482146348</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.119984748660716</v>
+        <v>0.1878607006484145</v>
       </c>
       <c r="C79">
-        <v>-1156.864067019606</v>
+        <v>-4640.244948269557</v>
       </c>
       <c r="D79">
-        <v>7058.288397551815</v>
+        <v>3685.870535322275</v>
       </c>
       <c r="E79">
-        <v>3808.050562530613</v>
+        <v>3919.013581551023</v>
       </c>
       <c r="F79">
-        <v>8544.152464571422</v>
+        <v>8655.115483591831</v>
       </c>
       <c r="G79">
         <v>329</v>
@@ -9518,45 +9518,45 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M79">
-        <v>1013.336482298171</v>
+        <v>1737.94718910524</v>
       </c>
       <c r="N79">
-        <v>-196.669815631504</v>
+        <v>-921.2805224385731</v>
       </c>
       <c r="O79">
-        <v>-52.11750114234856</v>
+        <v>-244.1393384462219</v>
       </c>
       <c r="P79">
-        <v>-144.5523144891554</v>
+        <v>-677.1411839923512</v>
       </c>
       <c r="Q79">
-        <v>155.4476855108446</v>
+        <v>-377.1411839923512</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2094184499157871</v>
+        <v>0.2306372521287709</v>
       </c>
       <c r="T79">
-        <v>3.778717088124415</v>
+        <v>4.268758709671384</v>
       </c>
       <c r="U79">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.2135684152768782</v>
+        <v>0.1245243054698837</v>
       </c>
       <c r="W79">
-        <v>0.09327078594816225</v>
+        <v>0.1757955194616474</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8059185482146348</v>
+        <v>0.4699030395089953</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1878607006484145</v>
+        <v>0.1894107006484145</v>
       </c>
       <c r="C80">
-        <v>-4640.244948269557</v>
+        <v>-4790.989817137883</v>
       </c>
       <c r="D80">
-        <v>3685.870535322275</v>
+        <v>3646.088685474357</v>
       </c>
       <c r="E80">
-        <v>3919.013581551023</v>
+        <v>4029.976600571431</v>
       </c>
       <c r="F80">
-        <v>8655.115483591831</v>
+        <v>8766.078502612239</v>
       </c>
       <c r="G80">
         <v>329</v>
@@ -9600,37 +9600,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M80">
-        <v>1737.94718910524</v>
+        <v>1760.228563324538</v>
       </c>
       <c r="N80">
-        <v>-921.2805224385731</v>
+        <v>-943.5618966578709</v>
       </c>
       <c r="O80">
-        <v>-244.1393384462219</v>
+        <v>-250.0439026143358</v>
       </c>
       <c r="P80">
-        <v>-677.1411839923512</v>
+        <v>-693.5179940435351</v>
       </c>
       <c r="Q80">
-        <v>-377.1411839923512</v>
+        <v>-393.5179940435351</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2306372521287709</v>
+        <v>0.2394390260396647</v>
       </c>
       <c r="T80">
-        <v>4.268758709671384</v>
+        <v>4.47203293394145</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1245243054698837</v>
+        <v>0.1229480484386194</v>
       </c>
       <c r="W80">
-        <v>0.1757955194616474</v>
+        <v>0.1761120318735252</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4699030395089953</v>
+        <v>0.4639548997683751</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -9646,22 +9646,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1894107006484145</v>
+        <v>0.1909607006484145</v>
       </c>
       <c r="C81">
-        <v>-4790.989817137883</v>
+        <v>-4940.885119050567</v>
       </c>
       <c r="D81">
-        <v>3646.088685474357</v>
+        <v>3607.15640258208</v>
       </c>
       <c r="E81">
-        <v>4029.976600571431</v>
+        <v>4140.939619591839</v>
       </c>
       <c r="F81">
-        <v>8766.078502612239</v>
+        <v>8877.041521632647</v>
       </c>
       <c r="G81">
         <v>329</v>
@@ -9682,37 +9682,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M81">
-        <v>1760.228563324538</v>
+        <v>1782.509937543836</v>
       </c>
       <c r="N81">
-        <v>-943.5618966578709</v>
+        <v>-965.8432708771688</v>
       </c>
       <c r="O81">
-        <v>-250.0439026143358</v>
+        <v>-255.9484667824497</v>
       </c>
       <c r="P81">
-        <v>-693.5179940435351</v>
+        <v>-709.8948040947191</v>
       </c>
       <c r="Q81">
-        <v>-393.5179940435351</v>
+        <v>-409.8948040947191</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2394390260396647</v>
+        <v>0.249120977341648</v>
       </c>
       <c r="T81">
-        <v>4.47203293394145</v>
+        <v>4.695634580638522</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1229480484386194</v>
+        <v>0.1214111978331367</v>
       </c>
       <c r="W81">
-        <v>0.1761120318735252</v>
+        <v>0.1764206314751061</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4639548997683751</v>
+        <v>0.4581554635212705</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -9728,22 +9728,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1909607006484145</v>
+        <v>0.1925107006484145</v>
       </c>
       <c r="C82">
-        <v>-4940.885119050567</v>
+        <v>-5089.95778105742</v>
       </c>
       <c r="D82">
-        <v>3607.15640258208</v>
+        <v>3569.046759595635</v>
       </c>
       <c r="E82">
-        <v>4140.939619591839</v>
+        <v>4251.902638612247</v>
       </c>
       <c r="F82">
-        <v>8877.041521632647</v>
+        <v>8988.004540653055</v>
       </c>
       <c r="G82">
         <v>329</v>
@@ -9764,37 +9764,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M82">
-        <v>1782.509937543836</v>
+        <v>1804.791311763134</v>
       </c>
       <c r="N82">
-        <v>-965.8432708771688</v>
+        <v>-988.1246450964668</v>
       </c>
       <c r="O82">
-        <v>-255.9484667824497</v>
+        <v>-261.8530309505637</v>
       </c>
       <c r="P82">
-        <v>-709.8948040947191</v>
+        <v>-726.2716141459031</v>
       </c>
       <c r="Q82">
-        <v>-409.8948040947191</v>
+        <v>-426.2716141459031</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.249120977341648</v>
+        <v>0.259822081412261</v>
       </c>
       <c r="T82">
-        <v>4.695634580638522</v>
+        <v>4.942773242777393</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1214111978331367</v>
+        <v>0.1199122941561843</v>
       </c>
       <c r="W82">
-        <v>0.1764206314751061</v>
+        <v>0.1767216113334382</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4581554635212705</v>
+        <v>0.4524992232308843</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -9810,22 +9810,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1925107006484145</v>
+        <v>0.1940607006484145</v>
       </c>
       <c r="C83">
-        <v>-5089.95778105742</v>
+        <v>-5238.2336041667</v>
       </c>
       <c r="D83">
-        <v>3569.046759595635</v>
+        <v>3531.733955506763</v>
       </c>
       <c r="E83">
-        <v>4251.902638612247</v>
+        <v>4362.865657632655</v>
       </c>
       <c r="F83">
-        <v>8988.004540653055</v>
+        <v>9098.967559673463</v>
       </c>
       <c r="G83">
         <v>329</v>
@@ -9846,37 +9846,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M83">
-        <v>1804.791311763134</v>
+        <v>1827.072685982431</v>
       </c>
       <c r="N83">
-        <v>-988.1246450964668</v>
+        <v>-1010.406019315765</v>
       </c>
       <c r="O83">
-        <v>-261.8530309505637</v>
+        <v>-267.7575951186777</v>
       </c>
       <c r="P83">
-        <v>-726.2716141459031</v>
+        <v>-742.648424197087</v>
       </c>
       <c r="Q83">
-        <v>-426.2716141459031</v>
+        <v>-442.648424197087</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.259822081412261</v>
+        <v>0.2717121970462755</v>
       </c>
       <c r="T83">
-        <v>4.942773242777393</v>
+        <v>5.217371756265025</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1199122941561843</v>
+        <v>0.1184499491054992</v>
       </c>
       <c r="W83">
-        <v>0.1767216113334382</v>
+        <v>0.1770152502196158</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4524992232308843</v>
+        <v>0.4469809400207516</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -9892,22 +9892,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1940607006484145</v>
+        <v>0.1956107006484145</v>
       </c>
       <c r="C84">
-        <v>-5238.2336041667</v>
+        <v>-5385.737321597448</v>
       </c>
       <c r="D84">
-        <v>3531.733955506763</v>
+        <v>3495.193257096423</v>
       </c>
       <c r="E84">
-        <v>4362.865657632655</v>
+        <v>4473.828676653063</v>
       </c>
       <c r="F84">
-        <v>9098.967559673463</v>
+        <v>9209.930578693871</v>
       </c>
       <c r="G84">
         <v>329</v>
@@ -9928,37 +9928,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M84">
-        <v>1827.072685982431</v>
+        <v>1849.354060201729</v>
       </c>
       <c r="N84">
-        <v>-1010.406019315765</v>
+        <v>-1032.687393535063</v>
       </c>
       <c r="O84">
-        <v>-267.7575951186777</v>
+        <v>-273.6621592867916</v>
       </c>
       <c r="P84">
-        <v>-742.648424197087</v>
+        <v>-759.0252342482711</v>
       </c>
       <c r="Q84">
-        <v>-442.648424197087</v>
+        <v>-459.0252342482711</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2717121970462755</v>
+        <v>0.2850011498137035</v>
       </c>
       <c r="T84">
-        <v>5.217371756265025</v>
+        <v>5.524275977221792</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1184499491054992</v>
+        <v>0.117022841284951</v>
       </c>
       <c r="W84">
-        <v>0.1770152502196158</v>
+        <v>0.1773018134699818</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4469809400207516</v>
+        <v>0.4415956274903811</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -9974,22 +9974,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1956107006484145</v>
+        <v>0.1971607006484145</v>
       </c>
       <c r="C85">
-        <v>-5385.737321597448</v>
+        <v>-5532.492653452637</v>
       </c>
       <c r="D85">
-        <v>3495.193257096423</v>
+        <v>3459.400944261643</v>
       </c>
       <c r="E85">
-        <v>4473.828676653063</v>
+        <v>4584.791695673471</v>
       </c>
       <c r="F85">
-        <v>9209.930578693871</v>
+        <v>9320.893597714279</v>
       </c>
       <c r="G85">
         <v>329</v>
@@ -10010,37 +10010,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M85">
-        <v>1849.354060201729</v>
+        <v>1871.635434421027</v>
       </c>
       <c r="N85">
-        <v>-1032.687393535063</v>
+        <v>-1054.968767754361</v>
       </c>
       <c r="O85">
-        <v>-273.6621592867916</v>
+        <v>-279.5667234549056</v>
       </c>
       <c r="P85">
-        <v>-759.0252342482711</v>
+        <v>-775.4020442994552</v>
       </c>
       <c r="Q85">
-        <v>-459.0252342482711</v>
+        <v>-475.4020442994552</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2850011498137035</v>
+        <v>0.2999512216770601</v>
       </c>
       <c r="T85">
-        <v>5.524275977221792</v>
+        <v>5.869543225798155</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.117022841284951</v>
+        <v>0.1156297122220349</v>
       </c>
       <c r="W85">
-        <v>0.1773018134699818</v>
+        <v>0.1775815537858154</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4415956274903811</v>
+        <v>0.4363385366869241</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -10056,22 +10056,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1971607006484145</v>
+        <v>0.1987107006484145</v>
       </c>
       <c r="C86">
-        <v>-5532.492653452636</v>
+        <v>-5678.522358067105</v>
       </c>
       <c r="D86">
-        <v>3459.400944261643</v>
+        <v>3424.334258667583</v>
       </c>
       <c r="E86">
-        <v>4584.791695673471</v>
+        <v>4695.754714693879</v>
       </c>
       <c r="F86">
-        <v>9320.893597714279</v>
+        <v>9431.856616734687</v>
       </c>
       <c r="G86">
         <v>329</v>
@@ -10092,37 +10092,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M86">
-        <v>1871.635434421027</v>
+        <v>1893.916808640325</v>
       </c>
       <c r="N86">
-        <v>-1054.968767754361</v>
+        <v>-1077.250141973658</v>
       </c>
       <c r="O86">
-        <v>-279.5667234549056</v>
+        <v>-285.4712876230195</v>
       </c>
       <c r="P86">
-        <v>-775.4020442994552</v>
+        <v>-791.778854350639</v>
       </c>
       <c r="Q86">
-        <v>-475.4020442994552</v>
+        <v>-491.778854350639</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2999512216770598</v>
+        <v>0.3168946364555305</v>
       </c>
       <c r="T86">
-        <v>5.86954322579815</v>
+        <v>6.260846107518027</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1156297122220349</v>
+        <v>0.1142693626664816</v>
       </c>
       <c r="W86">
-        <v>0.1775815537858154</v>
+        <v>0.1778547119765705</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4363385366869241</v>
+        <v>0.4312051421376663</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -10138,22 +10138,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1987107006484145</v>
+        <v>0.2002607006484145</v>
       </c>
       <c r="C87">
-        <v>-5678.522358067105</v>
+        <v>-5823.848280263877</v>
       </c>
       <c r="D87">
-        <v>3424.334258667583</v>
+        <v>3389.971355491218</v>
       </c>
       <c r="E87">
-        <v>4695.754714693879</v>
+        <v>4806.717733714287</v>
       </c>
       <c r="F87">
-        <v>9431.856616734687</v>
+        <v>9542.819635755095</v>
       </c>
       <c r="G87">
         <v>329</v>
@@ -10174,37 +10174,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M87">
-        <v>1893.916808640325</v>
+        <v>1916.198182859623</v>
       </c>
       <c r="N87">
-        <v>-1077.250141973658</v>
+        <v>-1099.531516192956</v>
       </c>
       <c r="O87">
-        <v>-285.4712876230195</v>
+        <v>-291.3758517911335</v>
       </c>
       <c r="P87">
-        <v>-791.778854350639</v>
+        <v>-808.1556644018228</v>
       </c>
       <c r="Q87">
-        <v>-491.778854350639</v>
+        <v>-508.1556644018228</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3168946364555305</v>
+        <v>0.336258539059497</v>
       </c>
       <c r="T87">
-        <v>6.260846107518027</v>
+        <v>6.708049400912173</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1142693626664816</v>
+        <v>0.1129406491471039</v>
       </c>
       <c r="W87">
-        <v>0.1778547119765705</v>
+        <v>0.1781215176512616</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4312051421376663</v>
+        <v>0.4261911288569957</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -10220,22 +10220,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2002607006484145</v>
+        <v>0.2018107006484145</v>
       </c>
       <c r="C88">
-        <v>-5823.848280263877</v>
+        <v>-5968.491396733835</v>
       </c>
       <c r="D88">
-        <v>3389.971355491218</v>
+        <v>3356.291258041668</v>
       </c>
       <c r="E88">
-        <v>4806.717733714287</v>
+        <v>4917.680752734695</v>
       </c>
       <c r="F88">
-        <v>9542.819635755095</v>
+        <v>9653.782654775503</v>
       </c>
       <c r="G88">
         <v>329</v>
@@ -10256,37 +10256,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M88">
-        <v>1916.198182859623</v>
+        <v>1938.479557078921</v>
       </c>
       <c r="N88">
-        <v>-1099.531516192956</v>
+        <v>-1121.812890412254</v>
       </c>
       <c r="O88">
-        <v>-291.3758517911335</v>
+        <v>-297.2804159592474</v>
       </c>
       <c r="P88">
-        <v>-808.1556644018228</v>
+        <v>-824.5324744530069</v>
       </c>
       <c r="Q88">
-        <v>-508.1556644018228</v>
+        <v>-524.5324744530069</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.336258539059497</v>
+        <v>0.3586015036025352</v>
       </c>
       <c r="T88">
-        <v>6.708049400912173</v>
+        <v>7.224053200982339</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1129406491471039</v>
+        <v>0.1116424807661027</v>
       </c>
       <c r="W88">
-        <v>0.1781215176512616</v>
+        <v>0.1783821898621666</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4261911288569957</v>
+        <v>0.421292380249444</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -10302,22 +10302,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2018107006484145</v>
+        <v>0.2033607006484145</v>
       </c>
       <c r="C89">
-        <v>-5968.491396733835</v>
+        <v>-6112.471858736889</v>
       </c>
       <c r="D89">
-        <v>3356.291258041668</v>
+        <v>3323.273815059022</v>
       </c>
       <c r="E89">
-        <v>4917.680752734695</v>
+        <v>5028.643771755103</v>
       </c>
       <c r="F89">
-        <v>9653.782654775503</v>
+        <v>9764.745673795911</v>
       </c>
       <c r="G89">
         <v>329</v>
@@ -10338,37 +10338,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M89">
-        <v>1938.479557078921</v>
+        <v>1960.760931298219</v>
       </c>
       <c r="N89">
-        <v>-1121.812890412254</v>
+        <v>-1144.094264631552</v>
       </c>
       <c r="O89">
-        <v>-297.2804159592474</v>
+        <v>-303.1849801273614</v>
       </c>
       <c r="P89">
-        <v>-824.5324744530069</v>
+        <v>-840.909284504191</v>
       </c>
       <c r="Q89">
-        <v>-524.5324744530069</v>
+        <v>-540.909284504191</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3586015036025352</v>
+        <v>0.3846682955694132</v>
       </c>
       <c r="T89">
-        <v>7.224053200982339</v>
+        <v>7.826057634397536</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1116424807661027</v>
+        <v>0.1103738162119424</v>
       </c>
       <c r="W89">
-        <v>0.1783821898621666</v>
+        <v>0.178636937704642</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.421292380249444</v>
+        <v>0.4165049668375186</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -10384,22 +10384,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2033607006484145</v>
+        <v>0.2049107006484145</v>
       </c>
       <c r="C90">
-        <v>-6112.471858736889</v>
+        <v>-6255.80903230724</v>
       </c>
       <c r="D90">
-        <v>3323.273815059022</v>
+        <v>3290.899660509079</v>
       </c>
       <c r="E90">
-        <v>5028.643771755103</v>
+        <v>5139.60679077551</v>
       </c>
       <c r="F90">
-        <v>9764.745673795911</v>
+        <v>9875.708692816319</v>
       </c>
       <c r="G90">
         <v>329</v>
@@ -10420,37 +10420,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M90">
-        <v>1960.760931298219</v>
+        <v>1983.042305517517</v>
       </c>
       <c r="N90">
-        <v>-1144.094264631552</v>
+        <v>-1166.37563885085</v>
       </c>
       <c r="O90">
-        <v>-303.1849801273614</v>
+        <v>-309.0895442954753</v>
       </c>
       <c r="P90">
-        <v>-840.909284504191</v>
+        <v>-857.2860945553749</v>
       </c>
       <c r="Q90">
-        <v>-540.909284504191</v>
+        <v>-557.2860945553749</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3846682955694132</v>
+        <v>0.4154745042575418</v>
       </c>
       <c r="T90">
-        <v>7.826057634397536</v>
+        <v>8.537517419342768</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1103738162119424</v>
+        <v>0.109133660973606</v>
       </c>
       <c r="W90">
-        <v>0.178636937704642</v>
+        <v>0.1788859608764999</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4165049668375186</v>
+        <v>0.4118251357494566</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -10466,22 +10466,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2049107006484145</v>
+        <v>0.2064607006484145</v>
       </c>
       <c r="C91">
-        <v>-6255.80903230724</v>
+        <v>-6398.521536131349</v>
       </c>
       <c r="D91">
-        <v>3290.899660509079</v>
+        <v>3259.150175705377</v>
       </c>
       <c r="E91">
-        <v>5139.60679077551</v>
+        <v>5250.569809795918</v>
       </c>
       <c r="F91">
-        <v>9875.708692816319</v>
+        <v>9986.671711836727</v>
       </c>
       <c r="G91">
         <v>329</v>
@@ -10502,37 +10502,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M91">
-        <v>1983.042305517517</v>
+        <v>2005.323679736815</v>
       </c>
       <c r="N91">
-        <v>-1166.37563885085</v>
+        <v>-1188.657013070148</v>
       </c>
       <c r="O91">
-        <v>-309.0895442954753</v>
+        <v>-314.9941084635892</v>
       </c>
       <c r="P91">
-        <v>-857.2860945553749</v>
+        <v>-873.6629046065588</v>
       </c>
       <c r="Q91">
-        <v>-557.2860945553749</v>
+        <v>-573.6629046065588</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4154745042575418</v>
+        <v>0.452441954683296</v>
       </c>
       <c r="T91">
-        <v>8.537517419342768</v>
+        <v>9.391269161277044</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.109133660973606</v>
+        <v>0.1079210647405659</v>
       </c>
       <c r="W91">
-        <v>0.1788859608764999</v>
+        <v>0.1791294502000944</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4118251357494566</v>
+        <v>0.407249300907796</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -10548,22 +10548,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2064607006484145</v>
+        <v>0.2080107006484145</v>
       </c>
       <c r="C92">
-        <v>-6398.521536131349</v>
+        <v>-6540.627277254247</v>
       </c>
       <c r="D92">
-        <v>3259.150175705377</v>
+        <v>3228.007453602889</v>
       </c>
       <c r="E92">
-        <v>5250.569809795918</v>
+        <v>5361.532828816328</v>
       </c>
       <c r="F92">
-        <v>9986.671711836727</v>
+        <v>10097.63473085714</v>
       </c>
       <c r="G92">
         <v>329</v>
@@ -10584,37 +10584,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M92">
-        <v>2005.323679736815</v>
+        <v>2027.605053956113</v>
       </c>
       <c r="N92">
-        <v>-1188.657013070148</v>
+        <v>-1210.938387289446</v>
       </c>
       <c r="O92">
-        <v>-314.9941084635892</v>
+        <v>-320.8986726317033</v>
       </c>
       <c r="P92">
-        <v>-873.6629046065588</v>
+        <v>-890.039714657743</v>
       </c>
       <c r="Q92">
-        <v>-573.6629046065588</v>
+        <v>-590.039714657743</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.452441954683296</v>
+        <v>0.497624394092551</v>
       </c>
       <c r="T92">
-        <v>9.391269161277044</v>
+        <v>10.43474351253005</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1079210647405659</v>
+        <v>0.1067351189741861</v>
       </c>
       <c r="W92">
-        <v>0.1791294502000944</v>
+        <v>0.1793675881099834</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.407249300907796</v>
+        <v>0.4027740338648531</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -10630,22 +10630,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2080107006484145</v>
+        <v>0.2095607006484145</v>
       </c>
       <c r="C93">
-        <v>-6540.627277254247</v>
+        <v>-6682.143484758053</v>
       </c>
       <c r="D93">
-        <v>3228.007453602889</v>
+        <v>3197.454265119491</v>
       </c>
       <c r="E93">
-        <v>5361.532828816328</v>
+        <v>5472.495847836736</v>
       </c>
       <c r="F93">
-        <v>10097.63473085714</v>
+        <v>10208.59774987754</v>
       </c>
       <c r="G93">
         <v>329</v>
@@ -10666,37 +10666,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M93">
-        <v>2027.605053956113</v>
+        <v>2049.886428175411</v>
       </c>
       <c r="N93">
-        <v>-1210.938387289446</v>
+        <v>-1233.219761508744</v>
       </c>
       <c r="O93">
-        <v>-320.8986726317033</v>
+        <v>-326.8032367998172</v>
       </c>
       <c r="P93">
-        <v>-890.039714657743</v>
+        <v>-906.4165247089269</v>
       </c>
       <c r="Q93">
-        <v>-590.039714657743</v>
+        <v>-606.4165247089269</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.497624394092551</v>
+        <v>0.5541024433541201</v>
       </c>
       <c r="T93">
-        <v>10.43474351253005</v>
+        <v>11.73908645159631</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1067351189741861</v>
+        <v>0.1055749546375102</v>
       </c>
       <c r="W93">
-        <v>0.1793675881099834</v>
+        <v>0.1796005491087879</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4027740338648531</v>
+        <v>0.3983960552358873</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -10712,22 +10712,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2095607006484145</v>
+        <v>0.2111107006484145</v>
       </c>
       <c r="C94">
-        <v>-6682.143484758053</v>
+        <v>-6823.086741545863</v>
       </c>
       <c r="D94">
-        <v>3197.454265119491</v>
+        <v>3167.474027352089</v>
       </c>
       <c r="E94">
-        <v>5472.495847836736</v>
+        <v>5583.458866857144</v>
       </c>
       <c r="F94">
-        <v>10208.59774987754</v>
+        <v>10319.56076889795</v>
       </c>
       <c r="G94">
         <v>329</v>
@@ -10748,37 +10748,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M94">
-        <v>2049.886428175411</v>
+        <v>2072.167802394709</v>
       </c>
       <c r="N94">
-        <v>-1233.219761508744</v>
+        <v>-1255.501135728042</v>
       </c>
       <c r="O94">
-        <v>-326.8032367998172</v>
+        <v>-332.7078009679312</v>
       </c>
       <c r="P94">
-        <v>-906.4165247089269</v>
+        <v>-922.7933347601108</v>
       </c>
       <c r="Q94">
-        <v>-606.4165247089269</v>
+        <v>-622.7933347601108</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5541024433541201</v>
+        <v>0.6267170781189944</v>
       </c>
       <c r="T94">
-        <v>11.73908645159631</v>
+        <v>13.41609880182435</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1055749546375102</v>
+        <v>0.1044397400715154</v>
       </c>
       <c r="W94">
-        <v>0.1796005491087879</v>
+        <v>0.1798285001936397</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3983960552358873</v>
+        <v>0.3941122266849638</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -10794,22 +10794,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2111107006484145</v>
+        <v>0.2126607006484145</v>
       </c>
       <c r="C95">
-        <v>-6823.086741545863</v>
+        <v>-6963.473014354116</v>
       </c>
       <c r="D95">
-        <v>3167.474027352089</v>
+        <v>3138.050773564245</v>
       </c>
       <c r="E95">
-        <v>5583.458866857144</v>
+        <v>5694.421885877552</v>
       </c>
       <c r="F95">
-        <v>10319.56076889795</v>
+        <v>10430.52378791836</v>
       </c>
       <c r="G95">
         <v>329</v>
@@ -10830,37 +10830,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M95">
-        <v>2072.167802394709</v>
+        <v>2094.449176614007</v>
       </c>
       <c r="N95">
-        <v>-1255.501135728042</v>
+        <v>-1277.78250994734</v>
       </c>
       <c r="O95">
-        <v>-332.7078009679312</v>
+        <v>-338.6123651360451</v>
       </c>
       <c r="P95">
-        <v>-922.7933347601108</v>
+        <v>-939.1701448112949</v>
       </c>
       <c r="Q95">
-        <v>-622.7933347601108</v>
+        <v>-639.1701448112949</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6267170781189944</v>
+        <v>0.7235365911388271</v>
       </c>
       <c r="T95">
-        <v>13.41609880182435</v>
+        <v>15.65211526879509</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1044397400715154</v>
+        <v>0.1033286790069248</v>
       </c>
       <c r="W95">
-        <v>0.1798285001936397</v>
+        <v>0.1800516012554095</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3941122266849638</v>
+        <v>0.3899195434223578</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -10876,22 +10876,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2126607006484145</v>
+        <v>0.2142107006484145</v>
       </c>
       <c r="C96">
-        <v>-6963.473014354116</v>
+        <v>-7103.317682107634</v>
       </c>
       <c r="D96">
-        <v>3138.050773564245</v>
+        <v>3109.169124831134</v>
       </c>
       <c r="E96">
-        <v>5694.421885877552</v>
+        <v>5805.38490489796</v>
       </c>
       <c r="F96">
-        <v>10430.52378791836</v>
+        <v>10541.48680693877</v>
       </c>
       <c r="G96">
         <v>329</v>
@@ -10912,37 +10912,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M96">
-        <v>2094.449176614007</v>
+        <v>2116.730550833305</v>
       </c>
       <c r="N96">
-        <v>-1277.78250994734</v>
+        <v>-1300.063884166638</v>
       </c>
       <c r="O96">
-        <v>-338.6123651360451</v>
+        <v>-344.5169293041591</v>
       </c>
       <c r="P96">
-        <v>-939.1701448112949</v>
+        <v>-955.546954862479</v>
       </c>
       <c r="Q96">
-        <v>-639.1701448112949</v>
+        <v>-655.546954862479</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7235365911388271</v>
+        <v>0.8590839093665927</v>
       </c>
       <c r="T96">
-        <v>15.65211526879509</v>
+        <v>18.78253832255411</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1033286790069248</v>
+        <v>0.1022410087015888</v>
       </c>
       <c r="W96">
-        <v>0.1800516012554095</v>
+        <v>0.180270005452721</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3899195434223578</v>
+        <v>0.3858151271758067</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -10958,22 +10958,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2142107006484145</v>
+        <v>0.2157607006484145</v>
       </c>
       <c r="C97">
-        <v>-7103.317682107634</v>
+        <v>-7242.635562723121</v>
       </c>
       <c r="D97">
-        <v>3109.169124831134</v>
+        <v>3080.814263236055</v>
       </c>
       <c r="E97">
-        <v>5805.38490489796</v>
+        <v>5916.347923918368</v>
       </c>
       <c r="F97">
-        <v>10541.48680693877</v>
+        <v>10652.44982595918</v>
       </c>
       <c r="G97">
         <v>329</v>
@@ -10994,37 +10994,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M97">
-        <v>2116.730550833305</v>
+        <v>2139.011925052603</v>
       </c>
       <c r="N97">
-        <v>-1300.063884166638</v>
+        <v>-1322.345258385936</v>
       </c>
       <c r="O97">
-        <v>-344.5169293041591</v>
+        <v>-350.421493472273</v>
       </c>
       <c r="P97">
-        <v>-955.546954862479</v>
+        <v>-971.9237649136629</v>
       </c>
       <c r="Q97">
-        <v>-655.546954862479</v>
+        <v>-671.9237649136629</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8590839093665927</v>
+        <v>1.062404886708242</v>
       </c>
       <c r="T97">
-        <v>18.78253832255411</v>
+        <v>23.47817290319265</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1022410087015888</v>
+        <v>0.1011759981942806</v>
       </c>
       <c r="W97">
-        <v>0.180270005452721</v>
+        <v>0.1804838595625885</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3858151271758067</v>
+        <v>0.3817962196010587</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -11040,22 +11040,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2157607006484145</v>
+        <v>0.2173107006484145</v>
       </c>
       <c r="C98">
-        <v>-7242.63556272312</v>
+        <v>-7381.440938459247</v>
       </c>
       <c r="D98">
-        <v>3080.814263236057</v>
+        <v>3052.971906520337</v>
       </c>
       <c r="E98">
-        <v>5916.347923918368</v>
+        <v>6027.310942938776</v>
       </c>
       <c r="F98">
-        <v>10652.44982595918</v>
+        <v>10763.41284497958</v>
       </c>
       <c r="G98">
         <v>329</v>
@@ -11076,37 +11076,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M98">
-        <v>2139.011925052603</v>
+        <v>2161.293299271901</v>
       </c>
       <c r="N98">
-        <v>-1322.345258385936</v>
+        <v>-1344.626632605234</v>
       </c>
       <c r="O98">
-        <v>-350.421493472273</v>
+        <v>-356.326057640387</v>
       </c>
       <c r="P98">
-        <v>-971.9237649136629</v>
+        <v>-988.3005749648469</v>
       </c>
       <c r="Q98">
-        <v>-671.9237649136629</v>
+        <v>-688.3005749648469</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.062404886708239</v>
+        <v>1.401273182277652</v>
       </c>
       <c r="T98">
-        <v>23.47817290319259</v>
+        <v>31.30423053759012</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1011759981942806</v>
+        <v>0.1001329466665045</v>
       </c>
       <c r="W98">
-        <v>0.1804838595625885</v>
+        <v>0.1806933043093659</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3817962196010587</v>
+        <v>0.3778601761000169</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -11122,22 +11122,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2173107006484145</v>
+        <v>0.2188607006484145</v>
       </c>
       <c r="C99">
-        <v>-7381.440938459247</v>
+        <v>-7519.747579904482</v>
       </c>
       <c r="D99">
-        <v>3052.971906520337</v>
+        <v>3025.62828409551</v>
       </c>
       <c r="E99">
-        <v>6027.310942938776</v>
+        <v>6138.273961959184</v>
       </c>
       <c r="F99">
-        <v>10763.41284497958</v>
+        <v>10874.37586399999</v>
       </c>
       <c r="G99">
         <v>329</v>
@@ -11158,37 +11158,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M99">
-        <v>2161.293299271901</v>
+        <v>2183.574673491199</v>
       </c>
       <c r="N99">
-        <v>-1344.626632605234</v>
+        <v>-1366.908006824532</v>
       </c>
       <c r="O99">
-        <v>-356.326057640387</v>
+        <v>-362.230621808501</v>
       </c>
       <c r="P99">
-        <v>-988.3005749648469</v>
+        <v>-1004.677385016031</v>
       </c>
       <c r="Q99">
-        <v>-688.3005749648469</v>
+        <v>-704.6773850160309</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.401273182277652</v>
+        <v>2.079009773416477</v>
       </c>
       <c r="T99">
-        <v>31.30423053759012</v>
+        <v>46.95634580638517</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1001329466665045</v>
+        <v>0.09911118190460136</v>
       </c>
       <c r="W99">
-        <v>0.1806933043093659</v>
+        <v>0.180898474673556</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3778601761000169</v>
+        <v>0.3740044600173635</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -11204,22 +11204,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2188607006484145</v>
+        <v>0.2204107006484145</v>
       </c>
       <c r="C100">
-        <v>-7519.747579904482</v>
+        <v>-7657.568768687297</v>
       </c>
       <c r="D100">
-        <v>3025.62828409551</v>
+        <v>2998.770114333103</v>
       </c>
       <c r="E100">
-        <v>6138.273961959184</v>
+        <v>6249.236980979592</v>
       </c>
       <c r="F100">
-        <v>10874.37586399999</v>
+        <v>10985.3388830204</v>
       </c>
       <c r="G100">
         <v>329</v>
@@ -11240,37 +11240,37 @@
         <v>816.6666666666667</v>
       </c>
       <c r="M100">
-        <v>2183.574673491199</v>
+        <v>2205.856047710497</v>
       </c>
       <c r="N100">
-        <v>-1366.908006824532</v>
+        <v>-1389.18938104383</v>
       </c>
       <c r="O100">
-        <v>-362.230621808501</v>
+        <v>-368.1351859766149</v>
       </c>
       <c r="P100">
-        <v>-1004.677385016031</v>
+        <v>-1021.054195067215</v>
       </c>
       <c r="Q100">
-        <v>-704.6773850160309</v>
+        <v>-721.0541950672149</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.079009773416477</v>
+        <v>4.112219546832955</v>
       </c>
       <c r="T100">
-        <v>46.95634580638517</v>
+        <v>93.91269161277035</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.09911118190460136</v>
+        <v>0.09811005885505993</v>
       </c>
       <c r="W100">
-        <v>0.180898474673556</v>
+        <v>0.181099500181904</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -11278,91 +11278,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3740044600173635</v>
+        <v>0.3702266371889054</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2204107006484145</v>
-      </c>
-      <c r="C101">
-        <v>-7657.568768687297</v>
-      </c>
-      <c r="D101">
-        <v>2998.770114333103</v>
-      </c>
-      <c r="E101">
-        <v>6249.236980979592</v>
-      </c>
-      <c r="F101">
-        <v>10985.3388830204</v>
-      </c>
-      <c r="G101">
-        <v>329</v>
-      </c>
-      <c r="H101">
-        <v>6360.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1116.666666666667</v>
-      </c>
-      <c r="K101">
-        <v>300</v>
-      </c>
-      <c r="L101">
-        <v>816.6666666666667</v>
-      </c>
-      <c r="M101">
-        <v>2205.856047710497</v>
-      </c>
-      <c r="N101">
-        <v>-1389.18938104383</v>
-      </c>
-      <c r="O101">
-        <v>-368.1351859766149</v>
-      </c>
-      <c r="P101">
-        <v>-1021.054195067215</v>
-      </c>
-      <c r="Q101">
-        <v>-721.0541950672149</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.112219546832955</v>
-      </c>
-      <c r="T101">
-        <v>93.91269161277035</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.09811005885505993</v>
-      </c>
-      <c r="W101">
-        <v>0.181099500181904</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3702266371889054</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
